--- a/src/service_ia/training/version_1/fit/report_fit_grid.xlsx
+++ b/src/service_ia/training/version_1/fit/report_fit_grid.xlsx
@@ -2,28 +2,33 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report BEST FIT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report ML FIT" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -37,12 +42,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -55,14 +75,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -425,41 +448,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>features</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>best_estimator</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>best_params</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>best_scorer</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>scorer</t>
         </is>
@@ -689,14 +712,275 @@
           <t>{'colsample_bytree': 1.0, 'learning_rate': 0.01, 'max_depth': 5, 'num_leaves': 31, 'scale_pos_weight': 2, 'subsample': 1.0, 'n_estimators': 3288}</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0.53986424362829</t>
-        </is>
+      <c r="F7" t="n">
+        <v>0.53986424362829</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>make_scorer(accuracy_score, response_method='predict')</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_2_5</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>DecisionTreeClassifier(criterion='log_loss', max_depth=5, max_features='log2',
+                       min_samples_split=5)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>{'class_weight': None, 'criterion': 'log_loss', 'max_depth': 5, 'max_features': 'log2', 'min_samples_leaf': 1, 'min_samples_split': 5}</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0.5641867799100504</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>make_scorer(accuracy_score, response_method='predict')</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>estimator</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>cross_val_score</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>cross_val</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>precisions</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>recalls</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>threshold</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>thresholds</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>confusion matrix</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>macro avg</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>weighted avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>StackingClassifier(cv=5,
+                   estimators=[('dt', DecisionTreeClassifier(max_depth=5)),
+                               ('svc', SVC(probability=True)),
+                               ('rf', RandomForestClassifier()),
+                               ('knn', KNeighborsClassifier()),
+                               ('xgb',
+                                XGBClassifier(base_score=None, booster=None,
+                                              callbacks=None,
+                                              colsample_bylevel=None,
+                                              colsample_bynode=None,
+                                              colsample_bytree=None,
+                                              device=None,
+                                              early_stopping_rounds=None,
+                                              enable_...
+                                              max_cat_threshold=None,
+                                              max_cat_to_onehot=None,
+                                              max_delta_step=None,
+                                              max_depth=None, max_leaves=None,
+                                              min_child_weight=None,
+                                              missing=nan,
+                                              monotone_constraints=None,
+                                              multi_strategy=None,
+                                              n_estimators=None, n_jobs=None,
+                                              num_parallel_tree=None,
+                                              random_state=None, ...))],
+                   final_estimator=LogisticRegression(), n_jobs=-1,
+                   passthrough=True, stack_method='predict_proba', verbose=2)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_2_5/stack_method=predict_proba, passthrough=True</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>[0.57103064 0.55617456 0.58170845 0.55803157 0.56685237]</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([48.64854026, 52.55283785, 53.21854568, 51.34932375, 53.37448597]), 'score_time': array([5.23752403, 3.72090983, 4.39939737, 4.26069283, 4.88031125]), 'test_accuracy': array([0.57149489, 0.55942433, 0.5812442 , 0.56081708, 0.56499536]), 'test_precision': array([0.58297506, 0.56929461, 0.59129693, 0.56888169, 0.57390586]), 'test_recall': array([0.60752688, 0.61469534, 0.62096774, 0.62903226, 0.62275986]), 'test_f1': array([0.59499781, 0.59112452, 0.60576923, 0.59744681, 0.59733563]), 'test_roc_auc': array([0.59219032, 0.59100075, 0.59731632, 0.58371921, 0.58888405]), 'test_average_precision': array([0.603642  , 0.61557191, 0.59436882, 0.60101684, 0.6103649 ]), 'test_neg_log_loss': array([-0.68005465, -0.67773841, -0.68039188, -0.68195534, -0.67923023]), 'test_neg_brier_score': array([-0.24324631, -0.24254679, -0.2433393 , -0.24426651, -0.24323128]), 'test_f1_macro': array([0.57004696, 0.55676004, 0.57961729, 0.55715037, 0.56217109]), 'test_f1_weighted': array([0.57095047, 0.55800444, 0.58056429, 0.55860957, 0.56344446]), 'test_balanced_accuracy': array([0.57014109, 0.55734767, 0.57975169, 0.55825409, 0.56282502])}</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.5677808727948004</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.5968649865766</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.5775096363331658</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>[0.51810585 0.57750964 1.        ]</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.6175627240143369</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>[1.         0.61756272 0.        ]</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>[[2669 2521]
+ [2134 3446]]</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5556943576931085, 'recall': 0.5142581888246628, 'f1-score': 0.5341739217452216, 'support': 5190.0}</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5775096363331658, 'recall': 0.6175627240143369, 'f1-score': 0.5968649865766, 'support': 5580.0}</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5666019970131371, 'recall': 0.5659104564194999, 'f1-score': 0.5655194541609108, 'support': 10770.0}</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5669969811667871, 'recall': 0.5677808727948004, 'f1-score': 0.566654529150894, 'support': 10770.0}</t>
         </is>
       </c>
     </row>

--- a/src/service_ia/training/version_1/fit/report_fit_grid.xlsx
+++ b/src/service_ia/training/version_1/fit/report_fit_grid.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report BEST FIT" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report ML FIT" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Report BEST FIT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Report ML FIT" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -732,11 +732,7 @@
           <t>t=mean/event=under_over_2_5</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>DecisionTreeClassifier(criterion='log_loss', max_depth=5, max_features='log2',
@@ -748,12 +744,267 @@
           <t>{'class_weight': None, 'criterion': 'log_loss', 'max_depth': 5, 'max_features': 'log2', 'min_samples_leaf': 1, 'min_samples_split': 5}</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0.5641867799100504</t>
-        </is>
+      <c r="F8" t="n">
+        <v>0.5641867799100504</v>
       </c>
       <c r="G8" t="inlineStr">
+        <is>
+          <t>make_scorer(accuracy_score, response_method='predict')</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LogisticRegression(C=0.1, max_iter=6888, penalty='l1', solver='liblinear')</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>{'C': 0.1, 'class_weight': None, 'penalty': 'l1', 'solver': 'liblinear', 'max_iter': 6888}</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0.5727708106375731</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>make_scorer(accuracy_score, response_method='predict')</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>DecisionTreeClassifier(max_depth=5, max_features='sqrt', min_samples_split=10)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>{'class_weight': None, 'criterion': 'gini', 'max_depth': 5, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 10}</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5637502068504657</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>make_scorer(accuracy_score, response_method='predict')</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>DecisionTreeClassifier(class_weight='balanced', criterion='entropy',
+                       max_depth=5, max_features='sqrt', min_samples_split=5)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>{'class_weight': 'balanced', 'criterion': 'entropy', 'max_depth': 5, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 5}</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.5628779039433868</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>make_scorer(accuracy_score, response_method='predict')</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_1_5</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>DecisionTreeClassifier(max_depth=5, min_samples_leaf=2, min_samples_split=5)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>{'class_weight': None, 'criterion': 'gini', 'max_depth': 5, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 5}</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.5398653702318623</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>make_scorer(accuracy_score, response_method='predict')</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_2_5</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>DecisionTreeClassifier(max_depth=5, max_features='log2', min_samples_leaf=4,
+                       min_samples_split=10)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>{'class_weight': None, 'criterion': 'gini', 'max_depth': 5, 'max_features': 'log2', 'min_samples_leaf': 4, 'min_samples_split': 10}</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.5609903736799777</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>make_scorer(accuracy_score, response_method='predict')</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_2_5</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>DecisionTreeClassifier(max_depth=5, min_samples_split=5)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>{'class_weight': None, 'criterion': 'gini', 'max_depth': 5, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 5}</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.5398653702318624</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>make_scorer(accuracy_score, response_method='predict')</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_3_5</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>DecisionTreeClassifier(criterion='log_loss', max_depth=5, max_features='sqrt',
+                       min_samples_leaf=4, min_samples_split=10)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>{'class_weight': None, 'criterion': 'log_loss', 'max_depth': 5, 'max_features': 'sqrt', 'min_samples_leaf': 4, 'min_samples_split': 10}</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.5589601297703407</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>make_scorer(accuracy_score, response_method='predict')</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_3_5</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>DecisionTreeClassifier(max_depth=5, min_samples_leaf=2)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>{'class_weight': None, 'criterion': 'gini', 'max_depth': 5, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 2}</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0.5397157816005983</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>make_scorer(accuracy_score, response_method='predict')</t>
         </is>
@@ -770,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -917,40 +1168,30 @@
           <t>{'fit_time': array([48.64854026, 52.55283785, 53.21854568, 51.34932375, 53.37448597]), 'score_time': array([5.23752403, 3.72090983, 4.39939737, 4.26069283, 4.88031125]), 'test_accuracy': array([0.57149489, 0.55942433, 0.5812442 , 0.56081708, 0.56499536]), 'test_precision': array([0.58297506, 0.56929461, 0.59129693, 0.56888169, 0.57390586]), 'test_recall': array([0.60752688, 0.61469534, 0.62096774, 0.62903226, 0.62275986]), 'test_f1': array([0.59499781, 0.59112452, 0.60576923, 0.59744681, 0.59733563]), 'test_roc_auc': array([0.59219032, 0.59100075, 0.59731632, 0.58371921, 0.58888405]), 'test_average_precision': array([0.603642  , 0.61557191, 0.59436882, 0.60101684, 0.6103649 ]), 'test_neg_log_loss': array([-0.68005465, -0.67773841, -0.68039188, -0.68195534, -0.67923023]), 'test_neg_brier_score': array([-0.24324631, -0.24254679, -0.2433393 , -0.24426651, -0.24323128]), 'test_f1_macro': array([0.57004696, 0.55676004, 0.57961729, 0.55715037, 0.56217109]), 'test_f1_weighted': array([0.57095047, 0.55800444, 0.58056429, 0.55860957, 0.56344446]), 'test_balanced_accuracy': array([0.57014109, 0.55734767, 0.57975169, 0.55825409, 0.56282502])}</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0.5677808727948004</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.5968649865766</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.5775096363331658</t>
-        </is>
+      <c r="F2" t="n">
+        <v>0.5677808727948004</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5968649865766</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.5775096363331658</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>[0.51810585 0.57750964 1.        ]</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.6175627240143369</t>
-        </is>
+      <c r="J2" t="n">
+        <v>0.6175627240143369</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>[1.         0.61756272 0.        ]</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="L2" t="n">
+        <v>0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -981,6 +1222,4816 @@
       <c r="R2" t="inlineStr">
         <is>
           <t>{'precision': 0.5669969811667871, 'recall': 0.5677808727948004, 'f1-score': 0.566654529150894, 'support': 10770.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>StackingClassifier(cv=5,
+                   estimators=[('dt', DecisionTreeClassifier(max_depth=5)),
+                               ('svc', SVC(probability=True)),
+                               ('rf', RandomForestClassifier()),
+                               ('knn', KNeighborsClassifier()),
+                               ('xgb',
+                                XGBClassifier(base_score=None, booster=None,
+                                              callbacks=None,
+                                              colsample_bylevel=None,
+                                              colsample_bynode=None,
+                                              colsample_bytree=None,
+                                              device=None,
+                                              early_stopping_rounds=None,
+                                              enable_...
+                                              max_cat_threshold=None,
+                                              max_cat_to_onehot=None,
+                                              max_delta_step=None,
+                                              max_depth=None, max_leaves=None,
+                                              min_child_weight=None,
+                                              missing=nan,
+                                              monotone_constraints=None,
+                                              multi_strategy=None,
+                                              n_estimators=None, n_jobs=None,
+                                              num_parallel_tree=None,
+                                              random_state=None, ...))],
+                   final_estimator=LogisticRegression(), n_jobs=-1,
+                   passthrough=True, stack_method='predict_proba', verbose=2)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_2_5/stack_method=predict_proba, passthrough=True</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>[0.56499536 0.56406685 0.57753018 0.54642526 0.5636026 ]</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([26.42789984, 25.84443998, 25.37718415, 31.75025082, 34.83344603]), 'score_time': array([2.60132217, 2.61868644, 2.5959537 , 2.55013943, 2.61822009]), 'test_accuracy': array([0.56778087, 0.56313835, 0.57428041, 0.54735376, 0.56545961]), 'test_precision': array([0.57885763, 0.57359125, 0.58482523, 0.55717762, 0.575     ]), 'test_recall': array([0.60842294, 0.61111111, 0.61469534, 0.6155914 , 0.61827957]), 'test_f1': array([0.59327217, 0.59175705, 0.59938838, 0.58492976, 0.59585492]), 'test_roc_auc': array([0.59467994, 0.59069602, 0.59890384, 0.57549154, 0.59518235]), 'test_average_precision': array([0.60212428, 0.61604568, 0.59813704, 0.59254384, 0.61226915]), 'test_neg_log_loss': array([-0.67974133, -0.67791013, -0.6801151 , -0.68491895, -0.67796065]), 'test_neg_brier_score': array([-0.24303547, -0.24265279, -0.24318821, -0.24554696, -0.24259025]), 'test_f1_macro': array([0.5660764 , 0.56098087, 0.57260157, 0.54361342, 0.5629877 ]), 'test_f1_weighted': array([0.56706121, 0.56209533, 0.57357157, 0.54510956, 0.56417788]), 'test_balanced_accuracy': array([0.56625386, 0.5613359 , 0.57276193, 0.54478992, 0.56347505])}</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5636025998142989</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5944779982743744</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5732113144758736</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>[0.51810585 0.57321131 1.        ]</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.6173835125448028</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>[1.         0.61738351 0.        ]</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>[[2625 2565]
+ [2135 3445]]</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5514705882352942, 'recall': 0.5057803468208093, 'f1-score': 0.5276381909547738, 'support': 5190.0}</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5732113144758736, 'recall': 0.6173835125448028, 'f1-score': 0.5944779982743744, 'support': 5580.0}</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5623409513555839, 'recall': 0.5615819296828061, 'f1-score': 0.5610580946145741, 'support': 10770.0}</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>{'precision': 0.562734585674703, 'recall': 0.5636025998142989, 'f1-score': 0.5622682861120042, 'support': 10770.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>StackingClassifier(cv=5,
+                   estimators=[('dt', DecisionTreeClassifier(max_depth=5)),
+                               ('svc', SVC(probability=True)),
+                               ('rf', RandomForestClassifier()),
+                               ('knn', KNeighborsClassifier()),
+                               ('xgb',
+                                XGBClassifier(base_score=None, booster=None,
+                                              callbacks=None,
+                                              colsample_bylevel=None,
+                                              colsample_bynode=None,
+                                              colsample_bytree=None,
+                                              device=None,
+                                              early_stopping_rounds=None,
+                                              enable_...
+                                              max_cat_threshold=None,
+                                              max_cat_to_onehot=None,
+                                              max_delta_step=None,
+                                              max_depth=None, max_leaves=None,
+                                              min_child_weight=None,
+                                              missing=nan,
+                                              monotone_constraints=None,
+                                              multi_strategy=None,
+                                              n_estimators=None, n_jobs=None,
+                                              num_parallel_tree=None,
+                                              random_state=None, ...))],
+                   final_estimator=LogisticRegression(), n_jobs=-1,
+                   passthrough=True, stack_method='predict_proba', verbose=2)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_2_5/stack_method=predict_proba, passthrough=True</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>[0.5508839  0.54493308 0.5583174  0.52724665 0.53871893]</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([25.04120255, 25.76406431, 22.71213722, 27.16420197, 36.06487393]), 'score_time': array([2.57305074, 2.51516724, 2.54362011, 2.50130033, 2.52404261]), 'test_accuracy': array([0.5480172 , 0.541587  , 0.54636711, 0.53919694, 0.53537285]), 'test_precision': array([0.56255626, 0.5573921 , 0.56032172, 0.55535055, 0.55156538]), 'test_recall': array([0.57603687, 0.5599631 , 0.57841328, 0.55535055, 0.55258303]), 'test_f1': array([0.56921676, 0.55867464, 0.56922379, 0.55535055, 0.55207373]), 'test_roc_auc': array([0.56976264, 0.56258786, 0.5698453 , 0.56189048, 0.55267912]), 'test_average_precision': array([0.60666846, 0.58749334, 0.59053101, 0.59020951, 0.58875379]), 'test_neg_log_loss': array([-0.68150746, -0.68422041, -0.68398041, -0.68563635, -0.68478597]), 'test_neg_brier_score': array([-0.24437159, -0.24564315, -0.2453262 , -0.24616498, -0.24606123]), 'test_f1_macro': array([0.54691994, 0.54089873, 0.5450864 , 0.53858798, 0.53472604]), 'test_f1_weighted': array([0.54774022, 0.54154451, 0.54596328, 0.53919694, 0.53535626]), 'test_balanced_accuracy': array([0.546947  , 0.54089425, 0.54515902, 0.53858798, 0.53472405])}</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5629997242900469</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.560989010989011</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>[0.5182105  0.56098901 1.        ]</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.5650249031543996</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>[1.        0.5650249 0.       ]</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>[[2643 2397]
+ [2358 3063]]</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>{'precision': 0.528494301139772, 'recall': 0.5244047619047619, 'f1-score': 0.5264415894831193, 'support': 5040.0}</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>{'precision': 0.560989010989011, 'recall': 0.5650249031543996, 'f1-score': 0.5629997242900469, 'support': 5421.0}</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5447416560643915, 'recall': 0.5447148325295808, 'f1-score': 0.544720656886583, 'support': 10461.0}</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>{'precision': 0.545333400852297, 'recall': 0.5454545454545454, 'f1-score': 0.545386398658949, 'support': 10461.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>StackingClassifier(cv=5,
+                   estimators=[('dt', DecisionTreeClassifier(max_depth=5)),
+                               ('svc', SVC(probability=True)),
+                               ('rf', RandomForestClassifier()),
+                               ('knn', KNeighborsClassifier()),
+                               ('xgb',
+                                XGBClassifier(base_score=None, booster=None,
+                                              callbacks=None,
+                                              colsample_bylevel=None,
+                                              colsample_bynode=None,
+                                              colsample_bytree=None,
+                                              device=None,
+                                              early_stopping_rounds=None,
+                                              enable_...
+                                              max_cat_threshold=None,
+                                              max_cat_to_onehot=None,
+                                              max_delta_step=None,
+                                              max_depth=None, max_leaves=None,
+                                              min_child_weight=None,
+                                              missing=nan,
+                                              monotone_constraints=None,
+                                              multi_strategy=None,
+                                              n_estimators=None, n_jobs=None,
+                                              num_parallel_tree=None,
+                                              random_state=None, ...))],
+                   final_estimator=LogisticRegression(), n_jobs=-1,
+                   passthrough=True, stack_method='predict_proba', verbose=2)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_1_5/stack_method=predict_proba, passthrough=True</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>[0.77031419 0.77031419 0.76923077 0.77139762 0.76923077]</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([4.37237048, 3.60950089, 4.15586877, 3.71965694, 3.75548053]), 'score_time': array([0.44126105, 0.46763706, 0.43728018, 0.47316599, 0.44547558]), 'test_accuracy': array([0.76923077, 0.77031419, 0.76923077, 0.77139762, 0.76923077]), 'test_precision': array([0.77006508, 0.77031419, 0.77006508, 0.77114967, 0.76923077]), 'test_recall': array([0.99859353, 1.        , 0.99859353, 1.        , 1.        ]), 'test_f1': array([0.86956522, 0.87025704, 0.86956522, 0.87078996, 0.86956522]), 'test_roc_auc': array([0.5486957 , 0.56295942, 0.59169254, 0.58236473, 0.58986973]), 'test_average_precision': array([0.80078379, 0.80978983, 0.83133821, 0.81780735, 0.82881629]), 'test_neg_log_loss': array([-0.53979719, -0.53474868, -0.52984052, -0.53098565, -0.52998053]), 'test_neg_brier_score': array([-0.17707156, -0.17552122, -0.17422871, -0.17390805, -0.17414642]), 'test_f1_macro': array([0.43478261, 0.43512852, 0.43478261, 0.44008981, 0.43478261]), 'test_f1_weighted': array([0.66983843, 0.67037135, 0.66983843, 0.67293854, 0.66889632]), 'test_balanced_accuracy': array([0.49929677, 0.5       , 0.49929677, 0.50235849, 0.5       ])}</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.7700975081256771</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8700869352271335</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7702146108822892</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>[0.77009751 0.77021461 1.        ]</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.9997186268992684</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>[1.         0.99971863 0.        ]</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>[[   1 1060]
+ [   1 3553]]</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5, 'recall': 0.000942507068803016, 'f1-score': 0.0018814675446848542, 'support': 1061.0}</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7702146108822892, 'recall': 0.9997186268992684, 'f1-score': 0.8700869352271335, 'support': 3554.0}</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6351073054411446, 'recall': 0.5003305669840357, 'f1-score': 0.4359842013859092, 'support': 4615.0}</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7080915984996003, 'recall': 0.7700975081256771, 'f1-score': 0.6704843347480267, 'support': 4615.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>StackingClassifier(cv=5,
+                   estimators=[('dt', DecisionTreeClassifier(max_depth=5)),
+                               ('svc', SVC(probability=True)),
+                               ('rf', RandomForestClassifier()),
+                               ('knn', KNeighborsClassifier()),
+                               ('xgb',
+                                XGBClassifier(base_score=None, booster=None,
+                                              callbacks=None,
+                                              colsample_bylevel=None,
+                                              colsample_bynode=None,
+                                              colsample_bytree=None,
+                                              device=None,
+                                              early_stopping_rounds=None,
+                                              enable_...
+                                              max_cat_threshold=None,
+                                              max_cat_to_onehot=None,
+                                              max_delta_step=None,
+                                              max_depth=None, max_leaves=None,
+                                              min_child_weight=None,
+                                              missing=nan,
+                                              monotone_constraints=None,
+                                              multi_strategy=None,
+                                              n_estimators=None, n_jobs=None,
+                                              num_parallel_tree=None,
+                                              random_state=None, ...))],
+                   final_estimator=LogisticRegression(), n_jobs=-1,
+                   passthrough=True, stack_method='predict_proba', verbose=2)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stack_method=predict_proba, passthrough=True</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>[0.76906552 0.77228786 0.77228786 0.76799141 0.77121375]</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([2.40257072, 2.33355474, 2.30675745, 2.51818275, 2.36752844]), 'score_time': array([0.44118571, 0.44171429, 0.44672132, 0.44014668, 0.44706655]), 'test_accuracy': array([0.76906552, 0.77228786, 0.77121375, 0.76799141, 0.77121375]), 'test_precision': array([0.77072121, 0.77321814, 0.77096774, 0.76964478, 0.77096774]), 'test_recall': array([0.99721448, 0.99721448, 1.        , 0.9972106 , 1.        ]), 'test_f1': array([0.86945962, 0.87104623, 0.87067395, 0.86877278, 0.87067395]), 'test_roc_auc': array([0.62591052, 0.60974015, 0.57857897, 0.59946037, 0.64352377]), 'test_average_precision': array([0.8379709 , 0.83897166, 0.80653927, 0.84089961, 0.84852645]), 'test_neg_log_loss': array([-0.52215391, -0.52399417, -0.53797343, -0.52752437, -0.51782259]), 'test_neg_brier_score': array([-0.17090273, -0.17184635, -0.17541433, -0.17369188, -0.1694317 ]), 'test_f1_macro': array([0.43472981, 0.44928458, 0.43998814, 0.43438639, 0.43998814]), 'test_f1_weighted': array([0.67053922, 0.6780597 , 0.67267876, 0.66907635, 0.67267876]), 'test_balanced_accuracy': array([0.49860724, 0.5056495 , 0.50233645, 0.4986053 , 0.50233645])}</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.7707841031149302</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8703366144124438</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.7714347264110297</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>[0.77056928 0.77143473 1.        ]</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.9983272930025092</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>[1.         0.99832729 0.        ]</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>[[   7 1061]
+ [   6 3581]]</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5384615384615384, 'recall': 0.006554307116104869, 'f1-score': 0.012950971322849213, 'support': 1068.0}</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7714347264110297, 'recall': 0.9983272930025091, 'f1-score': 0.8703366144124438, 'support': 3587.0}</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>{'precision': 0.654948132436284, 'recall': 0.502440800059307, 'f1-score': 0.4416437928676465, 'support': 4655.0}</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7179835202391593, 'recall': 0.7707841031149302, 'f1-score': 0.6736260092954327, 'support': 4655.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>StackingClassifier(cv=5,
+                   estimators=[('dt', DecisionTreeClassifier(max_depth=5)),
+                               ('svc', SVC(probability=True)),
+                               ('rf', RandomForestClassifier()),
+                               ('knn', KNeighborsClassifier()),
+                               ('xgb',
+                                XGBClassifier(base_score=None, booster=None,
+                                              callbacks=None,
+                                              colsample_bylevel=None,
+                                              colsample_bynode=None,
+                                              colsample_bytree=None,
+                                              device=None,
+                                              early_stopping_rounds=None,
+                                              enable_...
+                                              max_cat_threshold=None,
+                                              max_cat_to_onehot=None,
+                                              max_delta_step=None,
+                                              max_depth=None, max_leaves=None,
+                                              min_child_weight=None,
+                                              missing=nan,
+                                              monotone_constraints=None,
+                                              multi_strategy=None,
+                                              n_estimators=None, n_jobs=None,
+                                              num_parallel_tree=None,
+                                              random_state=None, ...))],
+                   final_estimator=LogisticRegression(), n_jobs=-1,
+                   passthrough=True, stack_method='predict_proba', verbose=2)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_3_5/stack_method=predict_proba, passthrough=True</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>[0.69214209 0.6875     0.69827586 0.6875     0.69181034]</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([4.06253624, 3.20835686, 3.79213381, 3.15583324, 3.26931882]), 'score_time': array([0.48980594, 0.49456286, 0.48803258, 0.49260569, 0.49571753]), 'test_accuracy': array([0.68998924, 0.69073276, 0.69612069, 0.6875    , 0.69612069]), 'test_precision': array([0.53846154, 0.54385965, 0.56923077, 0.50943396, 0.58823529]), 'test_recall': array([0.09589041, 0.10616438, 0.12714777, 0.09278351, 0.10309278]), 'test_f1': array([0.1627907 , 0.17765043, 0.20786517, 0.15697674, 0.1754386 ]), 'test_roc_auc': array([0.6365562 , 0.6319947 , 0.62897387, 0.60310627, 0.65332556]), 'test_average_precision': array([0.43731563, 0.43476439, 0.44799271, 0.40595649, 0.45358691]), 'test_neg_log_loss': array([-0.597906  , -0.59775255, -0.5992073 , -0.61206085, -0.59247207]), 'test_neg_brier_score': array([-0.20505578, -0.2053674 , -0.20476709, -0.21016937, -0.202449  ]), 'test_f1_macro': array([0.48628306, 0.49360292, 0.50993258, 0.4825889 , 0.49458852]), 'test_f1_weighted': array([0.60641747, 0.61072324, 0.62255686, 0.60399171, 0.61358192]), 'test_balanced_accuracy': array([0.5291069 , 0.53264194, 0.54159586, 0.52598359, 0.53506288])}</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.6905839258780435</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.1737629459148446</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.5373665480427047</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>[0.31394096 0.53736655 1.        ]</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.1036376115305422</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>[1.         0.10363761 0.        ]</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>[[3054  130]
+ [1306  151]]</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7004587155963303, 'recall': 0.9591708542713567, 'f1-score': 0.8096500530222693, 'support': 3184.0}</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5373665480427047, 'recall': 0.10363761153054221, 'f1-score': 0.17376294591484465, 'support': 1457.0}</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6189126318195175, 'recall': 0.5314042329009495, 'f1-score': 0.491706499468557, 'support': 4641.0}</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6492574037830072, 'recall': 0.6905839258780435, 'f1-score': 0.6100190435295915, 'support': 4641.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>StackingClassifier(cv=5,
+                   estimators=[('dt', DecisionTreeClassifier(max_depth=5)),
+                               ('svc', SVC(probability=True)),
+                               ('rf', RandomForestClassifier()),
+                               ('knn', KNeighborsClassifier()),
+                               ('xgb',
+                                XGBClassifier(base_score=None, booster=None,
+                                              callbacks=None,
+                                              colsample_bylevel=None,
+                                              colsample_bynode=None,
+                                              colsample_bytree=None,
+                                              device=None,
+                                              early_stopping_rounds=None,
+                                              enable_...
+                                              max_cat_threshold=None,
+                                              max_cat_to_onehot=None,
+                                              max_delta_step=None,
+                                              max_depth=None, max_leaves=None,
+                                              min_child_weight=None,
+                                              missing=nan,
+                                              monotone_constraints=None,
+                                              multi_strategy=None,
+                                              n_estimators=None, n_jobs=None,
+                                              num_parallel_tree=None,
+                                              random_state=None, ...))],
+                   final_estimator=LogisticRegression(), n_jobs=-1,
+                   passthrough=True, stack_method='predict_proba', verbose=2)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_3_5/stack_method=predict_proba, passthrough=True</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>[0.68708241 0.68485523 0.68040089 0.68673356 0.68338907]</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([3.81921411, 3.29809117, 3.40056705, 3.2749722 , 3.55227518]), 'score_time': array([0.48139882, 0.49725246, 0.47562408, 0.47332025, 0.49267435]), 'test_accuracy': array([0.68596882, 0.68708241, 0.67928731, 0.68896321, 0.68896321]), 'test_precision': array([0.45454545, 0.5       , 0.        , 0.55555556, 0.75      ]), 'test_recall': array([0.01779359, 0.01067616, 0.        , 0.03558719, 0.01067616]), 'test_f1': array([0.03424658, 0.02090592, 0.        , 0.06688963, 0.02105263]), 'test_roc_auc': array([0.61043276, 0.5674109 , 0.54656039, 0.57640847, 0.62955239]), 'test_average_precision': array([0.39043574, 0.37455958, 0.34519984, 0.37701519, 0.40396804]), 'test_neg_log_loss': array([-0.60729287, -0.61512098, -0.62346681, -0.61589082, -0.61333049]), 'test_neg_brier_score': array([-0.20929889, -0.21229777, -0.21566822, -0.2120726 , -0.20780669]), 'test_f1_macro': array([0.42337329, 0.41734494, 0.40450928, 0.44013378, 0.41808099]), 'test_f1_weighted': array([0.56897081, 0.56567847, 0.55586242, 0.57952819, 0.56635802]), 'test_balanced_accuracy': array([0.50403456, 0.50290696, 0.49432739, 0.51130009, 0.50452639])}</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0.6867201426024956</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.0276625172890733</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.4878048780487805</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>[0.31305704 0.48780488 1.        ]</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.0142348754448398</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>[1.         0.01423488 0.        ]</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>[[3062   21]
+ [1385   20]]</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6885540814031932, 'recall': 0.9931884528057088, 'f1-score': 0.8132802124833998, 'support': 3083.0}</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>{'precision': 0.4878048780487805, 'recall': 0.014234875444839857, 'f1-score': 0.027662517289073305, 'support': 1405.0}</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5881794797259868, 'recall': 0.5037116641252743, 'f1-score': 0.42047136488623654, 'support': 4488.0}</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6257081298183114, 'recall': 0.6867201426024956, 'f1-score': 0.5673370614700244, 'support': 4488.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>XGBClassifier(base_score=None, booster=None, callbacks=None,
+              colsample_bylevel=None, colsample_bynode=None,
+              colsample_bytree=None, device=None, early_stopping_rounds=None,
+              enable_categorical=False, eval_metric='logloss',
+              feature_types=None, gamma=None, grow_policy=None,
+              importance_type=None, interaction_constraints=None,
+              learning_rate=0.05, max_bin=None, max_cat_threshold=None,
+              max_cat_to_onehot=None, max_delta_step=None, max_depth=3,
+              max_leaves=None, min_child_weight=None, missing=nan,
+              monotone_constraints=None, multi_strategy=None, n_estimators=500,
+              n_jobs=None, num_parallel_tree=None, random_state=None, ...)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>[0.75617615 0.76047261 0.76369495 0.76262084 0.76691729]</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.13855481, 0.12726831, 0.13131046, 0.12889433, 0.13300991]), 'score_time': array([0.01666117, 0.01109195, 0.01612139, 0.01612329, 0.01593947]), 'test_accuracy': array([0.75617615, 0.76047261, 0.76369495, 0.76262084, 0.76691729]), 'test_precision': array([0.77740113, 0.77469478, 0.77458564, 0.77133479, 0.77412281]), 'test_recall': array([0.95821727, 0.97214485, 0.9776848 , 0.9832636 , 0.9846583 ]), 'test_f1': array([0.85839052, 0.86226065, 0.86436498, 0.86450031, 0.86678944]), 'test_roc_auc': array([0.55784194, 0.5670518 , 0.54189966, 0.55415868, 0.58724045]), 'test_average_precision': array([0.80451924, 0.81629614, 0.78585824, 0.8026437 , 0.81617397]), 'test_neg_log_loss': array([-0.56046317, -0.54855316, -0.56942518, -0.55297566, -0.54410767]), 'test_neg_brier_score': array([-0.18401497, -0.18060734, -0.18428221, -0.18153299, -0.17786793]), 'test_f1_macro': array([0.49097132, 0.47228259, 0.47384916, 0.45389517, 0.46772948]), 'test_f1_weighted': array([0.6902696 , 0.68381742, 0.68483676, 0.67573662, 0.68333331]), 'test_balanced_accuracy': array([0.51666732, 0.5095466 , 0.51220688, 0.50331404, 0.51102074])}</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0.7619763694951665</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8632773938795657</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.7744077927828205</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>[0.77056928 0.77440779 1.        ]</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.9751881795372176</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>[1.         0.97518818 0.        ]</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>[[  49 1019]
+ [  89 3498]]</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>{'precision': 0.35507246376811596, 'recall': 0.04588014981273408, 'f1-score': 0.0812603648424544, 'support': 1068.0}</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7744077927828205, 'recall': 0.9751881795372177, 'f1-score': 0.8632773938795657, 'support': 3587.0}</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5647401282754683, 'recall': 0.5105341646749759, 'f1-score': 0.47226887936101003, 'support': 4655.0}</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6781993864696724, 'recall': 0.7619763694951665, 'f1-score': 0.6838586641241124, 'support': 4655.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>XGBClassifier(base_score=None, booster=None, callbacks=None,
+              colsample_bylevel=None, colsample_bynode=None,
+              colsample_bytree=None, device=None, early_stopping_rounds=None,
+              enable_categorical=False, eval_metric='logloss',
+              feature_types=None, gamma=None, grow_policy=None,
+              importance_type=None, interaction_constraints=None,
+              learning_rate=0.05, max_bin=None, max_cat_threshold=None,
+              max_cat_to_onehot=None, max_delta_step=None, max_depth=3,
+              max_leaves=None, min_child_weight=None, missing=nan,
+              monotone_constraints=None, multi_strategy=None, n_estimators=500,
+              n_jobs=None, num_parallel_tree=None, random_state=None, ...)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_1_5</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>[0.76489707 0.75947996 0.76273023 0.76923077 0.7616468 ]</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.12808132, 0.13727641, 0.13077712, 0.12326598, 0.12650585]), 'score_time': array([0.01413107, 0.01613259, 0.01728225, 0.01007915, 0.01108336]), 'test_accuracy': array([0.76489707, 0.75947996, 0.76273023, 0.76923077, 0.7616468 ]), 'test_precision': array([0.77444444, 0.77196885, 0.77152318, 0.77422907, 0.77041943]), 'test_recall': array([0.98030942, 0.97609001, 0.98312236, 0.98874824, 0.98309859]), 'test_f1': array([0.86530106, 0.8621118 , 0.86456401, 0.86843731, 0.86386139]), 'test_roc_auc': array([0.50791471, 0.53833294, 0.57355439, 0.5470703 , 0.55181512]), 'test_average_precision': array([0.76694819, 0.80138093, 0.81638298, 0.80007759, 0.79677492]), 'test_neg_log_loss': array([-0.57746583, -0.56125339, -0.5480026 , -0.5509037 , -0.55847941]), 'test_neg_brier_score': array([-0.1876536 , -0.18495497, -0.18029585, -0.18039218, -0.18300672]), 'test_f1_macro': array([0.4709484 , 0.46071692, 0.45411606, 0.46505566, 0.45366982]), 'test_f1_weighted': array([0.68414664, 0.67772239, 0.67601587, 0.68313523, 0.6745422 ]), 'test_balanced_accuracy': array([0.51138113, 0.50455444, 0.50335363, 0.51088355, 0.50328638])}</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0.7635969664138679</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8648581692059953</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.7725160433724275</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>[0.77009751 0.77251604 1.        ]</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.9822734946539112</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>[1.         0.98227349 0.        ]</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>[[  33 1028]
+ [  63 3491]]</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>{'precision': 0.34375, 'recall': 0.03110273327049953, 'f1-score': 0.05704407951598963, 'support': 1061.0}</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7725160433724275, 'recall': 0.9822734946539111, 'f1-score': 0.8648581692059953, 'support': 3554.0}</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5581330216862137, 'recall': 0.5066881139622054, 'f1-score': 0.4609511243609925, 'support': 4615.0}</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6739416615700125, 'recall': 0.7635969664138679, 'f1-score': 0.6791396970150753, 'support': 4615.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>XGBClassifier(base_score=None, booster=None, callbacks=None,
+              colsample_bylevel=None, colsample_bynode=None,
+              colsample_bytree=None, device=None, early_stopping_rounds=None,
+              enable_categorical=False, eval_metric='logloss',
+              feature_types=None, gamma=None, grow_policy=None,
+              importance_type=None, interaction_constraints=None,
+              learning_rate=0.05, max_bin=None, max_cat_threshold=None,
+              max_cat_to_onehot=None, max_delta_step=None, max_depth=3,
+              max_leaves=None, min_child_weight=None, missing=nan,
+              monotone_constraints=None, multi_strategy=None, n_estimators=500,
+              n_jobs=None, num_parallel_tree=None, random_state=None, ...)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_2_5</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>[0.57010214 0.5645311  0.56220984 0.54735376 0.55524605]</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.15520191, 0.14837146, 0.14864659, 0.15962815, 0.14642406]), 'score_time': array([0.0143621 , 0.01307082, 0.01462245, 0.01914454, 0.0151422 ]), 'test_accuracy': array([0.57010214, 0.5645311 , 0.56220984, 0.54735376, 0.55524605]), 'test_precision': array([0.58023649, 0.57416667, 0.57349193, 0.55949367, 0.56496711]), 'test_recall': array([0.6155914 , 0.61738351, 0.60483871, 0.59408602, 0.6155914 ]), 'test_f1': array([0.5973913 , 0.59499136, 0.58874836, 0.57627119, 0.58919383]), 'test_roc_auc': array([0.59020397, 0.58738804, 0.59267201, 0.56802785, 0.57246065]), 'test_average_precision': array([0.59794104, 0.60524451, 0.59655034, 0.58434128, 0.5920175 ]), 'test_neg_log_loss': array([-0.68401552, -0.68531054, -0.68480633, -0.69202768, -0.69192212]), 'test_neg_brier_score': array([-0.24519366, -0.24567722, -0.24525519, -0.24906007, -0.24880071]), 'test_f1_macro': array([0.56811796, 0.56205392, 0.56037915, 0.54523574, 0.55218801]), 'test_f1_weighted': array([0.569178  , 0.56324664, 0.56140644, 0.54635959, 0.55352805]), 'test_balanced_accuracy': array([0.568393  , 0.56254532, 0.56060818, 0.54559792, 0.55297874])}</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.5598885793871866</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5893259400450529</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.5704461590070447</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>[0.51810585 0.57044616 1.        ]</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.6094982078853046</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>[1.         0.60949821 0.        ]</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>[[2629 2561]
+ [2179 3401]]</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5467970049916805, 'recall': 0.5065510597302505, 'f1-score': 0.5259051810362072, 'support': 5190.0}</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5704461590070447, 'recall': 0.6094982078853046, 'f1-score': 0.5893259400450529, 'support': 5580.0}</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5586215819993625, 'recall': 0.5580246338077776, 'f1-score': 0.5576155605406301, 'support': 10770.0}</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5590497700247103, 'recall': 0.5598885793871866, 'f1-score': 0.5587638472636314, 'support': 10770.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>XGBClassifier(base_score=None, booster=None, callbacks=None,
+              colsample_bylevel=None, colsample_bynode=None,
+              colsample_bytree=None, device=None, early_stopping_rounds=None,
+              enable_categorical=False, eval_metric='logloss',
+              feature_types=None, gamma=None, grow_policy=None,
+              importance_type=None, interaction_constraints=None,
+              learning_rate=0.05, max_bin=None, max_cat_threshold=None,
+              max_cat_to_onehot=None, max_delta_step=None, max_depth=3,
+              max_leaves=None, min_child_weight=None, missing=nan,
+              monotone_constraints=None, multi_strategy=None, n_estimators=500,
+              n_jobs=None, num_parallel_tree=None, random_state=None, ...)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_2_5</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>[0.54610607 0.53298279 0.55927342 0.55449331 0.53202677]</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.15693569, 0.16297984, 0.16201711, 0.14890742, 0.16056538]), 'score_time': array([0.01413083, 0.01414323, 0.01922512, 0.01309013, 0.02017808]), 'test_accuracy': array([0.54610607, 0.53298279, 0.55927342, 0.55449331, 0.53202677]), 'test_precision': array([0.56141947, 0.54721977, 0.57055749, 0.5656304 , 0.54742547]), 'test_recall': array([0.56866359, 0.57195572, 0.60424354, 0.60424354, 0.55904059]), 'test_f1': array([0.56501832, 0.55931439, 0.58691756, 0.58429973, 0.55317207]), 'test_roc_auc': array([0.5714496 , 0.5486587 , 0.58066968, 0.56501951, 0.55647349]), 'test_average_precision': array([0.5935043 , 0.5665363 , 0.59695379, 0.58512149, 0.56904897]), 'test_neg_log_loss': array([-0.68652411, -0.69934939, -0.68600117, -0.69199675, -0.69734266]), 'test_neg_brier_score': array([-0.24655973, -0.25254249, -0.24617984, -0.24892605, -0.25138659]), 'test_f1_macro': array([0.54524642, 0.53130946, 0.55729075, 0.55219106, 0.5309764 ]), 'test_f1_weighted': array([0.54597381, 0.53232684, 0.55836706, 0.55335753, 0.53178274]), 'test_balanced_accuracy': array([0.5452445 , 0.53151357, 0.55757812, 0.5526178 , 0.53100839])}</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.5449765796768952</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.5698536056388939</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.558547387068202</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>[0.5182105  0.55854739 1.        ]</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.5816270060874378</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>[1.         0.58162701 0.        ]</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>[[2548 2492]
+ [2268 3153]]</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5290697674418605, 'recall': 0.5055555555555555, 'f1-score': 0.5170454545454546, 'support': 5040.0}</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>{'precision': 0.558547387068202, 'recall': 0.5816270060874378, 'f1-score': 0.5698536056388939, 'support': 5421.0}</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5438085772550312, 'recall': 0.5435912808214967, 'f1-score': 0.5434495300921742, 'support': 10461.0}</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5443453793331134, 'recall': 0.5449765796768952, 'f1-score': 0.5444111927232134, 'support': 10461.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>XGBClassifier(base_score=None, booster=None, callbacks=None,
+              colsample_bylevel=None, colsample_bynode=None,
+              colsample_bytree=None, device=None, early_stopping_rounds=None,
+              enable_categorical=False, eval_metric='logloss',
+              feature_types=None, gamma=None, grow_policy=None,
+              importance_type=None, interaction_constraints=None,
+              learning_rate=0.05, max_bin=None, max_cat_threshold=None,
+              max_cat_to_onehot=None, max_delta_step=None, max_depth=3,
+              max_leaves=None, min_child_weight=None, missing=nan,
+              monotone_constraints=None, multi_strategy=None, n_estimators=500,
+              n_jobs=None, num_parallel_tree=None, random_state=None, ...)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_3_5</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>[0.67384284 0.66271552 0.67672414 0.66487069 0.68426724]</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.13462067, 0.13385749, 0.1240418 , 0.13773799, 0.13007975]), 'score_time': array([0.01712942, 0.01613021, 0.01258445, 0.01611042, 0.01510859]), 'test_accuracy': array([0.67384284, 0.66271552, 0.67672414, 0.66487069, 0.68426724]), 'test_precision': array([0.44761905, 0.40707965, 0.45454545, 0.40909091, 0.49      ]), 'test_recall': array([0.1609589 , 0.15753425, 0.15463918, 0.15463918, 0.16838488]), 'test_f1': array([0.23677582, 0.22716049, 0.23076923, 0.2244389 , 0.25063939]), 'test_roc_auc': array([0.58419174, 0.59760274, 0.62162629, 0.58673335, 0.6227322 ]), 'test_average_precision': array([0.37522865, 0.4010584 , 0.40637176, 0.3800807 , 0.41222446]), 'test_neg_log_loss': array([-0.63034564, -0.62035044, -0.60923372, -0.63407781, -0.60835746]), 'test_neg_brier_score': array([-0.21852388, -0.21502752, -0.2102584 , -0.21883672, -0.20951438]), 'test_f1_macro': array([0.51469181, 0.5057236 , 0.51306538, 0.5053466 , 0.52531969]), 'test_f1_weighted': array([0.61790066, 0.60898406, 0.61831804, 0.61008158, 0.62773282]), 'test_balanced_accuracy': array([0.53495355, 0.52609417, 0.5349334 , 0.52629918, 0.54416104])}</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.6724843783667314</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.2338709677419354</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.4402277039848197</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>[0.31394096 0.4402277  1.        ]</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0.1592312971859986</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>[1.        0.1592313 0.       ]</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>[[2889  295]
+ [1225  232]]</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7022362664073895, 'recall': 0.9073492462311558, 'f1-score': 0.7917237599342286, 'support': 3184.0}</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>{'precision': 0.44022770398481975, 'recall': 0.15923129718599863, 'f1-score': 0.23387096774193547, 'support': 1457.0}</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5712319851961046, 'recall': 0.5332902717085772, 'f1-score': 0.512797363838082, 'support': 4641.0}</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6199810465302759, 'recall': 0.6724843783667314, 'f1-score': 0.616590918256967, 'support': 4641.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>XGBClassifier(base_score=None, booster=None, callbacks=None,
+              colsample_bylevel=None, colsample_bynode=None,
+              colsample_bytree=None, device=None, early_stopping_rounds=None,
+              enable_categorical=False, eval_metric='logloss',
+              feature_types=None, gamma=None, grow_policy=None,
+              importance_type=None, interaction_constraints=None,
+              learning_rate=0.05, max_bin=None, max_cat_threshold=None,
+              max_cat_to_onehot=None, max_delta_step=None, max_depth=3,
+              max_leaves=None, min_child_weight=None, missing=nan,
+              monotone_constraints=None, multi_strategy=None, n_estimators=500,
+              n_jobs=None, num_parallel_tree=None, random_state=None, ...)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_3_5</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>[0.65812918 0.66592428 0.65924276 0.67112598 0.66778149]</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.11895442, 0.13108897, 0.117939  , 0.14485407, 0.11998558]), 'score_time': array([0.01511717, 0.01107812, 0.01109409, 0.01928377, 0.01110888]), 'test_accuracy': array([0.65812918, 0.66592428, 0.65924276, 0.67112598, 0.66778149]), 'test_precision': array([0.37254902, 0.38554217, 0.37113402, 0.41860465, 0.41237113]), 'test_recall': array([0.13523132, 0.113879  , 0.12811388, 0.12811388, 0.14234875]), 'test_f1': array([0.19843342, 0.17582418, 0.19047619, 0.19618529, 0.21164021]), 'test_roc_auc': array([0.58803071, 0.55187828, 0.54894825, 0.58798008, 0.60622429]), 'test_average_precision': array([0.38005025, 0.35640164, 0.35328575, 0.37400277, 0.39655064]), 'test_neg_log_loss': array([-0.62564723, -0.63815382, -0.64741624, -0.62957069, -0.61313191]), 'test_neg_brier_score': array([-0.21688152, -0.22195876, -0.22419573, -0.21728504, -0.21188659]), 'test_f1_macro': array([0.4905826 , 0.48316348, 0.48733965, 0.49472894, 0.50059412]), 'test_f1_weighted': array([0.59989454, 0.59815904, 0.59841551, 0.60622518, 0.6085089 ]), 'test_balanced_accuracy': array([0.5157518 , 0.51561049, 0.5146242 , 0.52347252, 0.52490814])}</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.6644385026737968</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.1946524064171123</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3913978494623656</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>[0.31305704 0.39139785 1.        ]</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0.1295373665480427</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>[1.         0.12953737 0.        ]</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>[[2800  283]
+ [1223  182]]</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>{'precision': 0.695998011434253, 'recall': 0.90820629257217, 'f1-score': 0.7880664227413453, 'support': 3083.0}</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>{'precision': 0.3913978494623656, 'recall': 0.1295373665480427, 'f1-score': 0.1946524064171123, 'support': 1405.0}</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5436979304483093, 'recall': 0.5188718295601064, 'f1-score': 0.4913594145792288, 'support': 4488.0}</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6006407860397562, 'recall': 0.6644385026737968, 'f1-score': 0.602293986704013, 'support': 4488.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>GradientBoostingClassifier(learning_rate=0.5, max_depth=2, n_estimators=200,
+                           random_state=42)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>[0.72824919 0.73791622 0.73684211 0.73469388 0.73469388]</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.85441113, 0.8838501 , 0.86599135, 0.84159875, 0.83878636]), 'score_time': array([0.01132226, 0.00930619, 0.0100162 , 0.00899816, 0.0090301 ]), 'test_accuracy': array([0.72824919, 0.73791622, 0.73684211, 0.73469388, 0.73469388]), 'test_precision': array([0.77580071, 0.77622378, 0.7744186 , 0.77136259, 0.77136259]), 'test_recall': array([0.91086351, 0.9275766 , 0.92887029, 0.93165969, 0.93165969]), 'test_f1': array([0.83792441, 0.84517766, 0.84464172, 0.84396715, 0.84396715]), 'test_roc_auc': array([0.54025266, 0.56797704, 0.5214484 , 0.5461359 , 0.55780837]), 'test_average_precision': array([0.78935895, 0.81312096, 0.77677309, 0.79532449, 0.80713919]), 'test_neg_log_loss': array([-0.61190205, -0.59902635, -0.62213547, -0.60073446, -0.58921382]), 'test_neg_brier_score': array([-0.19896597, -0.19526674, -0.19958618, -0.19696321, -0.19307873]), 'test_f1_macro': array([0.49869642, 0.49601541, 0.4924963 , 0.47933125, 0.47933125]), 'test_f1_weighted': array([0.68270301, 0.68541062, 0.68275317, 0.67633647, 0.67633647]), 'test_balanced_accuracy': array([0.51176978, 0.51308408, 0.51116412, 0.50321302, 0.50321302])}</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.7344790547798067</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.8431472081218274</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.7738178430002329</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>[0.77056928 0.77381784 1.        ]</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0.9261221076108168</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>[1.         0.92612211 0.        ]</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>[[  97  971]
+ [ 265 3322]]</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>{'precision': 0.26795580110497236, 'recall': 0.09082397003745318, 'f1-score': 0.13566433566433567, 'support': 1068.0}</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7738178430002329, 'recall': 0.9261221076108168, 'f1-score': 0.8431472081218274, 'support': 3587.0}</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5208868220526026, 'recall': 0.508473038824135, 'f1-score': 0.48940577189308154, 'support': 4655.0}</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6577575506814062, 'recall': 0.7344790547798067, 'f1-score': 0.6808289035494104, 'support': 4655.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier(algorithm='SAMME',
+                   estimator=DecisionTreeClassifier(max_depth=1,
+                                                    max_leaf_nodes=16,
+                                                    random_state=42),
+                   learning_rate=0.5, n_estimators=500, random_state=42)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/samme</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>[0.77121375 0.77121375 0.77013963 0.77013963 0.77013963]</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([1.39736843, 1.39187717, 1.39476895, 1.39304328, 1.37707472]), 'score_time': array([0.09168386, 0.09143662, 0.09135699, 0.09146714, 0.0918479 ]), 'test_accuracy': array([0.77121375, 0.77121375, 0.77013963, 0.77013963, 0.77013963]), 'test_precision': array([0.77121375, 0.77121375, 0.77013963, 0.77013963, 0.77013963]), 'test_recall': array([1., 1., 1., 1., 1.]), 'test_f1': array([0.87083081, 0.87083081, 0.87014563, 0.87014563, 0.87014563]), 'test_roc_auc': array([0.60828854, 0.60070357, 0.58334963, 0.60320781, 0.64478812]), 'test_average_precision': array([0.82944675, 0.82918889, 0.80718928, 0.83798235, 0.84317899]), 'test_neg_log_loss': array([-0.54802491, -0.55032932, -0.55345478, -0.54842874, -0.5398329 ]), 'test_neg_brier_score': array([-0.18092735, -0.18184474, -0.18313252, -0.18117001, -0.17734212]), 'test_f1_macro': array([0.4354154 , 0.4354154 , 0.43507282, 0.43507282, 0.43507282]), 'test_f1_weighted': array([0.67159669, 0.67159669, 0.67013364, 0.67013364, 0.67013364]), 'test_balanced_accuracy': array([0.5, 0.5, 0.5, 0.5, 0.5])}</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.7705692803437164</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8704198010191702</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.7705692803437164</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>[0.77056928 1.        ]</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>[1. 0.]</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>[[   0 1068]
+ [   0 3587]]</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>{'precision': 0.0, 'recall': 0.0, 'f1-score': 0.0, 'support': 1068.0}</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7705692803437164, 'recall': 1.0, 'f1-score': 0.8704198010191702, 'support': 3587.0}</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>{'precision': 0.3852846401718582, 'recall': 0.5, 'f1-score': 0.4352099005095851, 'support': 4655.0}</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>{'precision': 0.593777015809433, 'recall': 0.7705692803437164, 'f1-score': 0.6707187596682628, 'support': 4655.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier(estimator=DecisionTreeClassifier(max_depth=1,
+                                                    max_leaf_nodes=16,
+                                                    random_state=42),
+                   learning_rate=0.5, n_estimators=500, random_state=42)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/samme_r</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>[0.76476907 0.7593985  0.76369495 0.76584318 0.76047261]</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([1.53047323, 1.52298665, 1.52639437, 1.5302937 , 1.53178453]), 'score_time': array([0.11807966, 0.1190567 , 0.12002873, 0.11611819, 0.12035251]), 'test_accuracy': array([0.76476907, 0.7593985 , 0.76369495, 0.76584318, 0.76047261]), 'test_precision': array([0.77447745, 0.77142857, 0.76923077, 0.7726776 , 0.76789588]), 'test_recall': array([0.98050139, 0.97771588, 0.9902371 , 0.986053  , 0.9874477 ]), 'test_f1': array([0.86539644, 0.86240786, 0.86585366, 0.86642157, 0.86394143]), 'test_roc_auc': array([0.57756614, 0.5593524 , 0.56073137, 0.56996963, 0.61050066]), 'test_average_precision': array([0.81533042, 0.80544653, 0.79561027, 0.81826009, 0.82451532]), 'test_neg_log_loss': array([-0.69141594, -0.69150047, -0.6914956 , -0.69123741, -0.69136109]), 'test_neg_brier_score': array([-0.24913449, -0.24917668, -0.24917422, -0.24904535, -0.24910699]), 'test_f1_macro': array([0.46674077, 0.45257145, 0.43743133, 0.45929774, 0.43197071]), 'test_f1_weighted': array([0.68298257, 0.67487799, 0.66889903, 0.67925831, 0.66535554]), 'test_balanced_accuracy': array([0.50903004, 0.50059503, 0.497455  , 0.50704519, 0.49372385])}</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0.7628356605800215</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.8648052902277737</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.771129067481983</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>[0.77056928 0.77112907 1.        ]</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0.9843880680234181</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>[1.         0.98438807 0.        ]</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>[[  20 1048]
+ [  56 3531]]</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>{'precision': 0.2631578947368421, 'recall': 0.018726591760299626, 'f1-score': 0.03496503496503497, 'support': 1068.0}</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>{'precision': 0.771129067481983, 'recall': 0.9843880680234179, 'f1-score': 0.8648052902277737, 'support': 3587.0}</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5171434811094126, 'recall': 0.5015573298918587, 'f1-score': 0.4498851625964044, 'support': 4655.0}</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>{'precision': 0.654584875754419, 'recall': 0.7628356605800215, 'f1-score': 0.6744144432630895, 'support': 4655.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier(max_leaf_nodes=16, n_estimators=500, n_jobs=-1,
+                       oob_score=True, random_state=42)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/oob=True</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>[0.77228786 0.77121375 0.77013963 0.77013963 0.77013963]</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.61107278, 0.60140872, 0.60665917, 0.60823607, 0.60907269]), 'score_time': array([0.11394691, 0.11506009, 0.10179448, 0.11505413, 0.10285997]), 'test_accuracy': array([0.77228786, 0.77121375, 0.77013963, 0.77013963, 0.77013963]), 'test_precision': array([0.77204301, 0.77121375, 0.77013963, 0.77013963, 0.77013963]), 'test_recall': array([1., 1., 1., 1., 1.]), 'test_f1': array([0.87135922, 0.87083081, 0.87014563, 0.87014563, 0.87014563]), 'test_roc_auc': array([0.59746034, 0.6038618 , 0.57430363, 0.60800454, 0.64027816]), 'test_average_precision': array([0.82434376, 0.83861592, 0.79681484, 0.82774095, 0.8422481 ]), 'test_neg_log_loss': array([-0.52765835, -0.52736003, -0.53365037, -0.5282831 , -0.51942104]), 'test_neg_brier_score': array([-0.17305997, -0.17295756, -0.17468523, -0.17337522, -0.16993952]), 'test_f1_macro': array([0.44035251, 0.4354154 , 0.43507282, 0.43507282, 0.43507282]), 'test_f1_weighted': array([0.6741424 , 0.67159669, 0.67013364, 0.67013364, 0.67013364]), 'test_balanced_accuracy': array([0.50234742, 0.5       , 0.5       , 0.5       , 0.5       ])}</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0.7707841031149302</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.8705254216721272</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.7707348517404383</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>[0.77056928 0.77073485 1.        ]</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>[1. 1. 0.]</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>[[   1 1067]
+ [   0 3587]]</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>{'precision': 1.0, 'recall': 0.0009363295880149813, 'f1-score': 0.0018709073900841909, 'support': 1068.0}</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7707348517404383, 'recall': 1.0, 'f1-score': 0.8705254216721272, 'support': 3587.0}</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>{'precision': 0.8853674258702191, 'recall': 0.5004681647940075, 'f1-score': 0.4361981645311057, 'support': 4655.0}</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>{'precision': 0.8233353196977341, 'recall': 0.7707841031149302, 'f1-score': 0.6712293913277186, 'support': 4655.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier(max_leaf_nodes=16, n_estimators=500, n_jobs=-1,
+                       random_state=42)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/oob=False</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>[0.77315436 0.76644295 0.77315436 0.77449664 0.77284946]</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.48572826, 0.48289371, 0.51194787, 0.48429799, 0.48120666]), 'score_time': array([0.10340333, 0.1023705 , 0.10291433, 0.10279894, 0.10275483]), 'test_accuracy': array([0.77315436, 0.76644295, 0.77315436, 0.77449664, 0.77284946]), 'test_precision': array([0.77315436, 0.77162162, 0.77388964, 0.77419355, 0.77284946]), 'test_recall': array([1.        , 0.99131944, 0.99826389, 1.        , 1.        ]), 'test_f1': array([0.87206662, 0.86778116, 0.87187263, 0.87272727, 0.87187263]), 'test_roc_auc': array([0.60304693, 0.60417694, 0.55870932, 0.60657051, 0.65563159]), 'test_average_precision': array([0.81649272, 0.82980977, 0.80603308, 0.82804846, 0.84881937]), 'test_neg_log_loss': array([-0.52443816, -0.52651045, -0.53423824, -0.52213549, -0.51389736]), 'test_neg_brier_score': array([-0.17140307, -0.17263753, -0.17500994, -0.17040059, -0.16776569]), 'test_f1_macro': array([0.43603331, 0.43389058, 0.44178427, 0.44224599, 0.43593632]), 'test_f1_weighted': array([0.67424211, 0.67092879, 0.67674529, 0.67742167, 0.67382629]), 'test_balanced_accuracy': array([0.5       , 0.49565972, 0.50209052, 0.50295858, 0.5       ])}</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0.7720193340494093</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.8712661106899166</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.7731431646932185</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>[0.77309345 0.77314316 1.        ]</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0.9979159430357764</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>[1.         0.99791594 0.        ]</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>[[   2  843]
+ [   6 2873]]</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>{'precision': 0.25, 'recall': 0.002366863905325444, 'f1-score': 0.004689331770222743, 'support': 845.0}</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7731431646932185, 'recall': 0.9979159430357764, 'f1-score': 0.8712661106899166, 'support': 2879.0}</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5115715823466093, 'recall': 0.5001414034705509, 'f1-score': 0.43797772123006967, 'support': 3724.0}</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6544385529408636, 'recall': 0.7720193340494093, 'f1-score': 0.674634161660072, 'support': 3724.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BaggingClassifier(estimator=DecisionTreeClassifier(max_leaf_nodes=16,
+                                                   random_state=42),
+                  max_samples=100, n_estimators=500, n_jobs=-1, random_state=42,
+                  verbose=1)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/bagging=True</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>[0.7704698  0.76510067 0.76912752 0.7704698  0.77284946]</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.19497371, 0.23759723, 0.24356532, 0.24769211, 0.27538991]), 'score_time': array([0.18973827, 0.21111131, 0.25090885, 0.21202159, 0.1319778 ]), 'test_accuracy': array([0.7704698 , 0.76510067, 0.76912752, 0.7704698 , 0.77284946]), 'test_precision': array([0.7704698 , 0.7699594 , 0.77016129, 0.7704698 , 0.77327935]), 'test_recall': array([1.        , 0.9912892 , 0.99825784, 1.        , 0.99825784]), 'test_f1': array([0.87035633, 0.86671744, 0.86949924, 0.87035633, 0.87148289]), 'test_roc_auc': array([0.56996149, 0.5732828 , 0.62128899, 0.59350612, 0.57678828]), 'test_average_precision': array([0.78823643, 0.80775879, 0.83638037, 0.81086403, 0.81682008]), 'test_neg_log_loss': array([-0.53841095, -0.53815304, -0.52405511, -0.53222872, -0.53478037]), 'test_neg_brier_score': array([-0.17575261, -0.17677033, -0.17173372, -0.17441662, -0.1756422 ]), 'test_f1_macro': array([0.43517817, 0.43900844, 0.43474962, 0.43517817, 0.44730214]), 'test_f1_weighted': array([0.67058327, 0.67037317, 0.66992291, 0.67058327, 0.67763685]), 'test_balanced_accuracy': array([0.5       , 0.49856858, 0.49912892, 0.5       , 0.50501127])}</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0.7696025778732546</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.8696840826245443</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.7708669897684437</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>[0.77067669 0.77086699 1.        ]</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0.997560975609756</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>[1.         0.99756098 0.        ]</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>[[   3  851]
+ [   7 2863]]</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>{'precision': 0.3, 'recall': 0.00351288056206089, 'f1-score': 0.006944444444444444, 'support': 854.0}</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7708669897684437, 'recall': 0.9975609756097561, 'f1-score': 0.8696840826245443, 'support': 2870.0}</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5354334948842219, 'recall': 0.5005369280859084, 'f1-score': 0.4383142635344944, 'support': 3724.0}</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6628862139192893, 'recall': 0.7696025778732546, 'f1-score': 0.6718377746208373, 'support': 3724.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BaggingClassifier(bootstrap=False,
+                  estimator=DecisionTreeClassifier(max_leaf_nodes=16,
+                                                   random_state=42),
+                  max_samples=100, n_estimators=500, n_jobs=-1, random_state=42,
+                  verbose=1)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/bagging=False</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>[0.7704698  0.76241611 0.76644295 0.7704698  0.7688172 ]</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.0978899 , 0.10007644, 0.10137033, 0.11344314, 0.09839535]), 'score_time': array([0.13113928, 0.13550091, 0.12052655, 0.12900639, 0.13376164]), 'test_accuracy': array([0.7704698 , 0.76241611, 0.76644295, 0.7704698 , 0.7688172 ]), 'test_precision': array([0.7704698 , 0.77303989, 0.76954178, 0.77266576, 0.77088949]), 'test_recall': array([1.        , 0.97909408, 0.99477352, 0.99477352, 0.99651568]), 'test_f1': array([0.87035633, 0.86395081, 0.86778116, 0.8697639 , 0.86930091]), 'test_roc_auc': array([0.57335412, 0.57517778, 0.60208448, 0.59761192, 0.56815946]), 'test_average_precision': array([0.79517346, 0.81807158, 0.82421518, 0.82152667, 0.8197012 ]), 'test_neg_log_loss': array([-0.53699916, -0.53759665, -0.52903703, -0.53076144, -0.5356891 ]), 'test_neg_brier_score': array([-0.17519236, -0.17698685, -0.17352714, -0.17412574, -0.17603567]), 'test_f1_macro': array([0.43517817, 0.46372144, 0.43389058, 0.4518311 , 0.43465046]), 'test_f1_weighted': array([0.67058327, 0.68022135, 0.66859917, 0.6779075 , 0.67067033]), 'test_balanced_accuracy': array([0.5       , 0.5070909 , 0.49738676, 0.50615869, 0.49825784])}</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0.7677228786251342</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.8682406702208683</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.7713125845737483</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>[0.77067669 0.77131258 1.        ]</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0.9930313588850174</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>[1.         0.99303136 0.        ]</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>[[   9  845]
+ [  20 2850]]</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>{'precision': 0.3103448275862069, 'recall': 0.01053864168618267, 'f1-score': 0.020385050962627407, 'support': 854.0}</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7713125845737483, 'recall': 0.9930313588850174, 'f1-score': 0.8682406702208683, 'support': 2870.0}</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5408287060799776, 'recall': 0.5017850002856, 'f1-score': 0.44431286059174785, 'support': 3724.0}</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>{'precision': 0.665601933535252, 'recall': 0.7677228786251342, 'f1-score': 0.6738076146766853, 'support': 3724.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>GradientBoostingClassifier(learning_rate=0.5, max_depth=2, n_estimators=200,
+                           random_state=42)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_1_5</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>[0.73131094 0.73672806 0.7291441  0.74214518 0.73997833]</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.85218644, 0.85407066, 0.85598516, 0.85312867, 0.84758925]), 'score_time': array([0.01060772, 0.00961375, 0.00959992, 0.0106194 , 0.00941372]), 'test_accuracy': array([0.73131094, 0.73672806, 0.7291441 , 0.74214518, 0.73997833]), 'test_precision': array([0.77331759, 0.77083333, 0.76833527, 0.7727797 , 0.77199074]), 'test_recall': array([0.92123769, 0.93670886, 0.92827004, 0.94233474, 0.93943662]), 'test_f1': array([0.84082157, 0.84571429, 0.84076433, 0.84917617, 0.84752224]), 'test_roc_auc': array([0.5244938 , 0.53343019, 0.53384152, 0.54986997, 0.55368644]), 'test_average_precision': array([0.78359839, 0.7870269 , 0.79630666, 0.79811769, 0.8000115 ]), 'test_neg_log_loss': array([-0.62949218, -0.6092483 , -0.60855613, -0.59002557, -0.59880498]), 'test_neg_brier_score': array([-0.20363278, -0.19737548, -0.19874008, -0.19206673, -0.19398085]), 'test_f1_macro': array([0.48985523, 0.47451766, 0.46748361, 0.48055824, 0.48258465]), 'test_f1_weighted': array([0.67959759, 0.67519709, 0.66928977, 0.67984356, 0.6790895 ]), 'test_balanced_accuracy': array([0.50778866, 0.5013733 , 0.4947954 , 0.50654473, 0.507277  ])}</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0.7358613217768147</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.8448122215149586</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.7714485003487561</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>[0.77009751 0.7714485  1.        ]</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0.9335959482273496</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>[1.         0.93359595 0.        ]</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>[[  78  983]
+ [ 236 3318]]</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>{'precision': 0.2484076433121019, 'recall': 0.07351555136663525, 'f1-score': 0.11345454545454546, 'support': 1061.0}</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7714485003487561, 'recall': 0.9335959482273495, 'f1-score': 0.8448122215149586, 'support': 3554.0}</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>{'precision': 0.509928071830429, 'recall': 0.5035557497969924, 'f1-score': 0.47913338348475204, 'support': 4615.0}</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6512001039639479, 'recall': 0.7358613217768147, 'f1-score': 0.6766712693372559, 'support': 4615.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier(algorithm='SAMME',
+                   estimator=DecisionTreeClassifier(max_depth=1,
+                                                    max_leaf_nodes=16,
+                                                    random_state=42),
+                   learning_rate=0.5, n_estimators=500, random_state=42)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_1_5/samme</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>[0.77031419 0.77031419 0.77031419 0.77031419 0.76923077]</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([1.39159775, 1.38913679, 1.38890791, 1.39559531, 1.38485122]), 'score_time': array([0.09358168, 0.09109735, 0.09115028, 0.090415  , 0.09185886]), 'test_accuracy': array([0.77031419, 0.77031419, 0.77031419, 0.77031419, 0.76923077]), 'test_precision': array([0.77031419, 0.77031419, 0.77031419, 0.77031419, 0.76923077]), 'test_recall': array([1., 1., 1., 1., 1.]), 'test_f1': array([0.87025704, 0.87025704, 0.87025704, 0.87025704, 0.86956522]), 'test_roc_auc': array([0.56302908, 0.59321843, 0.6104709 , 0.63868323, 0.60714475]), 'test_average_precision': array([0.80621603, 0.82247527, 0.8342973 , 0.84474779, 0.82979493]), 'test_neg_log_loss': array([-0.56146889, -0.55353719, -0.54488693, -0.54724333, -0.54784295]), 'test_neg_brier_score': array([-0.18670187, -0.18318419, -0.17955614, -0.1803263 , -0.18082747]), 'test_f1_macro': array([0.43512852, 0.43512852, 0.43512852, 0.43512852, 0.43478261]), 'test_f1_weighted': array([0.67037135, 0.67037135, 0.67037135, 0.67037135, 0.66889632]), 'test_balanced_accuracy': array([0.5, 0.5, 0.5, 0.5, 0.5])}</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0.7700975081256771</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.8701187415840372</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.7700975081256771</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>[0.77009751 1.        ]</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>[1. 0.]</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>[[   0 1061]
+ [   0 3554]]</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>{'precision': 0.0, 'recall': 0.0, 'f1-score': 0.0, 'support': 1061.0}</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7700975081256771, 'recall': 1.0, 'f1-score': 0.8701187415840372, 'support': 3554.0}</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>{'precision': 0.38504875406283856, 'recall': 0.5, 'f1-score': 0.4350593707920186, 'support': 4615.0}</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5930501720213773, 'recall': 0.7700975081256771, 'f1-score': 0.6700762746673171, 'support': 4615.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier(estimator=DecisionTreeClassifier(max_depth=1,
+                                                    max_leaf_nodes=16,
+                                                    random_state=42),
+                   learning_rate=0.5, n_estimators=500, random_state=42)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_1_5/samme_r</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>[0.76381365 0.76489707 0.76923077 0.77031419 0.76489707]</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([1.52437592, 1.56716251, 1.52018595, 1.52854538, 1.52533674]), 'score_time': array([0.11970615, 0.1207211 , 0.12201142, 0.12139201, 0.12104416]), 'test_accuracy': array([0.76381365, 0.76489707, 0.76923077, 0.77031419, 0.76489707]), 'test_precision': array([0.77117712, 0.77202643, 0.77065217, 0.77208288, 0.76881134]), 'test_recall': array([0.9859353 , 0.9859353 , 0.99718706, 0.99578059, 0.99295775]), 'test_f1': array([0.8654321 , 0.86596665, 0.86940527, 0.86977887, 0.86662569]), 'test_roc_auc': array([0.54413131, 0.55059311, 0.58169466, 0.58138949, 0.56831978]), 'test_average_precision': array([0.79063265, 0.81085994, 0.82458174, 0.81567887, 0.81421222]), 'test_neg_log_loss': array([-0.69146859, -0.69146629, -0.69148011, -0.6915195 , -0.69132883]), 'test_neg_brier_score': array([-0.24916073, -0.24915959, -0.24916649, -0.24918617, -0.24909087]), 'test_f1_macro': array([0.45041516, 0.45500975, 0.4393538 , 0.4486509 , 0.43787906]), 'test_f1_weighted': array([0.6747851 , 0.67718472, 0.67185183, 0.67632464, 0.66874263]), 'test_balanced_accuracy': array([0.50240161, 0.5047601 , 0.50095202, 0.50496577, 0.49882629])}</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0.7666305525460455</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.8674461538461539</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.7709472763071538</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>[0.77009751 0.77094728 1.        ]</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0.9915588069780528</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>[1.         0.99155881 0.        ]</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>[[  14 1047]
+ [  30 3524]]</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>{'precision': 0.3181818181818182, 'recall': 0.013195098963242224, 'f1-score': 0.025339366515837104, 'support': 1061.0}</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7709472763071538, 'recall': 0.9915588069780529, 'f1-score': 0.8674461538461539, 'support': 3554.0}</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>{'precision': 0.544564547244486, 'recall': 0.5023769529706476, 'f1-score': 0.4463927601809955, 'support': 4615.0}</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6668553692495197, 'recall': 0.7666305525460455, 'f1-score': 0.6738437050146336, 'support': 4615.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier(max_leaf_nodes=16, n_estimators=500, n_jobs=-1,
+                       oob_score=True, random_state=42)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_1_5/oob=True</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>[0.77031419 0.77031419 0.77031419 0.77031419 0.76923077]</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.60768008, 0.61990094, 0.6086967 , 0.61082578, 0.60957408]), 'score_time': array([0.1160264 , 0.12362361, 0.12475967, 0.11326671, 0.11439657]), 'test_accuracy': array([0.77031419, 0.77031419, 0.77031419, 0.77031419, 0.76923077]), 'test_precision': array([0.77031419, 0.77031419, 0.77031419, 0.77031419, 0.76923077]), 'test_recall': array([1., 1., 1., 1., 1.]), 'test_f1': array([0.87025704, 0.87025704, 0.87025704, 0.87025704, 0.86956522]), 'test_roc_auc': array([0.56244858, 0.57525277, 0.60071518, 0.62422711, 0.58456655]), 'test_average_precision': array([0.8033968 , 0.81302988, 0.83046603, 0.83786019, 0.81158812]), 'test_neg_log_loss': array([-0.53421335, -0.53135576, -0.52950386, -0.52497663, -0.53178081]), 'test_neg_brier_score': array([-0.17516242, -0.1740587 , -0.17364503, -0.17182537, -0.17437633]), 'test_f1_macro': array([0.43512852, 0.43512852, 0.43512852, 0.43512852, 0.43478261]), 'test_f1_weighted': array([0.67037135, 0.67037135, 0.67037135, 0.67037135, 0.66889632]), 'test_balanced_accuracy': array([0.5, 0.5, 0.5, 0.5, 0.5])}</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0.7700975081256771</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.8701187415840372</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.7700975081256771</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>[0.77009751 1.        ]</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>[1. 0.]</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>[[   0 1061]
+ [   0 3554]]</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>{'precision': 0.0, 'recall': 0.0, 'f1-score': 0.0, 'support': 1061.0}</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7700975081256771, 'recall': 1.0, 'f1-score': 0.8701187415840372, 'support': 3554.0}</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>{'precision': 0.38504875406283856, 'recall': 0.5, 'f1-score': 0.4350593707920186, 'support': 4615.0}</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5930501720213773, 'recall': 0.7700975081256771, 'f1-score': 0.6700762746673171, 'support': 4615.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier(max_leaf_nodes=16, n_estimators=500, n_jobs=-1,
+                       random_state=42)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_1_5/oob=False</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>[0.76860622 0.76860622 0.7696477  0.76829268 0.76829268]</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.47468472, 0.48753953, 0.47490335, 0.48108101, 0.48230267]), 'score_time': array([0.10210896, 0.10328841, 0.10330868, 0.10279727, 0.10398507]), 'test_accuracy': array([0.76860622, 0.76860622, 0.7696477 , 0.76829268, 0.76829268]), 'test_precision': array([0.76860622, 0.76860622, 0.7696477 , 0.76829268, 0.76829268]), 'test_recall': array([1., 1., 1., 1., 1.]), 'test_f1': array([0.86916603, 0.86916603, 0.86983155, 0.86896552, 0.86896552]), 'test_roc_auc': array([0.59246561, 0.57154477, 0.56922121, 0.58980785, 0.61224048]), 'test_average_precision': array([0.8178074 , 0.80333851, 0.80892321, 0.81468614, 0.83867715]), 'test_neg_log_loss': array([-0.53155214, -0.53480564, -0.53476397, -0.53294515, -0.53031083]), 'test_neg_brier_score': array([-0.1744457 , -0.17552188, -0.17551977, -0.17500362, -0.17420039]), 'test_f1_macro': array([0.43458301, 0.43458301, 0.43491577, 0.43448276, 0.43448276]), 'test_f1_weighted': array([0.66804642, 0.66804642, 0.66946385, 0.66761985, 0.66761985]), 'test_balanced_accuracy': array([0.5, 0.5, 0.5, 0.5, 0.5])}</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0.7686890574214518</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.869218989280245</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.7686890574214518</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>[0.76868906 1.        ]</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>[1. 0.]</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>[[   0  854]
+ [   0 2838]]</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>{'precision': 0.0, 'recall': 0.0, 'f1-score': 0.0, 'support': 854.0}</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7686890574214518, 'recall': 1.0, 'f1-score': 0.869218989280245, 'support': 2838.0}</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>{'precision': 0.3843445287107259, 'recall': 0.5, 'f1-score': 0.4346094946401225, 'support': 3692.0}</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>{'precision': 0.59088286699948, 'recall': 0.7686890574214518, 'f1-score': 0.6681591255626586, 'support': 3692.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BaggingClassifier(estimator=DecisionTreeClassifier(max_leaf_nodes=16,
+                                                   random_state=42),
+                  max_samples=100, n_estimators=500, n_jobs=-1, random_state=42,
+                  verbose=1)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_1_5/bagging=True</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>[0.7699594 0.7699594 0.7696477 0.7696477 0.7696477]</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.10020065, 0.10164857, 0.09228253, 0.09078526, 0.09885645]), 'score_time': array([0.12435865, 0.12684298, 0.12462687, 0.12239909, 0.1219008 ]), 'test_accuracy': array([0.7699594, 0.7699594, 0.7696477, 0.7696477, 0.7696477]), 'test_precision': array([0.7699594 , 0.7699594 , 0.7696477 , 0.7696477 , 0.77069199]), 'test_recall': array([1.        , 1.        , 1.        , 1.        , 0.99824253]), 'test_f1': array([0.87003058, 0.87003058, 0.86983155, 0.86983155, 0.86983155]), 'test_roc_auc': array([0.58492712, 0.583945  , 0.6086889 , 0.52437862, 0.56757937]), 'test_average_precision': array([0.80869022, 0.80562367, 0.84627562, 0.78338435, 0.80605106]), 'test_neg_log_loss': array([-0.53560049, -0.53578228, -0.52741329, -0.5516481 , -0.53728213]), 'test_neg_brier_score': array([-0.17553146, -0.17549226, -0.17365549, -0.18183769, -0.17623331]), 'test_f1_macro': array([0.43501529, 0.43501529, 0.43491577, 0.43491577, 0.43491577]), 'test_f1_weighted': array([0.66988823, 0.66988823, 0.66946385, 0.66946385, 0.67064248]), 'test_balanced_accuracy': array([0.5       , 0.5       , 0.5       , 0.5       , 0.49912127])}</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0.7697724810400867</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.8699112335475971</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.7699810349498781</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>[0.77004334 0.76998103 1.        ]</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0.9996482588814632</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>[1.         0.99964826 0.        ]</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>[[   0  849]
+ [   1 2842]]</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>{'precision': 0.0, 'recall': 0.0, 'f1-score': 0.0, 'support': 849.0}</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7699810349498781, 'recall': 0.9996482588814632, 'f1-score': 0.8699112335475971, 'support': 2843.0}</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>{'precision': 0.38499051747493906, 'recall': 0.4998241294407316, 'f1-score': 0.43495561677379857, 'support': 3692.0}</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5929187655369729, 'recall': 0.7697724810400867, 'f1-score': 0.6698693491267115, 'support': 3692.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BaggingClassifier(bootstrap=False,
+                  estimator=DecisionTreeClassifier(max_leaf_nodes=16,
+                                                   random_state=42),
+                  max_samples=100, n_estimators=500, n_jobs=-1, random_state=42,
+                  verbose=1)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_1_5/bagging=False</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>[0.7699594 0.7699594 0.7696477 0.7696477 0.7696477]</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.11071777, 0.10183215, 0.1021862 , 0.09803939, 0.09946036]), 'score_time': array([0.12457871, 0.12370491, 0.12563086, 0.13026357, 0.12292671]), 'test_accuracy': array([0.7699594, 0.7699594, 0.7696477, 0.7696477, 0.7696477]), 'test_precision': array([0.7699594 , 0.7699594 , 0.7696477 , 0.7696477 , 0.77069199]), 'test_recall': array([1.        , 1.        , 1.        , 1.        , 0.99824253]), 'test_f1': array([0.87003058, 0.87003058, 0.86983155, 0.86983155, 0.86983155]), 'test_roc_auc': array([0.58720149, 0.58651918, 0.59349627, 0.54387945, 0.56981521]), 'test_average_precision': array([0.81386952, 0.80984071, 0.83940281, 0.79949285, 0.81319754]), 'test_neg_log_loss': array([-0.5345153 , -0.5359884 , -0.53119428, -0.54650954, -0.53581209]), 'test_neg_brier_score': array([-0.17523573, -0.1754585 , -0.17502829, -0.18040288, -0.17573862]), 'test_f1_macro': array([0.43501529, 0.43501529, 0.43491577, 0.43491577, 0.43491577]), 'test_f1_weighted': array([0.66988823, 0.66988823, 0.66946385, 0.66946385, 0.67064248]), 'test_balanced_accuracy': array([0.5       , 0.5       , 0.5       , 0.5       , 0.49912127])}</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0.7697724810400867</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.8699112335475971</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.7699810349498781</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>[0.77004334 0.76998103 1.        ]</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0.9996482588814632</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>[1.         0.99964826 0.        ]</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>[[   0  849]
+ [   1 2842]]</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>{'precision': 0.0, 'recall': 0.0, 'f1-score': 0.0, 'support': 849.0}</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7699810349498781, 'recall': 0.9996482588814632, 'f1-score': 0.8699112335475971, 'support': 2843.0}</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>{'precision': 0.38499051747493906, 'recall': 0.4998241294407316, 'f1-score': 0.43495561677379857, 'support': 3692.0}</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5929187655369729, 'recall': 0.7697724810400867, 'f1-score': 0.6698693491267115, 'support': 3692.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>GradientBoostingClassifier(learning_rate=0.5, max_depth=2, n_estimators=200,
+                           random_state=42)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_2_5</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>[0.55710306 0.54967502 0.56592386 0.53760446 0.54967502]</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([1.83235979, 1.83069706, 1.82029724, 1.78633523, 1.82757449]), 'score_time': array([0.01567817, 0.01561284, 0.01495051, 0.01494527, 0.01564646]), 'test_accuracy': array([0.55710306, 0.54967502, 0.56592386, 0.53760446, 0.54967502]), 'test_precision': array([0.56772575, 0.56271478, 0.57987643, 0.55199307, 0.56003289]), 'test_recall': array([0.60842294, 0.58691756, 0.58870968, 0.57078853, 0.61021505]), 'test_f1': array([0.58737024, 0.5745614 , 0.58425967, 0.56123348, 0.58404803]), 'test_roc_auc': array([0.57796217, 0.56773261, 0.57878312, 0.5553078 , 0.56237181]), 'test_average_precision': array([0.5938953 , 0.58246138, 0.58024819, 0.57154453, 0.57876217]), 'test_neg_log_loss': array([-0.6956309 , -0.70623597, -0.70129211, -0.71509091, -0.71352213]), 'test_neg_brier_score': array([-0.24982095, -0.25352069, -0.25148614, -0.25754835, -0.25692882]), 'test_f1_macro': array([0.55470717, 0.54812883, 0.56507787, 0.53625953, 0.54657867]), 'test_f1_weighted': array([0.55588995, 0.549086  , 0.56577247, 0.53716388, 0.5479355 ]), 'test_balanced_accuracy': array([0.55517486, 0.54827574, 0.56506775, 0.53635766, 0.5474004 ])}</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0.5519962859795728</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.5783448396399545</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.5643868326795156</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>[0.51810585 0.56438683 1.        ]</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0.593010752688172</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>[1.         0.59301075 0.        ]</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>[[2636 2554]
+ [2271 3309]]</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5371917668636641, 'recall': 0.5078998073217726, 'f1-score': 0.5221352877092206, 'support': 5190.0}</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5643868326795156, 'recall': 0.593010752688172, 'f1-score': 0.5783448396399545, 'support': 5580.0}</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5507892997715899, 'recall': 0.5504552800049723, 'f1-score': 0.5502400636745876, 'support': 10770.0}</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5512816895426289, 'recall': 0.5519962859795728, 'f1-score': 0.5512577853669267, 'support': 10770.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier(algorithm='SAMME',
+                   estimator=DecisionTreeClassifier(max_depth=1,
+                                                    max_leaf_nodes=16,
+                                                    random_state=42),
+                   learning_rate=0.5, n_estimators=500, random_state=42)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_2_5/samme</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>[0.57103064 0.56638812 0.58310121 0.56081708 0.5645311 ]</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([2.71621656, 2.69683433, 2.78865004, 2.71480942, 2.69255829]), 'score_time': array([0.14635324, 0.14548969, 0.14621902, 0.14584279, 0.14564419]), 'test_accuracy': array([0.57103064, 0.56638812, 0.58310121, 0.56081708, 0.5645311 ]), 'test_precision': array([0.57973422, 0.56914894, 0.58650794, 0.56888169, 0.57283142]), 'test_recall': array([0.62544803, 0.67114695, 0.66218638, 0.62903226, 0.62724014]), 'test_f1': array([0.60172414, 0.61595395, 0.62205387, 0.59744681, 0.5988024 ]), 'test_roc_auc': array([0.59281229, 0.59563815, 0.60230118, 0.5780964 , 0.5945634 ]), 'test_average_precision': array([0.59611806, 0.60830544, 0.60081417, 0.59436488, 0.61326559]), 'test_neg_log_loss': array([-0.67957859, -0.6782996 , -0.67769955, -0.6831594 , -0.6788135 ]), 'test_neg_brier_score': array([-0.24318846, -0.24272464, -0.24227629, -0.24509701, -0.24297443]), 'test_f1_macro': array([0.5684677 , 0.55904307, 0.57862528, 0.55715037, 0.56133013]), 'test_f1_weighted': array([0.56967197, 0.56110391, 0.5801979 , 0.55860957, 0.56268707]), 'test_balanced_accuracy': array([0.56898606, 0.56245209, 0.5801298 , 0.55825409, 0.56217498])}</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>0.5691736304549675</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.6073121191604604</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.5753688261706222</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>[0.51810585 0.57536883 1.        ]</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0.6430107526881721</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>[1.         0.64301075 0.        ]</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>[[2542 2648]
+ [1992 3588]]</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5606528451698279, 'recall': 0.48978805394990366, 'f1-score': 0.5228301110654052, 'support': 5190.0}</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5753688261706222, 'recall': 0.6430107526881721, 'f1-score': 0.6073121191604604, 'support': 5580.0}</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5680108356702251, 'recall': 0.5663994033190378, 'f1-score': 0.5650711151129328, 'support': 10770.0}</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5682772810086796, 'recall': 0.5691736304549675, 'f1-score': 0.5666007336439018, 'support': 10770.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier(estimator=DecisionTreeClassifier(max_depth=1,
+                                                    max_leaf_nodes=16,
+                                                    random_state=42),
+                   learning_rate=0.5, n_estimators=500, random_state=42)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_2_5/samme_r</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>[0.5645311  0.56128134 0.57660167 0.5450325  0.54410399]</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([2.9876523 , 2.98628759, 2.97730827, 2.97645092, 3.02189445]), 'score_time': array([0.19624805, 0.19457436, 0.19553399, 0.19601083, 0.19664407]), 'test_accuracy': array([0.5645311 , 0.56128134, 0.57660167, 0.5450325 , 0.54410399]), 'test_precision': array([0.57555178, 0.57119067, 0.58869565, 0.55647841, 0.55482815]), 'test_recall': array([0.60752688, 0.61469534, 0.60663082, 0.60035842, 0.60752688]), 'test_f1': array([0.59110724, 0.59214502, 0.59752868, 0.57758621, 0.57998289]), 'test_roc_auc': array([0.59038309, 0.58634954, 0.59528551, 0.57324837, 0.58219254]), 'test_average_precision': array([0.59679441, 0.60518698, 0.5952611 , 0.59030038, 0.60399404]), 'test_neg_log_loss': array([-0.69297988, -0.69301863, -0.69300703, -0.69304966, -0.69299341]), 'test_neg_brier_score': array([-0.24991635, -0.24993571, -0.24992992, -0.24995123, -0.24992311]), 'test_f1_macro': array([0.56268371, 0.55875458, 0.57545386, 0.54231423, 0.54075287]), 'test_f1_weighted': array([0.56371297, 0.5599637 , 0.57625323, 0.54359149, 0.54217345]), 'test_balanced_accuracy': array([0.56291566, 0.55927445, 0.57547341, 0.54295378, 0.54172105])}</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>0.5583101207056639</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.5876029475509319</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.5691015952980688</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>[0.51810585 0.5691016  1.        ]</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0.6073476702508961</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>[1.         0.60734767 0.        ]</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>[[2624 2566]
+ [2191 3389]]</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5449636552440291, 'recall': 0.505587668593449, 'f1-score': 0.5245377311344328, 'support': 5190.0}</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5691015952980688, 'recall': 0.6073476702508961, 'f1-score': 0.5876029475509319, 'support': 5580.0}</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5570326252710489, 'recall': 0.5564676694221725, 'f1-score': 0.5560703393426824, 'support': 10770.0}</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5574696631828908, 'recall': 0.5583101207056639, 'f1-score': 0.5572121886649867, 'support': 10770.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier(max_leaf_nodes=16, n_estimators=500, n_jobs=-1,
+                       oob_score=True, random_state=42)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_2_5/oob=True</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>[0.57149489 0.56128134 0.58913649 0.55710306 0.55710306]</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.93540573, 0.93068862, 0.94098949, 0.94370532, 0.92601514]), 'score_time': array([0.12598038, 0.13606453, 0.12616348, 0.13626099, 0.12590337]), 'test_accuracy': array([0.57149489, 0.56128134, 0.58913649, 0.55710306, 0.55710306]), 'test_precision': array([0.57813765, 0.56511805, 0.59490551, 0.56318253, 0.5624037 ]), 'test_recall': array([0.63978495, 0.66487455, 0.64874552, 0.64695341, 0.65412186]), 'test_f1': array([0.60740111, 0.61095101, 0.62066009, 0.60216847, 0.6048053 ]), 'test_roc_auc': array([0.59373381, 0.60027987, 0.60806296, 0.57950739, 0.58983881]), 'test_average_precision': array([0.5962708 , 0.61241996, 0.60302341, 0.5928738 , 0.604416  ]), 'test_neg_log_loss': array([-0.6794319 , -0.67775626, -0.67717824, -0.68241952, -0.68032557]), 'test_neg_brier_score': array([-0.24320022, -0.24240346, -0.24207004, -0.2447035 , -0.24367707]), 'test_f1_macro': array([0.56788042, 0.55401196, 0.58627941, 0.55134602, 0.55055471]), 'test_f1_weighted': array([0.56931153, 0.55607382, 0.5875244 , 0.55318638, 0.55251922]), 'test_balanced_accuracy': array([0.56892908, 0.55738911, 0.58689684, 0.55372718, 0.55345785])}</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>0.5672237697307335</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.6091404612159329</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.5724192277383767</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>[0.51810585 0.57241923 1.        ]</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0.6508960573476702</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>[1.         0.65089606 0.        ]</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>[[2477 2713]
+ [1948 3632]]</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>{'precision': 0.559774011299435, 'recall': 0.4772639691714836, 'f1-score': 0.5152366094643785, 'support': 5190.0}</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5724192277383767, 'recall': 0.6508960573476702, 'f1-score': 0.6091404612159329, 'support': 5580.0}</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5660966195189059, 'recall': 0.5640800132595769, 'f1-score': 0.5621885353401557, 'support': 10770.0}</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5663255719056833, 'recall': 0.5672237697307335, 'f1-score': 0.563888744355156, 'support': 10770.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier(max_leaf_nodes=16, n_estimators=500, n_jobs=-1,
+                       random_state=42)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_2_5/oob=False</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>[0.57366589 0.57573999 0.56761463 0.57109692 0.55194428]</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.65756321, 0.68882442, 0.66058159, 0.66310239, 0.67056704]), 'score_time': array([0.1367557 , 0.12497902, 0.13669157, 0.1260581 , 0.14760089]), 'test_accuracy': array([0.57366589, 0.57573999, 0.56761463, 0.57109692, 0.55194428]), 'test_precision': array([0.57685009, 0.59140969, 0.57392996, 0.5801217 , 0.56345178]), 'test_recall': array([0.67781494, 0.59866221, 0.65774805, 0.63768116, 0.6187291 ]), 'test_f1': array([0.62327012, 0.59501385, 0.61298701, 0.60754116, 0.58979809]), 'test_roc_auc': array([0.5951991 , 0.59589134, 0.59512607, 0.59979728, 0.57458005]), 'test_average_precision': array([0.59994823, 0.60572762, 0.60504486, 0.6140241 , 0.58912651]), 'test_neg_log_loss': array([-0.67947247, -0.67936862, -0.6787951 , -0.67752983, -0.68399625]), 'test_neg_brier_score': array([-0.24320707, -0.24317738, -0.24290889, -0.24229108, -0.24546445]), 'test_f1_macro': array([0.56614408, 0.57477688, 0.56158884, 0.56736623, 0.54809597]), 'test_f1_weighted': array([0.56846358, 0.57561079, 0.56370681, 0.56902172, 0.5498144 ]), 'test_balanced_accuracy': array([0.56925813, 0.57475483, 0.56374085, 0.56823525, 0.54907399])}</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>0.5680129990714949</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.6059707812830828</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.5768998185849628</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>[0.52054318 0.57689982 1.        ]</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>0.6381270903010033</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>[1.         0.63812709 0.        ]</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>[[2032 2099]
+ [1623 2862]]</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5559507523939808, 'recall': 0.4918905833938514, 'f1-score': 0.5219624967891087, 'support': 4131.0}</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5768998185849628, 'recall': 0.6381270903010033, 'f1-score': 0.6059707812830828, 'support': 4485.0}</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5664252854894718, 'recall': 0.5650088368474273, 'f1-score': 0.5639666390360958, 'support': 8616.0}</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5668556458325317, 'recall': 0.5680129990714949, 'f1-score': 0.5656924359668564, 'support': 8616.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BaggingClassifier(estimator=DecisionTreeClassifier(max_leaf_nodes=16,
+                                                   random_state=42),
+                  max_samples=100, n_estimators=500, n_jobs=-1, random_state=42,
+                  verbose=1)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_2_5/bagging=True</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>[0.5812065  0.5443993  0.55194428 0.56355194 0.5618108 ]</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.12490916, 0.13638043, 0.12030458, 0.12089777, 0.12276411]), 'score_time': array([0.16593885, 0.1685822 , 0.18549848, 0.17134881, 0.1758976 ]), 'test_accuracy': array([0.5812065 , 0.5443993 , 0.55194428, 0.56355194, 0.5618108 ]), 'test_precision': array([0.58043274, 0.55613851, 0.56007944, 0.56987116, 0.56725146]), 'test_recall': array([0.69092945, 0.5941704 , 0.63157895, 0.64389698, 0.65173572]), 'test_f1': array([0.63087935, 0.57452575, 0.59368421, 0.60462671, 0.60656592]), 'test_roc_auc': array([0.6177813 , 0.57614415, 0.58828775, 0.58901226, 0.58676453]), 'test_average_precision': array([0.63290624, 0.58249405, 0.59596721, 0.5995802 , 0.60068326]), 'test_neg_log_loss': array([-0.67202637, -0.68411965, -0.68076775, -0.67957111, -0.68141497]), 'test_neg_brier_score': array([-0.23962234, -0.24550113, -0.2438759 , -0.24331207, -0.24418733]), 'test_f1_macro': array([0.57348257, 0.5421036 , 0.54716552, 0.55879004, 0.55606619]), 'test_f1_weighted': array([0.57554672, 0.54325145, 0.54886644, 0.56046602, 0.55791267]), 'test_balanced_accuracy': array([0.57711334, 0.54257257, 0.548922  , 0.56050271, 0.55839798])}</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>0.5605849582172702</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.6023944549464398</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.5670225385527876</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>[0.51810585 0.56702254 1.        ]</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>0.6424731182795699</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>[1.         0.64247312 0.        ]</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>[[1962 2190]
+ [1596 2868]]</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>{'precision': 0.551433389544688, 'recall': 0.4725433526011561, 'f1-score': 0.5089494163424124, 'support': 4152.0}</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5670225385527876, 'recall': 0.6424731182795699, 'f1-score': 0.6023944549464398, 'support': 4464.0}</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5592279640487379, 'recall': 0.557508235440363, 'f1-score': 0.5556719356444262, 'support': 8616.0}</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5595102188357925, 'recall': 0.5605849582172702, 'f1-score': 0.557363837457591, 'support': 8616.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BaggingClassifier(bootstrap=False,
+                  estimator=DecisionTreeClassifier(max_leaf_nodes=16,
+                                                   random_state=42),
+                  max_samples=100, n_estimators=500, n_jobs=-1, random_state=42,
+                  verbose=1)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_2_5/bagging=False</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>[0.57018561 0.55252467 0.5478816  0.5548462  0.56471271]</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.13009453, 0.13267326, 0.1209619 , 0.131428  , 0.13087058]), 'score_time': array([0.16560912, 0.16574717, 0.16209269, 0.16808915, 0.166713  ]), 'test_accuracy': array([0.57018561, 0.55252467, 0.5478816 , 0.5548462 , 0.56471271]), 'test_precision': array([0.57407407, 0.56568947, 0.55688623, 0.56468172, 0.56790123]), 'test_recall': array([0.65957447, 0.58408072, 0.62486002, 0.61590146, 0.66965286]), 'test_f1': array([0.61386139, 0.574738  , 0.58891821, 0.5891805 , 0.61459404]), 'test_roc_auc': array([0.61166204, 0.57588782, 0.58217596, 0.59048422, 0.5894521 ]), 'test_average_precision': array([0.62375022, 0.58078968, 0.59071759, 0.60496064, 0.60168616]), 'test_neg_log_loss': array([-0.67369006, -0.68495913, -0.6818735 , -0.67925193, -0.68148541]), 'test_neg_brier_score': array([-0.24043328, -0.24589689, -0.24442729, -0.24317375, -0.24420054]), 'test_f1_macro': array([0.56461545, 0.55130042, 0.5433308 , 0.55171501, 0.55729702]), 'test_f1_weighted': array([0.56638648, 0.55213019, 0.54499766, 0.55308491, 0.55939204]), 'test_balanced_accuracy': array([0.56685101, 0.55136647, 0.54496013, 0.55252904, 0.56073004])}</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>0.5580315691736305</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.5966101694915255</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.5659163987138264</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>[0.51810585 0.5659164  1.        ]</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0.6308243727598566</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>[1.         0.63082437 0.        ]</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>[[1992 2160]
+ [1648 2816]]</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5472527472527473, 'recall': 0.4797687861271676, 'f1-score': 0.5112936344969199, 'support': 4152.0}</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5659163987138264, 'recall': 0.6308243727598566, 'f1-score': 0.5966101694915255, 'support': 4464.0}</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5565845729832868, 'recall': 0.5552965794435121, 'f1-score': 0.5539519019942227, 'support': 8616.0}</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5569224942492952, 'recall': 0.5580315691736305, 'f1-score': 0.5554966303437072, 'support': 8616.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>GradientBoostingClassifier(learning_rate=0.5, max_depth=2, n_estimators=200,
+                           random_state=42)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_2_5</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>[0.54706163 0.54206501 0.54732314 0.53059273 0.52724665]</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([1.95742416, 1.95923257, 1.93066335, 1.94645715, 1.99852538]), 'score_time': array([0.01600194, 0.01521182, 0.01469064, 0.01508331, 0.01500297]), 'test_accuracy': array([0.54706163, 0.54206501, 0.54732314, 0.53059273, 0.52724665]), 'test_precision': array([0.56244303, 0.55536028, 0.55951347, 0.54450262, 0.543379  ]), 'test_recall': array([0.56866359, 0.58302583, 0.59409594, 0.57564576, 0.54889299]), 'test_f1': array([0.56553621, 0.56885689, 0.57628635, 0.55964126, 0.54612207]), 'test_roc_auc': array([0.56822745, 0.53441655, 0.56763237, 0.54299781, 0.54775907]), 'test_average_precision': array([0.59281853, 0.54993161, 0.57531601, 0.56696401, 0.54970913]), 'test_neg_log_loss': array([-0.69879294, -0.72401328, -0.70714396, -0.71752419, -0.7205447 ]), 'test_neg_brier_score': array([-0.25129499, -0.26200449, -0.25397938, -0.25943291, -0.25931735]), 'test_f1_macro': array([0.54624116, 0.54028981, 0.54519808, 0.5285412 , 0.52642762]), 'test_f1_weighted': array([0.54695101, 0.54132762, 0.54632748, 0.52967103, 0.5271431 ]), 'test_balanced_accuracy': array([0.54623656, 0.54052085, 0.54555988, 0.52889431, 0.52643062])}</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>0.5388586177229711</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.5633598841419262</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.553047805224809</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>[0.5182105  0.55304781 1.        ]</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0.574063825862387</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>[1.         0.57406383 0.        ]</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>[[2525 2515]
+ [2309 3112]]</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5223417459660736, 'recall': 0.5009920634920635, 'f1-score': 0.5114441968806968, 'support': 5040.0}</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>{'precision': 0.553047805224809, 'recall': 0.574063825862387, 'f1-score': 0.5633598841419262, 'support': 5421.0}</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5376947755954413, 'recall': 0.5375279446772252, 'f1-score': 0.5374020405113115, 'support': 10461.0}</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5382539481686933, 'recall': 0.5388586177229711, 'f1-score': 0.5383474509331893, 'support': 10461.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier(algorithm='SAMME',
+                   estimator=DecisionTreeClassifier(max_depth=1,
+                                                    max_leaf_nodes=16,
+                                                    random_state=42),
+                   learning_rate=0.5, n_estimators=500, random_state=42)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_2_5/samme</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>[0.55852843 0.54493308 0.55783939 0.55879541 0.53919694]</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([2.8779428 , 2.88219976, 2.87829399, 2.88380313, 2.90999198]), 'score_time': array([0.14531136, 0.14477158, 0.14376187, 0.14491248, 0.14367604]), 'test_accuracy': array([0.55852843, 0.54493308, 0.55783939, 0.55879541, 0.53919694]), 'test_precision': array([0.57884427, 0.57568807, 0.57926221, 0.57994042, 0.56329114]), 'test_recall': array([0.54470046, 0.46309963, 0.53597786, 0.53874539, 0.49261993]), 'test_f1': array([0.56125356, 0.51329243, 0.55678007, 0.55858441, 0.52559055]), 'test_roc_auc': array([0.58147904, 0.5626176 , 0.57960394, 0.57581552, 0.56470881]), 'test_average_precision': array([0.60654867, 0.58597252, 0.59237025, 0.5972683 , 0.58218567]), 'test_neg_log_loss': array([-0.68117411, -0.68438416, -0.68192962, -0.68279497, -0.68499114]), 'test_neg_brier_score': array([-0.24411188, -0.24569176, -0.24437203, -0.24490972, -0.24596001]), 'test_f1_macro': array([0.5585114 , 0.54300169, 0.55783686, 0.55879531, 0.53881758]), 'test_f1_weighted': array([0.55861228, 0.54192239, 0.55779847, 0.55878765, 0.53833706]), 'test_balanced_accuracy': array([0.55905658, 0.54801807, 0.55866353, 0.55955127, 0.54095282])}</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>0.5518592868750597</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.543613707165109</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.5755514326942899</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>[0.5182105  0.57555143 1.        ]</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>0.5150341265449179</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>[1.         0.51503413 0.        ]</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>[[2981 2059]
+ [2629 2792]]</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5313725490196078, 'recall': 0.591468253968254, 'f1-score': 0.55981220657277, 'support': 5040.0}</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5755514326942899, 'recall': 0.5150341265449179, 'f1-score': 0.543613707165109, 'support': 5421.0}</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5534619908569489, 'recall': 0.553251190256586, 'f1-score': 0.5517129568689395, 'support': 10461.0}</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5542665102470671, 'recall': 0.5518592868750597, 'f1-score': 0.5514179741581892, 'support': 10461.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier(estimator=DecisionTreeClassifier(max_depth=1,
+                                                    max_leaf_nodes=16,
+                                                    random_state=42),
+                   learning_rate=0.5, n_estimators=500, random_state=42)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_2_5/samme_r</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>[0.54706163 0.54493308 0.55592734 0.55688337 0.55258126]</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([3.10127878, 3.1086843 , 3.11190414, 3.34331679, 3.09427166]), 'score_time': array([0.1911521 , 0.19899869, 0.19271684, 0.19082093, 0.19315958]), 'test_accuracy': array([0.54706163, 0.54493308, 0.55592734, 0.55688337, 0.55258126]), 'test_precision': array([0.56278643, 0.55913978, 0.56744996, 0.56990205, 0.56468531]), 'test_recall': array([0.56589862, 0.57564576, 0.60147601, 0.5904059 , 0.59594096]), 'test_f1': array([0.56433824, 0.56727273, 0.58396776, 0.57997281, 0.57989228]), 'test_roc_auc': array([0.57193238, 0.55910099, 0.58239435, 0.56965768, 0.57245541]), 'test_average_precision': array([0.59756113, 0.57714894, 0.59716317, 0.59638202, 0.58232868]), 'test_neg_log_loss': array([-0.69302633, -0.69304246, -0.69299707, -0.69303043, -0.69301779]), 'test_neg_brier_score': array([-0.24993958, -0.24994764, -0.24992494, -0.24994163, -0.24993531]), 'test_f1_macro': array([0.54634822, 0.54371701, 0.55390084, 0.55554028, 0.55068234]), 'test_f1_weighted': array([0.54701006, 0.54457276, 0.55499314, 0.55642788, 0.5517435 ]), 'test_balanced_accuracy': array([0.54634217, 0.54377526, 0.55421023, 0.55561962, 0.55094667])}</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>0.5514769142529395</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.5751539297356031</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.5648230481949138</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>[0.5182105  0.56482305 1.        ]</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0.5858697657258808</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>[1.         0.58586977 0.        ]</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>[[2593 2447]
+ [2245 3176]]</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5359652749069863, 'recall': 0.5144841269841269, 'f1-score': 0.5250050617533913, 'support': 5040.0}</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5648230481949138, 'recall': 0.5858697657258808, 'f1-score': 0.5751539297356031, 'support': 5421.0}</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>{'precision': 0.55039416155095, 'recall': 0.5501769463550039, 'f1-score': 0.5500794957444972, 'support': 10461.0}</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5509196759196863, 'recall': 0.5514769142529394, 'f1-score': 0.5509927315107348, 'support': 10461.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier(max_leaf_nodes=16, n_estimators=500, n_jobs=-1,
+                       oob_score=True, random_state=42)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_2_5/oob=True</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>[0.54419494 0.53537285 0.56118547 0.5501912  0.54015296]</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.94254303, 0.93795419, 0.93015528, 0.93709326, 0.93296003]), 'score_time': array([0.13713741, 0.12521267, 0.12512755, 0.12534285, 0.13071322]), 'test_accuracy': array([0.54419494, 0.53537285, 0.56118547, 0.5501912 , 0.54015296]), 'test_precision': array([0.56504469, 0.55214153, 0.57242583, 0.56482321, 0.55700935]), 'test_recall': array([0.52442396, 0.54704797, 0.60516605, 0.57472325, 0.5498155 ]), 'test_f1': array([0.54397706, 0.54958295, 0.58834081, 0.56973022, 0.55338904]), 'test_roc_auc': array([0.56944444, 0.56204881, 0.58198984, 0.56666548, 0.55898202]), 'test_average_precision': array([0.59388514, 0.58539669, 0.59739029, 0.58786297, 0.5800104 ]), 'test_neg_log_loss': array([-0.68259685, -0.68457113, -0.68124049, -0.68412756, -0.68515702]), 'test_neg_brier_score': array([-0.24481102, -0.24578203, -0.24411818, -0.24555611, -0.24605887]), 'test_f1_macro': array([0.54419483, 0.53490993, 0.55926764, 0.54926171, 0.53974871]), 'test_f1_weighted': array([0.54418682, 0.53544299, 0.56032384, 0.55000531, 0.54024425]), 'test_balanced_accuracy': array([0.54495008, 0.53493272, 0.55952747, 0.54926639, 0.5397887 ])}</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>0.5462192906987859</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.5613159597079752</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.5624074074074074</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>[0.5182105  0.56240741 1.        ]</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0.5602287400848552</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>[1.         0.56022874 0.        ]</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>[[2677 2363]
+ [2384 3037]]</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5289468484489231, 'recall': 0.5311507936507937, 'f1-score': 0.53004653004653, 'support': 5040.0}</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5624074074074074, 'recall': 0.5602287400848552, 'f1-score': 0.5613159597079752, 'support': 5421.0}</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5456771279281653, 'recall': 0.5456897668678244, 'f1-score': 0.5456812448772526, 'support': 10461.0}</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5462864613075354, 'recall': 0.5462192906987859, 'f1-score': 0.546250676705042, 'support': 10461.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier(max_leaf_nodes=16, n_estimators=500, n_jobs=-1,
+                       random_state=42)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_2_5/oob=False</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>[0.54599761 0.54360812 0.56152927 0.53078302 0.5469217 ]</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.65936875, 0.65651774, 0.66894412, 0.66553855, 0.66220212]), 'score_time': array([0.12513733, 0.13646555, 0.14841652, 0.13325953, 0.12601376]), 'test_accuracy': array([0.54599761, 0.54360812, 0.56152927, 0.53078302, 0.5469217 ]), 'test_precision': array([0.55813953, 0.55478088, 0.56835938, 0.54852781, 0.55587669]), 'test_recall': array([0.63085714, 0.63729977, 0.66590389, 0.57551487, 0.66018307]), 'test_f1': array([0.59227468, 0.59318424, 0.61327713, 0.56169738, 0.60355649]), 'test_roc_auc': array([0.58102342, 0.57651888, 0.59121997, 0.55832806, 0.56535773]), 'test_average_precision': array([0.60796607, 0.60087792, 0.60878349, 0.58881943, 0.59535808]), 'test_neg_log_loss': array([-0.67991653, -0.68163335, -0.68074441, -0.68442289, -0.68367192]), 'test_neg_brier_score': array([-0.24350641, -0.24432857, -0.24388044, -0.24571625, -0.24535112]), 'test_f1_macro': array([0.54007265, 0.53672817, 0.55353512, 0.52843711, 0.53748257]), 'test_f1_weighted': array([0.54244263, 0.53922384, 0.55617604, 0.52992816, 0.54044464]), 'test_balanced_accuracy': array([0.54196174, 0.53927489, 0.55670195, 0.52868359, 0.54160593])}</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>0.5457695984703633</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.5931713582361126</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.5573209975864843</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>[0.52234704 0.557321   1.        ]</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0.6339510409517273</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>[1.         0.63395104 0.        ]</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>[[1796 2201]
+ [1600 2771]]</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5288574793875147, 'recall': 0.44933700275206406, 'f1-score': 0.48586500743946975, 'support': 3997.0}</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5573209975864843, 'recall': 0.6339510409517273, 'f1-score': 0.5931713582361126, 'support': 4371.0}</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5430892384869995, 'recall': 0.5416440218518956, 'f1-score': 0.5395181828377912, 'support': 8368.0}</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5437253137622393, 'recall': 0.5457695984703633, 'f1-score': 0.5419161617573623, 'support': 8368.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BaggingClassifier(estimator=DecisionTreeClassifier(max_leaf_nodes=16,
+                                                   random_state=42),
+                  max_samples=100, n_estimators=500, n_jobs=-1, random_state=42,
+                  verbose=1)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_2_5/bagging=True</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>[0.51612903 0.52927121 0.53942652 0.5469217  0.54393305]</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.11905766, 0.12567496, 0.13378882, 0.13160443, 0.13321376]), 'score_time': array([0.16339087, 0.16260195, 0.16456556, 0.17289877, 0.20248747]), 'test_accuracy': array([0.51612903, 0.52927121, 0.53942652, 0.5469217 , 0.54393305]), 'test_precision': array([0.5312843 , 0.54144806, 0.54943935, 0.56116723, 0.54961832]), 'test_recall': array([0.55824683, 0.59515571, 0.62096774, 0.57670127, 0.66435986]), 'test_f1': array([0.54443195, 0.56703297, 0.58301785, 0.56882821, 0.60156658]), 'test_roc_auc': array([0.54559513, 0.54375855, 0.56789945, 0.57180289, 0.58055787]), 'test_average_precision': array([0.57170659, 0.56737238, 0.58473583, 0.60085962, 0.60794687]), 'test_neg_log_loss': array([-0.68737382, -0.68864503, -0.68425492, -0.68219964, -0.68049449]), 'test_neg_brier_score': array([-0.24715997, -0.24778004, -0.24559677, -0.24462875, -0.24378884]), 'test_f1_macro': array([0.51425419, 0.52566308, 0.53433748, 0.54574912, 0.5341865 ]), 'test_f1_weighted': array([0.51533583, 0.52714587, 0.53614045, 0.54659062, 0.53664328]), 'test_balanced_accuracy': array([0.51456331, 0.52682197, 0.53629032, 0.5457948 , 0.53937596])}</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>0.5351338432122371</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.5734649122807017</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.5466137123745819</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>[0.51816444 0.54661371 1.        ]</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>0.603090405904059</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>[1.         0.60309041 0.        ]</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>[[1863 2169]
+ [1721 2615]]</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5198102678571429, 'recall': 0.46205357142857145, 'f1-score': 0.4892331932773109, 'support': 4032.0}</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5466137123745819, 'recall': 0.603090405904059, 'f1-score': 0.5734649122807017, 'support': 4336.0}</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5332119901158624, 'recall': 0.5325719886663153, 'f1-score': 0.5313490527790063, 'support': 8368.0}</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5336988595669439, 'recall': 0.5351338432122371, 'f1-score': 0.5328790744435038, 'support': 8368.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BaggingClassifier(bootstrap=False,
+                  estimator=DecisionTreeClassifier(max_leaf_nodes=16,
+                                                   random_state=42),
+                  max_samples=100, n_estimators=500, n_jobs=-1, random_state=42,
+                  verbose=1)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_2_5/bagging=False</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>[0.52867384 0.53584229 0.54181601 0.55768081 0.53616258]</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.11840487, 0.13881874, 0.13280702, 0.13153481, 0.13266778]), 'score_time': array([0.16903496, 0.20474887, 0.21554708, 0.15520906, 0.20134449]), 'test_accuracy': array([0.52867384, 0.53584229, 0.54181601, 0.55768081, 0.53616258]), 'test_precision': array([0.54295154, 0.54912664, 0.54926829, 0.56691254, 0.5443038 ]), 'test_recall': array([0.56862745, 0.58016148, 0.64861751, 0.62053057, 0.64475202]), 'test_f1': array([0.55549296, 0.56421761, 0.59482303, 0.59251101, 0.59028511]), 'test_roc_auc': array([0.5440887 , 0.5502016 , 0.56819104, 0.58680714, 0.57911397]), 'test_average_precision': array([0.57178245, 0.57630243, 0.58091087, 0.60880338, 0.61032543]), 'test_neg_log_loss': array([-0.68832119, -0.68746684, -0.68497077, -0.68050916, -0.6811695 ]), 'test_neg_brier_score': array([-0.24763042, -0.24720304, -0.24592549, -0.24379077, -0.24411167]), 'test_f1_macro': array([0.52695182, 0.53386599, 0.53383763, 0.55442544, 0.52792492]), 'test_f1_weighted': array([0.5279748 , 0.53495387, 0.53609635, 0.5558141 , 0.53019867]), 'test_balanced_accuracy': array([0.52718857, 0.53419474, 0.53770826, 0.5553025 , 0.53205343])}</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>0.5400334608030593</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.5798493614234254</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.5504663212435233</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>[0.51816444 0.55046632 1.        ]</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>0.6125461254612546</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>[1.         0.61254613 0.        ]</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>[[1863 2169]
+ [1680 2656]]</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5258255715495342, 'recall': 0.46205357142857145, 'f1-score': 0.4918811881188119, 'support': 4032.0}</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5504663212435233, 'recall': 0.6125461254612546, 'f1-score': 0.5798493614234254, 'support': 4336.0}</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5381459463965288, 'recall': 0.5372998484449131, 'f1-score': 0.5358652747711186, 'support': 8368.0}</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5385935317160181, 'recall': 0.5400334608030593, 'f1-score': 0.5374631670204376, 'support': 8368.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>GradientBoostingClassifier(learning_rate=0.5, max_depth=2, n_estimators=200,
+                           random_state=42)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_3_5</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>[0.63832078 0.63685345 0.65193966 0.65732759 0.6487069 ]</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.90304089, 0.90791941, 0.90090656, 0.90684676, 0.90152764]), 'score_time': array([0.01100373, 0.01000214, 0.00900126, 0.01100373, 0.01000047]), 'test_accuracy': array([0.63832078, 0.63685345, 0.65193966, 0.65732759, 0.6487069 ]), 'test_precision': array([0.36075949, 0.36196319, 0.38571429, 0.40559441, 0.39263804]), 'test_recall': array([0.19520548, 0.20205479, 0.18556701, 0.19931271, 0.21993127]), 'test_f1': array([0.25333333, 0.25934066, 0.25058005, 0.26728111, 0.28193833]), 'test_roc_auc': array([0.54867637, 0.54216206, 0.58881031, 0.54418532, 0.57967168]), 'test_average_precision': array([0.34673957, 0.36593333, 0.37175271, 0.35717921, 0.36842037]), 'test_neg_log_loss': array([-0.69449409, -0.684719  , -0.66481358, -0.69306286, -0.6647443 ]), 'test_neg_brier_score': array([-0.2396996 , -0.23709331, -0.22905238, -0.23636835, -0.23064334]), 'test_f1_macro': array([0.50734848, 0.50939909, 0.51195669, 0.52182621, 0.52470668]), 'test_f1_weighted': array([0.60168135, 0.60209317, 0.60940962, 0.61673203, 0.61522161]), 'test_balanced_accuracy': array([0.51832487, 0.51926639, 0.52527958, 0.53293736, 0.53225763])}</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>0.6466278819219996</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.2625899280575539</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.3807040417209908</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>[0.31394096 0.38070404 1.        ]</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>0.2004118050789293</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>[1.         0.20041181 0.        ]</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>[[2709  475]
+ [1165  292]]</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6992772328342798, 'recall': 0.8508165829145728, 'f1-score': 0.7676395579484273, 'support': 3184.0}</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>{'precision': 0.38070404172099087, 'recall': 0.2004118050789293, 'f1-score': 0.26258992805755393, 'support': 1457.0}</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5399906372776353, 'recall': 0.5256141939967511, 'f1-score': 0.5151147430029906, 'support': 4641.0}</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5992640590674059, 'recall': 0.6466278819219996, 'f1-score': 0.609083791787901, 'support': 4641.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier(algorithm='SAMME',
+                   estimator=DecisionTreeClassifier(max_depth=1,
+                                                    max_leaf_nodes=16,
+                                                    random_state=42),
+                   learning_rate=0.5, n_estimators=500, random_state=42)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_3_5/samme</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>[0.68891281 0.67672414 0.69073276 0.68642241 0.68642241]</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([1.41682363, 1.42214251, 1.41831422, 1.43394184, 1.4704752 ]), 'score_time': array([0.09773707, 0.09230304, 0.09267068, 0.09761906, 0.09421539]), 'test_accuracy': array([0.68891281, 0.67672414, 0.69073276, 0.68642241, 0.68642241]), 'test_precision': array([0.55172414, 0.4375    , 0.64285714, 0.5       , 0.5       ]), 'test_recall': array([0.05479452, 0.09589041, 0.03092784, 0.10996564, 0.02749141]), 'test_f1': array([0.09968847, 0.15730337, 0.05901639, 0.18028169, 0.05211726]), 'test_roc_auc': array([0.63574439, 0.61937839, 0.63659659, 0.60656697, 0.63999256]), 'test_average_precision': array([0.42515622, 0.41533445, 0.44659524, 0.40924909, 0.42719018]), 'test_neg_log_loss': array([-0.61866484, -0.61646527, -0.61035419, -0.62333147, -0.60923641]), 'test_neg_brier_score': array([-0.21376144, -0.21291064, -0.20988214, -0.21595199, -0.20942443]), 'test_f1_macro': array([0.45582992, 0.47865169, 0.43698724, 0.49320547, 0.43212706]), 'test_f1_weighted': array([0.58808913, 0.59777218, 0.57791172, 0.60987748, 0.57381175]), 'test_balanced_accuracy': array([0.51719318, 0.51964332, 0.51153927, 0.52986508, 0.50746627])}</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>0.6858435681965094</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.1131386861313868</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.4973262032085561</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>[0.31394096 0.4973262  1.        ]</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>0.06382978723404251</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>[1.         0.06382979 0.        ]</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>[[3090   94]
+ [1364   93]]</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6937584193982936, 'recall': 0.9704773869346733, 'f1-score': 0.8091123330714847, 'support': 3184.0}</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>{'precision': 0.49732620320855614, 'recall': 0.06382978723404255, 'f1-score': 0.11313868613138686, 'support': 1457.0}</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5955423113034248, 'recall': 0.517153587084358, 'f1-score': 0.4611255096014358, 'support': 4641.0}</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>{'precision': 0.63209030067637, 'recall': 0.6858435681965094, 'f1-score': 0.5906176975205856, 'support': 4641.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier(estimator=DecisionTreeClassifier(max_depth=1,
+                                                    max_leaf_nodes=16,
+                                                    random_state=42),
+                   learning_rate=0.5, n_estimators=500, random_state=42)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_3_5/samme_r</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>[0.67384284 0.67349138 0.68426724 0.67241379 0.68103448]</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([1.56782603, 1.56911373, 1.57234597, 1.56982303, 1.56597829]), 'score_time': array([0.12065744, 0.12184262, 0.12159109, 0.12369752, 0.12371826]), 'test_accuracy': array([0.67384284, 0.67349138, 0.68426724, 0.67241379, 0.68103448]), 'test_precision': array([0.43373494, 0.43373494, 0.48780488, 0.43925234, 0.47126437]), 'test_recall': array([0.12328767, 0.12328767, 0.13745704, 0.16151203, 0.14089347]), 'test_f1': array([0.192     , 0.192     , 0.21447721, 0.2361809 , 0.21693122]), 'test_roc_auc': array([0.60289832, 0.59125958, 0.63011216, 0.58029207, 0.62901703]), 'test_average_precision': array([0.39184525, 0.39221766, 0.43463025, 0.37603094, 0.41094624]), 'test_neg_log_loss': array([-0.69221738, -0.69226807, -0.69210812, -0.69222599, -0.69229643]), 'test_neg_brier_score': array([-0.2495351 , -0.24956044, -0.24948047, -0.24953942, -0.24957461]), 'test_f1_macro': array([0.49384221, 0.49370425, 0.50845236, 0.51383805, 0.50833029]), 'test_f1_weighted': array([0.60593647, 0.6055429 , 0.61805948, 0.61736108, 0.61697693]), 'test_balanced_accuracy': array([0.52475216, 0.52469415, 0.53576149, 0.53366025, 0.53433999])}</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>0.6770092652445594</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.210637177461822</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.4524886877828054</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>[0.31394096 0.45248869 1.        ]</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>0.1372683596431022</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>[1.         0.13726836 0.        ]</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>[[2942  242]
+ [1257  200]]</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7006430102405334, 'recall': 0.9239949748743719, 'f1-score': 0.7969660029798185, 'support': 3184.0}</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>{'precision': 0.45248868778280543, 'recall': 0.13726835964310227, 'f1-score': 0.210637177461822, 'support': 1457.0}</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5765658490116694, 'recall': 0.5306316672587371, 'f1-score': 0.5038015902208203, 'support': 4641.0}</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6227372037719039, 'recall': 0.6770092652445594, 'f1-score': 0.6128933680348236, 'support': 4641.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier(max_leaf_nodes=16, n_estimators=500, n_jobs=-1,
+                       oob_score=True, random_state=42)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_3_5/oob=True</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>[0.68568353 0.68857759 0.68642241 0.67456897 0.68103448]</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.71139026, 0.68548656, 0.69466305, 0.72042274, 0.70340276]), 'score_time': array([0.12541413, 0.14014339, 0.12187982, 0.12708688, 0.11337328]), 'test_accuracy': array([0.68568353, 0.68857759, 0.68642241, 0.67456897, 0.68103448]), 'test_precision': array([0.5       , 0.54545455, 0.5       , 0.36585366, 0.40740741]), 'test_recall': array([0.03082192, 0.06164384, 0.02405498, 0.05154639, 0.03780069]), 'test_f1': array([0.05806452, 0.11076923, 0.04590164, 0.09036145, 0.06918239]), 'test_roc_auc': array([0.6360132 , 0.62365383, 0.62834269, 0.60105628, 0.64769889]), 'test_average_precision': array([0.42646052, 0.42056503, 0.43056518, 0.38636169, 0.42873431]), 'test_neg_log_loss': array([-0.59962781, -0.60371797, -0.59949038, -0.60899925, -0.59408697]), 'test_neg_brier_score': array([-0.20577026, -0.20762573, -0.20545769, -0.20971319, -0.20329583]), 'test_f1_macro': array([0.43471701, 0.46100186, 0.42914037, 0.44609936, 0.43836233]), 'test_f1_weighted': array([0.57459334, 0.59082947, 0.57202896, 0.5787344 , 0.57600916]), 'test_balanced_accuracy': array([0.50834659, 0.51902946, 0.50653299, 0.50536503, 0.50634147])}</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>0.6832579185520362</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.0754716981132075</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.4511278195488721</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>[0.31394096 0.45112782 1.        ]</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>0.0411805078929306</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>[1.         0.04118051 0.        ]</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>[[3111   73]
+ [1397   60]]</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6901064773735581, 'recall': 0.977072864321608, 'f1-score': 0.8088923556942278, 'support': 3184.0}</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>{'precision': 0.45112781954887216, 'recall': 0.04118050789293068, 'f1-score': 0.07547169811320754, 'support': 1457.0}</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5706171484612151, 'recall': 0.5091266861072693, 'f1-score': 0.44218202690371766, 'support': 4641.0}</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6150812878776375, 'recall': 0.6832579185520362, 'f1-score': 0.5786415696361484, 'support': 4641.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier(max_leaf_nodes=16, n_estimators=500, n_jobs=-1,
+                       random_state=42)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_3_5/oob=False</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>[0.69044415 0.69179004 0.67924528 0.68328841 0.68598383]</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.54816437, 0.5554378 , 0.56040025, 0.56065154, 0.5626297 ]), 'score_time': array([0.12392092, 0.14586782, 0.12382674, 0.12442231, 0.14230371]), 'test_accuracy': array([0.69044415, 0.69179004, 0.67924528, 0.68328841, 0.68598383]), 'test_precision': array([0.55555556, 0.58823529, 0.36      , 0.42307692, 0.42857143]), 'test_recall': array([0.02164502, 0.04310345, 0.03896104, 0.04761905, 0.02597403]), 'test_f1': array([0.04166667, 0.08032129, 0.0703125 , 0.08560311, 0.04897959]), 'test_roc_auc': array([0.67853761, 0.63278561, 0.62178396, 0.59919858, 0.6139477 ]), 'test_average_precision': array([0.48196627, 0.43861921, 0.40352904, 0.3821888 , 0.39663634]), 'test_neg_log_loss': array([-0.5809826 , -0.59555723, -0.60062696, -0.60836801, -0.60236381]), 'test_neg_brier_score': array([-0.197356  , -0.20376079, -0.20602169, -0.2094767 , -0.20684462]), 'test_f1_macro': array([0.42853799, 0.44759799, 0.43825071, 0.44703954, 0.43046235]), 'test_f1_weighted': array([0.57485137, 0.58551212, 0.57709532, 0.58343064, 0.57441811]), 'test_balanced_accuracy': array([0.50691626, 0.51470241, 0.50382494, 0.50913242, 0.50515922])}</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>0.6861530172413793</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.065757818765036</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.4505494505494505</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>[0.31142241 0.45054945 1.        ]</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>0.0354671280276816</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>[1.         0.03546713 0.        ]</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>[[2506   50]
+ [1115   41]]</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>{'precision': 0.692074012703673, 'recall': 0.9804381846635368, 'f1-score': 0.8113971183422374, 'support': 2556.0}</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>{'precision': 0.45054945054945056, 'recall': 0.03546712802768166, 'f1-score': 0.06575781876503609, 'support': 1156.0}</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5713117316265618, 'recall': 0.5079526563456093, 'f1-score': 0.4385774685536367, 'support': 3712.0}</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6168578505672826, 'recall': 0.6861530172413793, 'f1-score': 0.5791883278489063, 'support': 3712.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BaggingClassifier(estimator=DecisionTreeClassifier(max_leaf_nodes=16,
+                                                   random_state=42),
+                  max_samples=100, n_estimators=500, n_jobs=-1, random_state=42,
+                  verbose=1)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_3_5/bagging=True</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>[0.6769852  0.68909825 0.68328841 0.70754717 0.68059299]</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.09849954, 0.10881567, 0.10805249, 0.10758376, 0.09355092]), 'score_time': array([0.15245247, 0.14460468, 0.18172002, 0.16187048, 0.17783165]), 'test_accuracy': array([0.6769852 , 0.68909825, 0.68328841, 0.70754717, 0.68059299]), 'test_precision': array([0.43396226, 0.52777778, 0.475     , 0.61111111, 0.45      ]), 'test_recall': array([0.09871245, 0.08154506, 0.08154506, 0.1888412 , 0.07725322]), 'test_f1': array([0.16083916, 0.14126394, 0.13919414, 0.28852459, 0.13186813]), 'test_roc_auc': array([0.59240932, 0.64094926, 0.61619603, 0.63209019, 0.64359132]), 'test_average_precision': array([0.39041549, 0.44311517, 0.41355651, 0.46655994, 0.43998281]), 'test_neg_log_loss': array([-0.61411632, -0.59550799, -0.60489968, -0.60102298, -0.59508343]), 'test_neg_brier_score': array([-0.211746  , -0.20400237, -0.20806585, -0.20546718, -0.20375706]), 'test_f1_macro': array([0.48041958, 0.47572646, 0.47256982, 0.55223515, 0.46808105]), 'test_f1_weighted': array([0.59956329, 0.60041842, 0.59657479, 0.65032695, 0.59314138]), 'test_balanced_accuracy': array([0.51994446, 0.52410587, 0.52014385, 0.56691569, 0.51701561])}</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.1749644381223328</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.5103734439834025</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>[0.31384698 0.51037344 1.        ]</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>0.1055793991416309</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>[1.        0.1055794 0.       ]</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>[[2429  118]
+ [1042  123]]</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6997983290118122, 'recall': 0.9536709854731056, 'f1-score': 0.8072449318710535, 'support': 2547.0}</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5103734439834025, 'recall': 0.1055793991416309, 'f1-score': 0.17496443812233287, 'support': 1165.0}</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6050858864976073, 'recall': 0.5296251923073683, 'f1-score': 0.4911046849966932, 'support': 3712.0}</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6403479003862471, 'recall': 0.6875, 'f1-score': 0.6088056066508866, 'support': 3712.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>BaggingClassifier(bootstrap=False,
+                  estimator=DecisionTreeClassifier(max_leaf_nodes=16,
+                                                   random_state=42),
+                  max_samples=100, n_estimators=500, n_jobs=-1, random_state=42,
+                  verbose=1)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_3_5/bagging=False</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>[0.67160162 0.68506057 0.68733154 0.70754717 0.69002695]</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.10174322, 0.10947919, 0.10222745, 0.1043098 , 0.09865689]), 'score_time': array([0.14885092, 0.15907693, 0.15246201, 0.16030407, 0.14100099]), 'test_accuracy': array([0.67160162, 0.68506057, 0.68733154, 0.70754717, 0.69002695]), 'test_precision': array([0.41269841, 0.48979592, 0.50943396, 0.66      , 0.54054054]), 'test_recall': array([0.11158798, 0.10300429, 0.11587983, 0.1416309 , 0.08583691]), 'test_f1': array([0.17567568, 0.17021277, 0.18881119, 0.23321555, 0.14814815]), 'test_roc_auc': array([0.59231676, 0.62578473, 0.62144068, 0.6348137 , 0.64962857]), 'test_average_precision': array([0.39580203, 0.42817558, 0.40955708, 0.45796466, 0.4486484 ]), 'test_neg_log_loss': array([-0.61635953, -0.60123521, -0.6035548 , -0.60064399, -0.59358837]), 'test_neg_brier_score': array([-0.21253049, -0.20639553, -0.20756683, -0.20540295, -0.20303492]), 'test_f1_macro': array([0.48531683, 0.4879303 , 0.49757755, 0.52626639, 0.4793459 ]), 'test_f1_weighted': array([0.60075505, 0.60637951, 0.61242865, 0.63527183, 0.60254075]), 'test_balanced_accuracy': array([0.51951948, 0.52699234, 0.53239964, 0.55411604, 0.52621904])}</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>0.6883081896551724</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.1834862385321101</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.5158730158730159</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>[0.31384698 0.51587302 1.        ]</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>0.111587982832618</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>[1.         0.11158798 0.        ]</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>[[2425  122]
+ [1035  130]]</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7008670520231214, 'recall': 0.9521005104043974, 'f1-score': 0.8073913767271517, 'support': 2547.0}</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5158730158730159, 'recall': 0.11158798283261803, 'f1-score': 0.1834862385321101, 'support': 1165.0}</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6083700339480687, 'recall': 0.5318442466185077, 'f1-score': 0.4954388076296309, 'support': 3712.0}</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6428072319490716, 'recall': 0.6883081896551724, 'f1-score': 0.6115806315770376, 'support': 3712.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>GradientBoostingClassifier(learning_rate=0.5, max_depth=2, n_estimators=200,
+                           random_state=42)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_3_5</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>[0.65478842 0.63585746 0.64253898 0.63768116 0.64882943]</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.86331749, 0.86525559, 0.8620894 , 0.85822296, 0.85796213]), 'score_time': array([0.01116562, 0.01000309, 0.01000333, 0.01000333, 0.01000357]), 'test_accuracy': array([0.65478842, 0.63585746, 0.64253898, 0.63768116, 0.64882943]), 'test_precision': array([0.40136054, 0.32307692, 0.35507246, 0.3358209 , 0.38513514]), 'test_recall': array([0.20996441, 0.14946619, 0.17437722, 0.16014235, 0.20284698]), 'test_f1': array([0.27570093, 0.20437956, 0.23389021, 0.21686747, 0.26573427]), 'test_roc_auc': array([0.58155926, 0.54036579, 0.54451282, 0.55519481, 0.56915816]), 'test_average_precision': array([0.38649669, 0.34336697, 0.35605954, 0.33897047, 0.36157289]), 'test_neg_log_loss': array([-0.66115198, -0.69023517, -0.68664487, -0.69444532, -0.66460286]), 'test_neg_brier_score': array([-0.22828753, -0.23857709, -0.23617216, -0.23879534, -0.23033727]), 'test_f1_macro': array([0.52454637, 0.48413924, 0.50038737, 0.49059472, 0.51748252]), 'test_f1_weighted': array([0.61765558, 0.58881547, 0.60010123, 0.59282285, 0.61150221]), 'test_balanced_accuracy': array([0.5336694 , 0.50342029, 0.51506544, 0.50783091, 0.52755985])}</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>0.6439393939393939</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.2397716460513796</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.3615494978479197</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>[0.31305704 0.3615495  1.        ]</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>0.1793594306049822</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>[1.         0.17935943 0.        ]</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>[[2638  445]
+ [1153  252]]</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6958586125032973, 'recall': 0.8556600713590659, 'f1-score': 0.7675298225196392, 'support': 3083.0}</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>{'precision': 0.3615494978479197, 'recall': 0.17935943060498222, 'f1-score': 0.23977164605137963, 'support': 1405.0}</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5287040551756085, 'recall': 0.517509750982024, 'f1-score': 0.5036507342855094, 'support': 4488.0}</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>{'precision': 0.591200790290551, 'recall': 0.6439393939393939, 'f1-score': 0.6023114094318708, 'support': 4488.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier(algorithm='SAMME',
+                   estimator=DecisionTreeClassifier(max_depth=1,
+                                                    max_leaf_nodes=16,
+                                                    random_state=42),
+                   learning_rate=0.5, n_estimators=500, random_state=42)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_3_5/samme</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>[0.68819599 0.68040089 0.68262806 0.68227425 0.68896321]</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([1.41113949, 1.39584923, 1.40376973, 1.41403675, 1.40064287]), 'score_time': array([0.09701085, 0.09879923, 0.09832001, 0.09894109, 0.09464002]), 'test_accuracy': array([0.68819599, 0.68040089, 0.68262806, 0.68227425, 0.68896321]), 'test_precision': array([0.55555556, 0.375     , 0.375     , 0.35714286, 1.        ]), 'test_recall': array([0.01779359, 0.03202847, 0.02135231, 0.01779359, 0.00711744]), 'test_f1': array([0.03448276, 0.05901639, 0.04040404, 0.03389831, 0.01413428]), 'test_roc_auc': array([0.60486108, 0.60198585, 0.56965745, 0.5901494 , 0.67284917]), 'test_average_precision': array([0.39543405, 0.38097455, 0.37916904, 0.38302243, 0.45483097]), 'test_neg_log_loss': array([-0.62187863, -0.63383853, -0.63773172, -0.63183544, -0.61266315]), 'test_neg_brier_score': array([-0.21535376, -0.22097806, -0.22277654, -0.22005005, -0.21108202]), 'test_f1_macro': array([0.42427989, 0.43326407, 0.42513864, 0.42188578, 0.41474417]), 'test_f1_weighted': array([0.57012826, 0.57329437, 0.56909279, 0.56678634, 0.56435879]), 'test_balanced_accuracy': array([0.50565531, 0.50385864, 0.50257243, 0.5015916 , 0.50355872])}</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>0.6844919786096256</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.036734693877551</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.4153846153846154</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>[0.31305704 0.41538462 1.        ]</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>0.0192170818505338</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>[1.         0.01921708 0.        ]</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>[[3045   38]
+ [1378   27]]</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6884467555957495, 'recall': 0.9876743431722348, 'f1-score': 0.8113509192645884, 'support': 3083.0}</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>{'precision': 0.4153846153846154, 'recall': 0.019217081850533807, 'f1-score': 0.036734693877551024, 'support': 1405.0}</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5519156854901824, 'recall': 0.5034457125113843, 'f1-score': 0.4240428065710697, 'support': 4488.0}</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6029627299726116, 'recall': 0.6844919786096256, 'f1-score': 0.5688518558357142, 'support': 4488.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier(estimator=DecisionTreeClassifier(max_depth=1,
+                                                    max_leaf_nodes=16,
+                                                    random_state=42),
+                   learning_rate=0.5, n_estimators=500, random_state=42)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_3_5/samme_r</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>[0.67594655 0.67817372 0.68151448 0.68673356 0.69007804]</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([1.52368546, 1.52033281, 1.5275023 , 1.48589301, 1.48148894]), 'score_time': array([0.12317657, 0.1229732 , 0.12004066, 0.11691427, 0.11727238]), 'test_accuracy': array([0.67594655, 0.67817372, 0.68151448, 0.68673356, 0.69007804]), 'test_precision': array([0.43243243, 0.43333333, 0.45901639, 0.5       , 0.52830189]), 'test_recall': array([0.113879  , 0.09252669, 0.09964413, 0.10676157, 0.09964413]), 'test_f1': array([0.18028169, 0.15249267, 0.16374269, 0.17595308, 0.16766467]), 'test_roc_auc': array([0.5852045 , 0.59091748, 0.5663381 , 0.5959872 , 0.6325565 ]), 'test_average_precision': array([0.3964085 , 0.38615987, 0.37414094, 0.38818391, 0.42835179]), 'test_neg_log_loss': array([-0.69212711, -0.6922383 , -0.69234607, -0.69217562, -0.69227418]), 'test_neg_brier_score': array([-0.24948998, -0.24954556, -0.24959944, -0.24951423, -0.24956349]), 'test_f1_macro': array([0.4891693 , 0.47693362, 0.48352196, 0.49128005, 0.48862686]), 'test_f1_weighted': array([0.60474417, 0.59832801, 0.60317212, 0.6090443 , 0.60849568]), 'test_balanced_accuracy': array([0.52290385, 0.51871067, 0.52307976, 0.52903013, 0.52952986])}</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>0.6824866310160428</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.1681260945709282</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.4675324675324675</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>[0.31305704 0.46753247 1.        ]</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>0.1024911032028469</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>[1.        0.1024911 0.       ]</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>[[2919  164]
+ [1261  144]]</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6983253588516747, 'recall': 0.9468050600064872, 'f1-score': 0.8038000826104915, 'support': 3083.0}</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>{'precision': 0.4675324675324675, 'recall': 0.10249110320284698, 'f1-score': 0.1681260945709282, 'support': 1405.0}</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5829289131920711, 'recall': 0.5246480816046671, 'f1-score': 0.48596308859070986, 'support': 4488.0}</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6260740192118606, 'recall': 0.6824866310160428, 'f1-score': 0.6047978648752895, 'support': 4488.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier(max_leaf_nodes=16, n_estimators=500, n_jobs=-1,
+                       oob_score=True, random_state=42)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_3_5/oob=True</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>[0.68708241 0.68374165 0.68708241 0.68561873 0.68896321]</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.68867755, 0.69776392, 0.7070744 , 0.70071054, 0.72534585]), 'score_time': array([0.12203169, 0.1232698 , 0.1280849 , 0.11600184, 0.12495303]), 'test_accuracy': array([0.68708241, 0.68374165, 0.68708241, 0.68561873, 0.68896321]), 'test_precision': array([0.5, 0.2, 0. , 0. , 1. ]), 'test_recall': array([0.00355872, 0.00355872, 0.        , 0.        , 0.00711744]), 'test_f1': array([0.00706714, 0.00699301, 0.        , 0.        , 0.01413428]), 'test_roc_auc': array([0.60403052, 0.59755331, 0.56312544, 0.58879466, 0.66701715]), 'test_average_precision': array([0.39168663, 0.38346427, 0.37063324, 0.37831089, 0.44451329]), 'test_neg_log_loss': array([-0.60859539, -0.60933162, -0.61704659, -0.61168931, -0.59675855]), 'test_neg_brier_score': array([-0.20966592, -0.20998507, -0.21297177, -0.21093646, -0.2045727 ]), 'test_f1_macro': array([0.41067171, 0.40945677, 0.40726073, 0.40674603, 0.41474417]), 'test_f1_weighted': array([0.56168633, 0.56004455, 0.55964336, 0.5586523 , 0.56435879]), 'test_balanced_accuracy': array([0.50096899, 0.49853787, 0.5       , 0.49918831, 0.50355872])}</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>0.6864973262032086</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.0056537102473498</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>[0.31305704 0.4        1.        ]</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>0.0028469750889679</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>[1.         0.00284698 0.        ]</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>[[3077    6]
+ [1401    4]]</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6871371147833855, 'recall': 0.9980538436587739, 'f1-score': 0.8139135035048274, 'support': 3083.0}</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>{'precision': 0.4, 'recall': 0.0028469750889679717, 'f1-score': 0.005653710247349823, 'support': 1405.0}</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5435685573916927, 'recall': 0.500450409373871, 'f1-score': 0.4097836068760886, 'support': 4488.0}</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5972468192685333, 'recall': 0.6864973262032086, 'f1-score': 0.5608820842698103, 'support': 4488.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier(max_leaf_nodes=16, n_estimators=500, n_jobs=-1,
+                       random_state=42)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_3_5/oob=False</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>[0.69637883 0.69359331 0.6908078  0.69220056 0.68662953]</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.57014346, 0.55460286, 0.56477332, 0.54727864, 0.56740785]), 'score_time': array([0.12471366, 0.12163806, 0.14712834, 0.12440705, 0.13582993]), 'test_accuracy': array([0.69637883, 0.69359331, 0.6908078 , 0.69220056, 0.68662953]), 'test_precision': array([1.        , 1.        , 0.33333333, 0.5       , 0.16666667]), 'test_recall': array([0.00909091, 0.00452489, 0.00452489, 0.00452489, 0.00452489]), 'test_f1': array([0.01801802, 0.00900901, 0.00892857, 0.00896861, 0.00881057]), 'test_roc_auc': array([0.6267981 , 0.60960332, 0.58683322, 0.58468458, 0.58047835]), 'test_average_precision': array([0.42627835, 0.39938425, 0.36997727, 0.3813635 , 0.36285846]), 'test_neg_log_loss': array([-0.59790436, -0.60294515, -0.6079043 , -0.60762292, -0.61078968]), 'test_neg_brier_score': array([-0.20460977, -0.20709296, -0.20920658, -0.20897073, -0.21051124]), 'test_f1_macro': array([0.41922318, 0.41389495, 0.41288013, 0.41338785, 0.41135318]), 'test_f1_weighted': array([0.57456445, 0.56953356, 0.56815956, 0.56884706, 0.566091  ]), 'test_balanced_accuracy': array([0.50454545, 0.50226244, 0.50025037, 0.50125641, 0.49723226])}</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>0.6919220055710307</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.0107334525939177</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>[0.30752089 0.42857143 1.        ]</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>0.0054347826086956</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>[1.         0.00543478 0.        ]</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>[[2478    8]
+ [1098    6]]</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6929530201342282, 'recall': 0.996781979082864, 'f1-score': 0.8175519630484989, 'support': 2486.0}</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>{'precision': 0.42857142857142855, 'recall': 0.005434782608695652, 'f1-score': 0.01073345259391771, 'support': 1104.0}</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5607622243528284, 'recall': 0.5011083808457798, 'f1-score': 0.41414270782120827, 'support': 3590.0}</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6116501574363644, 'recall': 0.6919220055710307, 'f1-score': 0.5694384155438031, 'support': 3590.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>BaggingClassifier(estimator=DecisionTreeClassifier(max_leaf_nodes=16,
+                                                   random_state=42),
+                  max_samples=100, n_estimators=500, n_jobs=-1, random_state=42,
+                  verbose=1)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_3_5/bagging=True</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>[0.68384401 0.67966574 0.67688022 0.67827298 0.69498607]</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.09705734, 0.10064673, 0.10280585, 0.09916878, 0.10027695]), 'score_time': array([0.1522615 , 0.15329552, 0.1347065 , 0.13528538, 0.14927411]), 'test_accuracy': array([0.68384401, 0.67966574, 0.67688022, 0.67827298, 0.69498607]), 'test_precision': array([0.33333333, 0.4       , 0.26666667, 0.35      , 0.71428571]), 'test_recall': array([0.01339286, 0.04444444, 0.01777778, 0.03111111, 0.04444444]), 'test_f1': array([0.02575107, 0.08      , 0.03333333, 0.05714286, 0.08368201]), 'test_roc_auc': array([0.58986408, 0.59490647, 0.57574938, 0.5662114 , 0.60846518]), 'test_average_precision': array([0.37953591, 0.38018685, 0.35951194, 0.35788598, 0.41853485]), 'test_neg_log_loss': array([-0.61139039, -0.61178611, -0.61689058, -0.62106393, -0.60642644]), 'test_neg_brier_score': array([-0.21069429, -0.21105725, -0.21354978, -0.21498336, -0.20838832]), 'test_f1_macro': array([0.41852807, 0.44303541, 0.4196767 , 0.4315941 , 0.45036231]), 'test_f1_weighted': array([0.56622973, 0.57854167, 0.56388286, 0.57136141, 0.58722905]), 'test_balanced_accuracy': array([0.50062355, 0.50700924, 0.4977327 , 0.50237097, 0.51816543])}</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>0.6827298050139275</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.056338028169014</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.4096385542168674</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>[0.31309192 0.40963855 1.        ]</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>0.0302491103202846</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>[1.         0.03024911 0.        ]</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>[[2417   49]
+ [1090   34]]</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6891930424864556, 'recall': 0.9801297648012977, 'f1-score': 0.8093085551649087, 'support': 2466.0}</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>{'precision': 0.40963855421686746, 'recall': 0.030249110320284697, 'f1-score': 0.056338028169014086, 'support': 1124.0}</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5494157983516615, 'recall': 0.5051894375607912, 'f1-score': 0.43282329166696143, 'support': 3590.0}</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6016667904488465, 'recall': 0.6827298050139275, 'f1-score': 0.5735595656542164, 'support': 3590.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>BaggingClassifier(bootstrap=False,
+                  estimator=DecisionTreeClassifier(max_leaf_nodes=16,
+                                                   random_state=42),
+                  max_samples=100, n_estimators=500, n_jobs=-1, random_state=42,
+                  verbose=1)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_3_5/bagging=False</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>[0.67966574 0.68523677 0.67966574 0.68523677 0.68802228]</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([0.09948373, 0.09985304, 0.10025978, 0.1026783 , 0.10973334]), 'score_time': array([0.15831852, 0.14907742, 0.15329218, 0.14292669, 0.15508509]), 'test_accuracy': array([0.67966574, 0.68523677, 0.67966574, 0.68523677, 0.68802228]), 'test_precision': array([0.3125    , 0.46666667, 0.27272727, 0.45454545, 0.53846154]), 'test_recall': array([0.02232143, 0.03111111, 0.01333333, 0.02222222, 0.03111111]), 'test_f1': array([0.04166667, 0.05833333, 0.02542373, 0.04237288, 0.05882353]), 'test_roc_auc': array([0.58809283, 0.59483435, 0.5742078 , 0.57499211, 0.595222  ]), 'test_average_precision': array([0.37208776, 0.37755677, 0.36104446, 0.37443582, 0.40347107]), 'test_neg_log_loss': array([-0.61229958, -0.61133573, -0.61701745, -0.61844204, -0.61140351]), 'test_neg_brier_score': array([-0.21126063, -0.21102343, -0.21351225, -0.21360394, -0.21037734]), 'test_f1_macro': array([0.42467949, 0.43468506, 0.41687853, 0.42701977, 0.43592262]), 'test_f1_weighted': array([0.56870938, 0.57516175, 0.56299258, 0.57059271, 0.57667826]), 'test_balanced_accuracy': array([0.50002711, 0.50744197, 0.49855308, 0.50502592, 0.50947036])}</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>0.6835654596100279</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>0.0453781512605042</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>0.4090909090909091</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>[0.31309192 0.40909091 1.        ]</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>0.02402135231316726</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>[1.         0.02402135 0.        ]</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>[[2427   39]
+ [1097   27]]</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6887060158910329, 'recall': 0.9841849148418491, 'f1-score': 0.8103505843071787, 'support': 2466.0}</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>{'precision': 0.4090909090909091, 'recall': 0.02402135231316726, 'f1-score': 0.0453781512605042, 'support': 1124.0}</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>{'precision': 0.548898462490971, 'recall': 0.5041031335775081, 'f1-score': 0.4278643677838414, 'support': 3590.0}</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6011607846811892, 'recall': 0.6835654596100279, 'f1-score': 0.5708438949633173, 'support': 3590.0}</t>
         </is>
       </c>
     </row>

--- a/src/service_ia/training/version_1/fit/report_fit_grid.xlsx
+++ b/src/service_ia/training/version_1/fit/report_fit_grid.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25420" windowHeight="16300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Report BEST FIT" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Report ML FIT" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report BEST FIT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report ML FIT" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,16 +27,21 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
+      <b val="1"/>
       <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b val="1"/>
@@ -50,12 +55,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -83,13 +103,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -457,75 +480,80 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="10.08984375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="39.1796875" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="18.54296875" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="10.109375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="39.21875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="18.5546875" bestFit="1" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>features</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>best_estimator</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>best_params</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>best_scorer</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>scorer</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>t=mean/event=under_over_1_5/stat=['form']</t>
+          <t>t=mean/event=under_over_1_5/stat=['mean_statistics']</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>{'mean_Total Shots_away_stat', 'under_over_1_5', 'mean_Ball Possession_home_stat', 'mean_Total Shots_home_stat', 'mean_Ball Possession_away_stat'}</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DecisionTreeClassifier(class_weight='balanced', criterion='log_loss',
-                       max_depth=5, min_samples_leaf=2, min_samples_split=5)</t>
+          <t>DecisionTreeClassifier(criterion='entropy', max_depth=5, max_features='sqrt',
+                       min_samples_split=5)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>{'class_weight': 'balanced', 'criterion': 'log_loss', 'max_depth': 5, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 5}</t>
+          <t>{'class_weight': None, 'criterion': 'entropy', 'max_depth': 5, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.5685480143536183</v>
+        <v>0.761407600493895</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -534,29 +562,34 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>t=std/event=under_over_1_5/stat=['form']</t>
+          <t>t=mean/event=under_over_2_5/stat=['mean_statistics']</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>{'mean_Total Shots_away_stat', 'under_over_2_5', 'mean_Ball Possession_home_stat', 'mean_Total Shots_home_stat', 'mean_Ball Possession_away_stat'}</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DecisionTreeClassifier(class_weight='balanced', max_depth=5,
-                       min_samples_split=10)</t>
+          <t>DecisionTreeClassifier(criterion='log_loss', max_depth=5, max_features='log2',
+                       min_samples_leaf=2, min_samples_split=5)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>{'class_weight': 'balanced', 'criterion': 'gini', 'max_depth': 5, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 10}</t>
+          <t>{'class_weight': None, 'criterion': 'log_loss', 'max_depth': 5, 'max_features': 'log2', 'min_samples_leaf': 2, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.5370828419378877</v>
+        <v>0.567320655706345</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -565,29 +598,36 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>t=mean/event=under_over_2_5/stat=['form']</t>
+          <t>t=mean/event=under_over_3_5/stat=['mean_statistics']</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>{'under_over_3_5', 'mean_Total Shots_away_stat', 'mean_Ball Possession_home_stat', 'mean_Total Shots_home_stat', 'mean_Ball Possession_away_stat'}</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DecisionTreeClassifier(class_weight='balanced', criterion='entropy',
-                       max_depth=5, max_features='sqrt', min_samples_split=10)</t>
+          <t>DecisionTreeClassifier(criterion='entropy', max_depth=5, max_features='log2',
+                       min_samples_split=5)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>{'class_weight': 'balanced', 'criterion': 'entropy', 'max_depth': 5, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 10}</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>0.5715153701307512</v>
+          <t>{'class_weight': None, 'criterion': 'entropy', 'max_depth': 5, 'max_features': 'log2', 'min_samples_leaf': 1, 'min_samples_split': 5}</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.6891525423728814</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -596,107 +636,41 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>t=std/event=under_over_2_5/stat=['form']</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>DecisionTreeClassifier(class_weight='balanced', criterion='log_loss',
-                       max_depth=5, min_samples_leaf=2, min_samples_split=10)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>{'class_weight': 'balanced', 'criterion': 'log_loss', 'max_depth': 5, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 10}</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0.5372353945538716</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>make_scorer(accuracy_score, response_method='predict')</t>
-        </is>
-      </c>
+      <c r="A5" s="1" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>t=mean/event=under_over_3_5/stat=['form']</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>DecisionTreeClassifier(class_weight='balanced', criterion='log_loss',
-                       max_depth=5, min_samples_leaf=4)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>{'class_weight': 'balanced', 'criterion': 'log_loss', 'max_depth': 5, 'max_features': None, 'min_samples_leaf': 4, 'min_samples_split': 2}</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0.5682510581546578</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>make_scorer(accuracy_score, response_method='predict')</t>
-        </is>
-      </c>
+      <c r="A6" s="1" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>t=std/event=under_over_3_5/stat=['form']</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>DecisionTreeClassifier(class_weight='balanced', max_depth=5,
-                       min_samples_split=5)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>{'class_weight': 'balanced', 'criterion': 'gini', 'max_depth': 5, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 5}</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0.5370828419378877</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>make_scorer(accuracy_score, response_method='predict')</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="C26" s="2" t="n"/>
+      <c r="A7" s="1" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="C11" s="1" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -710,148 +684,158 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <dimension ref="A1:R17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="10.33203125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="48.109375" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="5.6640625" customWidth="1" min="13" max="13"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>estimator</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>cross_val_score</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>cross_val</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>precisions</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>recalls</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>threshold</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>thresholds</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>confusion matrix</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>macro avg</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>weighted avg</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" customFormat="1" s="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RandomForestClassifier(max_leaf_nodes=16, n_estimators=500, n_jobs=-1,
-                       oob_score=True, random_state=42)</t>
+          <t>AdaBoostClassifier(algorithm='SAMME',
+                   estimator=DecisionTreeClassifier(criterion='entropy',
+                                                    max_depth=5,
+                                                    max_features='sqrt',
+                                                    min_samples_split=5),
+                   learning_rate=0.5, n_estimators=500, random_state=42)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>t=mean/event=under_over_1_5/oob=True/stat=['form']</t>
+          <t>t=mean/event=under_over_1_5/samme/stat=['mean_statistics']</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[0.76847826 0.76931447 0.76931447 0.76931447 0.76931447]</t>
+          <t>[0.76914779 0.76457883 0.76025918 0.76457883 0.76673866]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>{'fit_time': array([0.6010108 , 0.60884881, 0.59588575, 0.59519172, 0.59531927]), 'score_time': array([0.11496067, 0.10350513, 0.11388278, 0.11431766, 0.11303544]), 'test_accuracy': array([0.76847826, 0.76931447, 0.76931447, 0.76931447, 0.76931447]), 'test_precision': array([0.76847826, 0.76931447, 0.76931447, 0.76931447, 0.76931447]), 'test_recall': array([1., 1., 1., 1., 1.]), 'test_f1': array([0.8690842, 0.8696187, 0.8696187, 0.8696187, 0.8696187]), 'test_roc_auc': array([0.57584451, 0.61794454, 0.60686264, 0.64696699, 0.62350885]), 'test_average_precision': array([0.80768026, 0.83395049, 0.83355946, 0.84055127, 0.83449239]), 'test_neg_log_loss': array([-0.53704452, -0.52638996, -0.52958788, -0.51980159, -0.52684177]), 'test_neg_brier_score': array([-0.17640917, -0.17272514, -0.1738327 , -0.17008975, -0.17315575]), 'test_f1_macro': array([0.4345421 , 0.43480935, 0.43480935, 0.43480935, 0.43480935]), 'test_f1_weighted': array([0.66787232, 0.66901025, 0.66901025, 0.66901025, 0.66901025]), 'test_balanced_accuracy': array([0.5, 0.5, 0.5, 0.5, 0.5])}</t>
+          <t>{'fit_time': array([4.87046599, 4.86511469, 4.93495631, 5.00040483, 6.77991104]), 'score_time': array([0.27093172, 0.28057528, 0.27226996, 0.35573649, 0.40513325]), 'test_accuracy': array([0.76914779, 0.76457883, 0.76025918, 0.76457883, 0.76673866]), 'test_precision': array([0.77593819, 0.77433628, 0.77369008, 0.77348066, 0.77398015]), 'test_recall': array([0.98459384, 0.98039216, 0.97335203, 0.98176718, 0.98457223]), 'test_f1': array([0.86790123, 0.86526576, 0.8621118 , 0.86526576, 0.86666667]), 'test_roc_auc': array([0.57100775, 0.56698576, 0.59479551, 0.62009693, 0.61208015]), 'test_average_precision': array([0.80418107, 0.81490306, 0.82064048, 0.84454951, 0.83753679]), 'test_neg_log_loss': array([-0.61339161, -0.6185404 , -0.62999361, -0.62119022, -0.62151356]), 'test_neg_brier_score': array([-0.21069881, -0.21340594, -0.21876579, -0.21458755, -0.21469786]), 'test_f1_macro': array([0.47668566, 0.46682091, 0.47237821, 0.46682091, 0.46781609]), 'test_f1_weighted': array([0.68811932, 0.68282449, 0.68281752, 0.68196392, 0.68317817]), 'test_balanced_accuracy': array([0.5157711 , 0.509064  , 0.5101502 , 0.50966293, 0.51106546])}</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.7691470844212358</v>
+        <v>0.7650615417836321</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8695117451727955</v>
+        <v>0.8654464506554539</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7691470844212358</v>
+        <v>0.7742863465368445</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[0.76914708 1.        ]</t>
+          <t>[0.77024401 0.77428635 1.        ]</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0.9809363610877488</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>[1. 0.]</t>
+          <t>[1.         0.98093636 0.        ]</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -859,83 +843,86 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>[1]</t>
+          <t>[0 1]</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>[[   0 1061]
- [   0 3535]]</t>
+          <t>[[  44 1020]
+ [  68 3499]]</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'precision': 0.0, 'recall': 0.0, 'f1-score': 0.0, 'support': 1061.0}</t>
+          <t>{'precision': 0.39285714285714285, 'recall': 0.041353383458646614, 'f1-score': 0.07482993197278912, 'support': 1064.0}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'precision': 0.7691470844212358, 'recall': 1.0, 'f1-score': 0.8695117451727955, 'support': 3535.0}</t>
+          <t>{'precision': 0.7742863465368445, 'recall': 0.9809363610877488, 'f1-score': 0.8654464506554539, 'support': 3567.0}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'precision': 0.3845735422106179, 'recall': 0.5, 'f1-score': 0.43475587258639775, 'support': 4596.0}</t>
+          <t>{'precision': 0.5835717446969937, 'recall': 0.5111448722731977, 'f1-score': 0.4701381913141215, 'support': 4631.0}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'precision': 0.5915872374736877, 'recall': 0.7691470844212358, 'f1-score': 0.6687824236696763, 'support': 4596.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t>{'precision': 0.6866507013813268, 'recall': 0.7650615417836321, 'f1-score': 0.6837975679350144, 'support': 4631.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" customFormat="1" s="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RandomForestClassifier(max_leaf_nodes=16, n_estimators=500, n_jobs=-1,
-                       random_state=42)</t>
+          <t>AdaBoostClassifier(estimator=DecisionTreeClassifier(criterion='entropy',
+                                                    max_depth=5,
+                                                    max_features='sqrt',
+                                                    min_samples_split=5),
+                   learning_rate=0.5, n_estimators=500, random_state=42)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>t=mean/event=under_over_1_5/oob=False/stat=['form']</t>
+          <t>t=mean/event=under_over_1_5/samme_r/stat=['mean_statistics']</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[0.76630435 0.76598639 0.76734694 0.76598639 0.76598639]</t>
+          <t>[0.71952535 0.71598272 0.74190065 0.7462203  0.72462203]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>{'fit_time': array([0.46829343, 0.47996783, 0.48185825, 0.47706985, 0.48505521]), 'score_time': array([0.11339235, 0.11304259, 0.10328293, 0.10176349, 0.10302544]), 'test_accuracy': array([0.76630435, 0.76598639, 0.76734694, 0.76598639, 0.76598639]), 'test_precision': array([0.76630435, 0.76598639, 0.76702997, 0.76598639, 0.76598639]), 'test_recall': array([1., 1., 1., 1., 1.]), 'test_f1': array([0.86769231, 0.86748844, 0.86815729, 0.86748844, 0.86748844]), 'test_roc_auc': array([0.62918522, 0.62496386, 0.58121979, 0.63651948, 0.60772853]), 'test_average_precision': array([0.83130412, 0.83526695, 0.80941715, 0.84803018, 0.83157153]), 'test_neg_log_loss': array([-0.52661665, -0.52795766, -0.53932891, -0.52717099, -0.53265226]), 'test_neg_brier_score': array([-0.17284659, -0.17361861, -0.17780701, -0.17341742, -0.17528306]), 'test_f1_macro': array([0.43384615, 0.43374422, 0.43985899, 0.43374422, 0.43374422]), 'test_f1_weighted': array([0.66491639, 0.66448435, 0.66770203, 0.66448435, 0.66448435]), 'test_balanced_accuracy': array([0.5       , 0.5       , 0.50290698, 0.5       , 0.5       ])}</t>
+          <t>{'fit_time': array([3.5214045 , 3.29636574, 3.39681959, 3.25196385, 3.26699066]), 'score_time': array([0.22914004, 0.21440005, 0.20892572, 0.21654081, 0.20588374]), 'test_accuracy': array([0.71952535, 0.71598272, 0.74190065, 0.7462203 , 0.72462203]), 'test_precision': array([0.76832151, 0.77070828, 0.78080569, 0.78795181, 0.77068558]), 'test_recall': array([0.91036415, 0.89915966, 0.92426367, 0.91725105, 0.914446  ]), 'test_f1': array([0.83333333, 0.82999354, 0.84649968, 0.84769929, 0.83643361]), 'test_roc_auc': array([0.50307729, 0.49578511, 0.58279175, 0.60227565, 0.56814755]), 'test_average_precision': array([0.78032836, 0.77425826, 0.82115392, 0.82985928, 0.80972106]), 'test_neg_log_loss': array([-0.631374  , -0.63041451, -0.62495437, -0.62086738, -0.62760955]), 'test_neg_brier_score': array([-0.21967894, -0.21920216, -0.21648863, -0.2145571 , -0.21777938]), 'test_f1_macro': array([0.4744898 , 0.48384923, 0.51816509, 0.54359074, 0.48306322]), 'test_f1_weighted': array([0.66842789, 0.67149981, 0.69545159, 0.70779622, 0.67386797]), 'test_balanced_accuracy': array([0.49508818, 0.49910813, 0.52785954, 0.54547999, 0.50182394])}</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.7663220892274211</v>
+        <v>0.7296480241848413</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8676629178863041</v>
+        <v>0.8387844450167397</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7662585034013606</v>
+        <v>0.7756608716361039</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[0.76605005 0.7662585  1.        ]</t>
+          <t>[0.77024401 0.77566087 1.        ]</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0.9130922343706196</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>[1. 1. 0.]</t>
+          <t>[1.         0.91309223 0.        ]</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -948,377 +935,1271 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>[[   1  859]
- [   0 2816]]</t>
+          <t>[[ 122  942]
+ [ 310 3257]]</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'precision': 1.0, 'recall': 0.0011627906976744186, 'f1-score': 0.0023228803716608595, 'support': 860.0}</t>
+          <t>{'precision': 0.2824074074074074, 'recall': 0.11466165413533834, 'f1-score': 0.16310160427807488, 'support': 1064.0}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'precision': 0.7662585034013606, 'recall': 1.0, 'f1-score': 0.8676629178863041, 'support': 2816.0}</t>
+          <t>{'precision': 0.7756608716361039, 'recall': 0.9130922343706196, 'f1-score': 0.8387844450167397, 'support': 3567.0}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'precision': 0.8831292517006804, 'recall': 0.5005813953488372, 'f1-score': 0.4349928991289825, 'support': 3676.0}</t>
+          <t>{'precision': 0.5290341395217556, 'recall': 0.5138769442529789, 'f1-score': 0.5009430246474073, 'support': 4631.0}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'precision': 0.8209423138134471, 'recall': 0.7663220892274211, 'f1-score': 0.6652166631902777, 'support': 3676.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>{'precision': 0.6623329325431794, 'recall': 0.7296480241848413, 'f1-score': 0.683542263512542, 'support': 4631.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" customFormat="1" s="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RandomForestClassifier(max_leaf_nodes=16, n_estimators=500, n_jobs=-1,
-                       oob_score=True, random_state=42)</t>
+          <t>AdaBoostClassifier(algorithm='SAMME',
+                   estimator=DecisionTreeClassifier(criterion='entropy',
+                                                    max_depth=5,
+                                                    max_features='sqrt',
+                                                    min_samples_split=5),
+                   learning_rate=0.5, n_estimators=500, random_state=42)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>t=mean/event=under_over_2_5/oob=True/stat=['form']</t>
+          <t>t=mean/event=under_over_1_5/samme/stat=['mean_statistics']</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[0.56362773 0.57122507 0.56552707 0.58547009 0.56009501]</t>
+          <t>[0.76914779 0.76457883 0.76025918 0.76457883 0.76673866]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>{'fit_time': array([0.80562782, 0.78863883, 0.80768132, 0.81199098, 0.80637956]), 'score_time': array([0.12794685, 0.12777901, 0.12509155, 0.127846  , 0.126158  ]), 'test_accuracy': array([0.56362773, 0.57122507, 0.56552707, 0.58547009, 0.56009501]), 'test_precision': array([0.57107438, 0.57401575, 0.5762565 , 0.58521401, 0.57255937]), 'test_recall': array([0.63336389, 0.66819432, 0.60953254, 0.68864469, 0.59670027]), 'test_f1': array([0.60060843, 0.61753494, 0.59242762, 0.63273033, 0.58438061]), 'test_roc_auc': array([0.58723456, 0.59589747, 0.59397489, 0.61194649, 0.58840577]), 'test_average_precision': array([0.60281833, 0.60030977, 0.59089795, 0.62568313, 0.59942327]), 'test_neg_log_loss': array([-0.68021799, -0.67900578, -0.68004892, -0.6748644 , -0.68092136]), 'test_neg_brier_score': array([-0.24362585, -0.24299789, -0.24349388, -0.24098565, -0.2439679 ]), 'test_f1_macro': array([0.55985419, 0.56484527, 0.56362611, 0.57849051, 0.55858788]), 'test_f1_weighted': array([0.5613249 , 0.5667467 , 0.56466548, 0.58049939, 0.55953137]), 'test_balanced_accuracy': array([0.56101692, 0.5675947 , 0.56387957, 0.58150183, 0.55870517])}</t>
+          <t>{'fit_time': array([4.84384561, 3.77059317, 2.94065809, 2.87615728, 2.95669127]), 'score_time': array([0.26623249, 0.15581632, 0.15842557, 0.16177201, 0.16112065]), 'test_accuracy': array([0.76914779, 0.76457883, 0.76025918, 0.76457883, 0.76673866]), 'test_precision': array([0.77593819, 0.77433628, 0.77369008, 0.77348066, 0.77398015]), 'test_recall': array([0.98459384, 0.98039216, 0.97335203, 0.98176718, 0.98457223]), 'test_f1': array([0.86790123, 0.86526576, 0.8621118 , 0.86526576, 0.86666667]), 'test_roc_auc': array([0.57100775, 0.56698576, 0.59479551, 0.62009693, 0.61208015]), 'test_average_precision': array([0.80418107, 0.81490306, 0.82064048, 0.84454951, 0.83753679]), 'test_neg_log_loss': array([-0.61339161, -0.6185404 , -0.62999361, -0.62119022, -0.62151356]), 'test_neg_brier_score': array([-0.21069881, -0.21340594, -0.21876579, -0.21458755, -0.21469786]), 'test_f1_macro': array([0.47668566, 0.46682091, 0.47237821, 0.46682091, 0.46781609]), 'test_f1_weighted': array([0.68811932, 0.68282449, 0.68281752, 0.68196392, 0.68317817]), 'test_balanced_accuracy': array([0.5157711 , 0.509064  , 0.5101502 , 0.50966293, 0.51106546])}</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.5691898565865704</v>
+        <v>0.2548045778449579</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6059763724808895</v>
+        <v>0.0725611394786347</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5759577278731837</v>
+        <v>0.8766233766233766</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[0.51818786 0.57595773 1.        ]</t>
+          <t>[0.77024401 0.87662338 1.        ]</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.6392961876832844</v>
+        <v>0.0378469301934398</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>[1.         0.63929619 0.        ]</t>
+          <t>[1.         0.03784693 0.        ]</t>
         </is>
       </c>
       <c r="L4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>[[1045   19]
+ [3432  135]]</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>{'precision': 0.2334152334152334, 'recall': 0.9821428571428571, 'f1-score': 0.37718823317090777, 'support': 1064.0}</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>{'precision': 0.8766233766233766, 'recall': 0.03784693019343986, 'f1-score': 0.07256113947863478, 'support': 3567.0}</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5550193050193051, 'recall': 0.5099948936681484, 'f1-score': 0.22487468632477128, 'support': 4631.0}</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7288424514725529, 'recall': 0.2548045778449579, 'f1-score': 0.14255103964891733, 'support': 4631.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" customFormat="1" s="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier(estimator=DecisionTreeClassifier(criterion='entropy',
+                                                    max_depth=5,
+                                                    max_features='sqrt',
+                                                    min_samples_split=5),
+                   learning_rate=0.5, n_estimators=500, random_state=42)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/samme_r/stat=['mean_statistics']</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>[0.71952535 0.71598272 0.74190065 0.7462203  0.72462203]</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([3.18883133, 3.20442629, 3.28602409, 3.24172187, 3.25121593]), 'score_time': array([0.20926142, 0.20932651, 0.21267605, 0.20720577, 0.20924568]), 'test_accuracy': array([0.71952535, 0.71598272, 0.74190065, 0.7462203 , 0.72462203]), 'test_precision': array([0.76832151, 0.77070828, 0.78080569, 0.78795181, 0.77068558]), 'test_recall': array([0.91036415, 0.89915966, 0.92426367, 0.91725105, 0.914446  ]), 'test_f1': array([0.83333333, 0.82999354, 0.84649968, 0.84769929, 0.83643361]), 'test_roc_auc': array([0.50307729, 0.49578511, 0.58279175, 0.60227565, 0.56814755]), 'test_average_precision': array([0.78032836, 0.77425826, 0.82115392, 0.82985928, 0.80972106]), 'test_neg_log_loss': array([-0.631374  , -0.63041451, -0.62495437, -0.62086738, -0.62760955]), 'test_neg_brier_score': array([-0.21967894, -0.21920216, -0.21648863, -0.2145571 , -0.21777938]), 'test_f1_macro': array([0.4744898 , 0.48384923, 0.51816509, 0.54359074, 0.48306322]), 'test_f1_weighted': array([0.66842789, 0.67149981, 0.69545159, 0.70779622, 0.67386797]), 'test_balanced_accuracy': array([0.49508818, 0.49910813, 0.52785954, 0.54547999, 0.50182394])}</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2647376376592528</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1022936989190614</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.8584070796460177</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>[0.77024401 0.85840708 1.        ]</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0543874404261284</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>[1.         0.05438744 0.        ]</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>[[1032   32]
+ [3373  194]]</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>{'precision': 0.23427922814982974, 'recall': 0.9699248120300752, 'f1-score': 0.37739989029072957, 'support': 1064.0}</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>{'precision': 0.8584070796460177, 'recall': 0.0543874404261284, 'f1-score': 0.10229369891906143, 'support': 3567.0}</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5463431538979238, 'recall': 0.5121561262281018, 'f1-score': 0.2398467946048955, 'support': 4631.0}</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7150099658494417, 'recall': 0.26473763765925284, 'f1-score': 0.16550099488525769, 'support': 4631.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" customFormat="1" s="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier(algorithm='SAMME',
+                   estimator=DecisionTreeClassifier(criterion='entropy',
+                                                    max_depth=5,
+                                                    max_features='sqrt',
+                                                    min_samples_split=5),
+                   learning_rate=0.5, n_estimators=500, random_state=42)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/samme/stat=['mean_statistics']</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>[0.76914779 0.76457883 0.76025918 0.76457883 0.76673866]</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([2.86749315, 2.83700228, 2.90187645, 3.28211403, 3.62887788]), 'score_time': array([0.15946817, 0.15800977, 0.16106296, 0.18194151, 0.19150996]), 'test_accuracy': array([0.76914779, 0.76457883, 0.76025918, 0.76457883, 0.76673866]), 'test_precision': array([0.77593819, 0.77433628, 0.77369008, 0.77348066, 0.77398015]), 'test_recall': array([0.98459384, 0.98039216, 0.97335203, 0.98176718, 0.98457223]), 'test_f1': array([0.86790123, 0.86526576, 0.8621118 , 0.86526576, 0.86666667]), 'test_roc_auc': array([0.57100775, 0.56698576, 0.59479551, 0.62009693, 0.61208015]), 'test_average_precision': array([0.80418107, 0.81490306, 0.82064048, 0.84454951, 0.83753679]), 'test_neg_log_loss': array([-0.61339161, -0.6185404 , -0.62999361, -0.62119022, -0.62151356]), 'test_neg_brier_score': array([-0.21069881, -0.21340594, -0.21876579, -0.21458755, -0.21469786]), 'test_f1_macro': array([0.47668566, 0.46682091, 0.47237821, 0.46682091, 0.46781609]), 'test_f1_weighted': array([0.68811932, 0.68282449, 0.68281752, 0.68196392, 0.68317817]), 'test_balanced_accuracy': array([0.5157711 , 0.509064  , 0.5101502 , 0.50966293, 0.51106546])}</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4806737205787087</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5510546947918611</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8245810055865922</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>[0.77024401 0.82458101 1.        ]</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.4137931034482758</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>[1.        0.4137931 0.       ]</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>[[ 750  314]
+ [2091 1476]]</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>{'precision': 0.26399155227032733, 'recall': 0.7048872180451128, 'f1-score': 0.38412291933418696, 'support': 1064.0}</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>{'precision': 0.8245810055865922, 'recall': 0.41379310344827586, 'f1-score': 0.5510546947918611, 'support': 3567.0}</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5442862789284597, 'recall': 0.5593401607466943, 'f1-score': 0.467588807063024, 'support': 4631.0}</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6957822195083141, 'recall': 0.4806737205787087, 'f1-score': 0.5127011190874851, 'support': 4631.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" customFormat="1" s="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier(estimator=DecisionTreeClassifier(criterion='entropy',
+                                                    max_depth=5,
+                                                    max_features='sqrt',
+                                                    min_samples_split=5),
+                   learning_rate=0.5, n_estimators=500, random_state=42)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/samme_r/stat=['mean_statistics']</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>[0.71952535 0.71598272 0.74190065 0.7462203  0.72462203]</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([3.47788954, 4.02875924, 3.64563131, 3.60807896, 3.77462387]), 'score_time': array([0.24483037, 0.23672342, 0.23043442, 0.23118305, 0.23464704]), 'test_accuracy': array([0.71952535, 0.71598272, 0.74190065, 0.7462203 , 0.72462203]), 'test_precision': array([0.76832151, 0.77070828, 0.78080569, 0.78795181, 0.77068558]), 'test_recall': array([0.91036415, 0.89915966, 0.92426367, 0.91725105, 0.914446  ]), 'test_f1': array([0.83333333, 0.82999354, 0.84649968, 0.84769929, 0.83643361]), 'test_roc_auc': array([0.50307729, 0.49578511, 0.58279175, 0.60227565, 0.56814755]), 'test_average_precision': array([0.78032836, 0.77425826, 0.82115392, 0.82985928, 0.80972106]), 'test_neg_log_loss': array([-0.631374  , -0.63041451, -0.62495437, -0.62086738, -0.62760955]), 'test_neg_brier_score': array([-0.21967894, -0.21920216, -0.21648863, -0.2145571 , -0.21777938]), 'test_f1_macro': array([0.4744898 , 0.48384923, 0.51816509, 0.54359074, 0.48306322]), 'test_f1_weighted': array([0.66842789, 0.67149981, 0.69545159, 0.70779622, 0.67386797]), 'test_balanced_accuracy': array([0.49508818, 0.49910813, 0.52785954, 0.54547999, 0.50182394])}</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.4748434463398834</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5568513119533528</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7954190525767829</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>[0.77024401 0.79541905 1.        ]</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.4283711802635268</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>[1.         0.42837118 0.        ]</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>[[ 671  393]
+ [2039 1528]]</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>{'precision': 0.24760147601476015, 'recall': 0.6306390977443609, 'f1-score': 0.3555908850026497, 'support': 1064.0}</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7954190525767829, 'recall': 0.4283711802635268, 'f1-score': 0.5568513119533528, 'support': 3567.0}</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5215102642957715, 'recall': 0.5295051390039438, 'f1-score': 0.45622109847800124, 'support': 4631.0}</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6695546817147678, 'recall': 0.4748434463398834, 'f1-score': 0.510610522863405, 'support': 4631.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" customFormat="1" s="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier(algorithm='SAMME',
+                   estimator=DecisionTreeClassifier(criterion='entropy',
+                                                    max_depth=5,
+                                                    max_features='sqrt',
+                                                    min_samples_split=5),
+                   learning_rate=0.5, n_estimators=1000, random_state=42)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/samme/stat=['mean_statistics']</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>[0.7626753  0.76133909 0.7537797  0.75809935 0.76457883]</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([6.10459805, 5.88559365, 5.96499062, 6.02640605, 6.10518336]), 'score_time': array([0.38443255, 0.31256151, 0.31308556, 0.31377935, 0.32120657]), 'test_accuracy': array([0.7626753 , 0.76133909, 0.7537797 , 0.75809935, 0.76457883]), 'test_precision': array([0.77202643, 0.77727784, 0.77216611, 0.77076412, 0.77469478]), 'test_recall': array([0.98179272, 0.96778711, 0.96493689, 0.97615708, 0.97896213]), 'test_f1': array([0.86436498, 0.8621335 , 0.85785536, 0.86138614, 0.86493185]), 'test_roc_auc': array([0.55226786, 0.53560198, 0.58261726, 0.6118431 , 0.60059657]), 'test_average_precision': array([0.79615998, 0.80049944, 0.81522732, 0.83718039, 0.8319441 ]), 'test_neg_log_loss': array([-0.64499171, -0.6478679 , -0.65088803, -0.64429144, -0.64662793]), 'test_neg_brier_score': array([-0.22614698, -0.22757643, -0.22899803, -0.22577723, -0.22693094]), 'test_f1_macro': array([0.45804456, 0.48729165, 0.46925026, 0.4561168 , 0.47448273]), 'test_f1_weighted': array([0.67764168, 0.69049965, 0.67908023, 0.67494474, 0.68530839]), 'test_balanced_accuracy': array([0.50498087, 0.51691243, 0.50594262, 0.50216305, 0.51295524])}</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2537248974303606</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.0694668820678513</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8775510204081632</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>[0.77024401 0.87755102 1.        ]</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.0361648444070647</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>[1.         0.03616484 0.        ]</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>[[1046   18]
+ [3438  129]]</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>{'precision': 0.23327386262265834, 'recall': 0.9830827067669173, 'f1-score': 0.37707281903388606, 'support': 1064.0}</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>{'precision': 0.8775510204081632, 'recall': 0.03616484440706476, 'f1-score': 0.06946688206785137, 'support': 3567.0}</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5554124415154108, 'recall': 0.509623775586991, 'f1-score': 0.22326985055086873, 'support': 4631.0}</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7295244827524134, 'recall': 0.25372489743036064, 'f1-score': 0.14014118933018369, 'support': 4631.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" customFormat="1" s="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier(estimator=DecisionTreeClassifier(criterion='entropy',
+                                                    max_depth=5,
+                                                    max_features='sqrt',
+                                                    min_samples_split=5),
+                   learning_rate=0.5, n_estimators=1000, random_state=42)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/samme_r/stat=['mean_statistics']</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>[0.73678533 0.73434125 0.73866091 0.73758099 0.73758099]</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([6.37989569, 6.56236458, 6.55527663, 7.196872  , 6.39235067]), 'score_time': array([0.41284037, 0.42791104, 0.5244503 , 0.43959045, 0.41503787]), 'test_accuracy': array([0.73678533, 0.73434125, 0.73866091, 0.73758099, 0.73758099]), 'test_precision': array([0.77011494, 0.77400468, 0.7754386 , 0.77325581, 0.77011494]), 'test_recall': array([0.93837535, 0.92577031, 0.92987377, 0.93267882, 0.93969144]), 'test_f1': array([0.8459596 , 0.84311224, 0.84566327, 0.84551812, 0.846494  ]), 'test_roc_auc': array([0.54075433, 0.50946699, 0.58643963, 0.57951261, 0.56870724]), 'test_average_precision': array([0.79418781, 0.77705042, 0.82497842, 0.82020478, 0.81577297]), 'test_neg_log_loss': array([-0.63009441, -0.63328642, -0.62952252, -0.62842447, -0.63041083]), 'test_neg_brier_score': array([-0.21891372, -0.2204576 , -0.21864225, -0.21811011, -0.21906599]), 'test_f1_macro': array([0.47112795, 0.48845753, 0.49677529, 0.48727519, 0.47157414]), 'test_f1_weighted': array([0.67370686, 0.68072175, 0.68515973, 0.6807109 , 0.67401467]), 'test_balanced_accuracy': array([0.49970411, 0.50769647, 0.51423266, 0.50859293, 0.50036215])}</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2988555387605269</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1940928270042194</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.8463203463203464</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>[0.77024401 0.84632035 1.        ]</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.1096159237454443</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>[1.         0.10961592 0.        ]</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>[[ 993   71]
+ [3176  391]]</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>{'precision': 0.2381866154953226, 'recall': 0.9332706766917294, 'f1-score': 0.37951461876552645, 'support': 1064.0}</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>{'precision': 0.8463203463203464, 'recall': 0.10961592374544435, 'f1-score': 0.1940928270042194, 'support': 3567.0}</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5422534809078345, 'recall': 0.5214433002185869, 'f1-score': 0.28680372288487294, 'support': 4631.0}</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7065979775883607, 'recall': 0.2988555387605269, 'f1-score': 0.23669459475071708, 'support': 4631.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" customFormat="1" s="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier(algorithm='SAMME',
+                   estimator=DecisionTreeClassifier(criterion='entropy',
+                                                    max_depth=5,
+                                                    max_features='sqrt',
+                                                    min_samples_split=5),
+                   learning_rate=0.5, n_estimators=1000, random_state=42)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/samme/stat=['mean_statistics']</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>[0.7626753  0.76133909 0.7537797  0.75809935 0.76457883]</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([6.24789834, 5.91122866, 5.8037231 , 5.79604125, 5.79910803]), 'score_time': array([0.32171702, 0.31229043, 0.31910324, 0.30957508, 0.31641126]), 'test_accuracy': array([0.7626753 , 0.76133909, 0.7537797 , 0.75809935, 0.76457883]), 'test_precision': array([0.77202643, 0.77727784, 0.77216611, 0.77076412, 0.77469478]), 'test_recall': array([0.98179272, 0.96778711, 0.96493689, 0.97615708, 0.97896213]), 'test_f1': array([0.86436498, 0.8621335 , 0.85785536, 0.86138614, 0.86493185]), 'test_roc_auc': array([0.55226786, 0.53560198, 0.58261726, 0.6118431 , 0.60059657]), 'test_average_precision': array([0.79615998, 0.80049944, 0.81522732, 0.83718039, 0.8319441 ]), 'test_neg_log_loss': array([-0.64499171, -0.6478679 , -0.65088803, -0.64429144, -0.64662793]), 'test_neg_brier_score': array([-0.22614698, -0.22757643, -0.22899803, -0.22577723, -0.22693094]), 'test_f1_macro': array([0.45804456, 0.48729165, 0.46925026, 0.4561168 , 0.47448273]), 'test_f1_weighted': array([0.67764168, 0.69049965, 0.67908023, 0.67494474, 0.68530839]), 'test_balanced_accuracy': array([0.50498087, 0.51691243, 0.50594262, 0.50216305, 0.51295524])}</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0.7691643273591017</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8692674575027516</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.7709327548806941</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>[0.77024401 0.77093275 1.        ]</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.9963554807961872</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>[1.         0.99635548 0.        ]</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>[[   8 1056]
+ [  13 3554]]</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>{'precision': 0.38095238095238093, 'recall': 0.007518796992481203, 'f1-score': 0.014746543778801843, 'support': 1064.0}</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7709327548806941, 'recall': 0.9963554807961873, 'f1-score': 0.8692674575027516, 'support': 3567.0}</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5759425679165375, 'recall': 0.5019371388943342, 'f1-score': 0.4420070006407767, 'support': 4631.0}</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6813324271200106, 'recall': 0.7691643273591017, 'f1-score': 0.6729361570919801, 'support': 4631.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" customFormat="1" s="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier(estimator=DecisionTreeClassifier(criterion='entropy',
+                                                    max_depth=5,
+                                                    max_features='sqrt',
+                                                    min_samples_split=5),
+                   learning_rate=0.5, n_estimators=1000, random_state=42)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/samme_r/stat=['mean_statistics']</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>[0.73678533 0.73434125 0.73866091 0.73758099 0.73758099]</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([6.74290156, 6.4620595 , 6.44973636, 6.54752564, 6.83197093]), 'score_time': array([0.40999842, 0.4021275 , 0.4084301 , 0.49883628, 0.43063879]), 'test_accuracy': array([0.73678533, 0.73434125, 0.73866091, 0.73758099, 0.73758099]), 'test_precision': array([0.77011494, 0.77400468, 0.7754386 , 0.77325581, 0.77011494]), 'test_recall': array([0.93837535, 0.92577031, 0.92987377, 0.93267882, 0.93969144]), 'test_f1': array([0.8459596 , 0.84311224, 0.84566327, 0.84551812, 0.846494  ]), 'test_roc_auc': array([0.54075433, 0.50946699, 0.58643963, 0.57951261, 0.56870724]), 'test_average_precision': array([0.79418781, 0.77705042, 0.82497842, 0.82020478, 0.81577297]), 'test_neg_log_loss': array([-0.63009441, -0.63328642, -0.62952252, -0.62842447, -0.63041083]), 'test_neg_brier_score': array([-0.21891372, -0.2204576 , -0.21864225, -0.21811011, -0.21906599]), 'test_f1_macro': array([0.47112795, 0.48845753, 0.49677529, 0.48727519, 0.47157414]), 'test_f1_weighted': array([0.67370686, 0.68072175, 0.68515973, 0.6807109 , 0.67401467]), 'test_balanced_accuracy': array([0.49970411, 0.50769647, 0.51423266, 0.50859293, 0.50036215])}</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.7620384366227597</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8641853586393887</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.7710578403342864</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>[0.77024401 0.77105784 1.        ]</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.9828987945051864</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>[1.         0.98289879 0.        ]</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>[[  23 1041]
+ [  61 3506]]</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>{'precision': 0.27380952380952384, 'recall': 0.021616541353383457, 'f1-score': 0.04006968641114982, 'support': 1064.0}</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7710578403342864, 'recall': 0.9828987945051865, 'f1-score': 0.8641853586393887, 'support': 3567.0}</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5224336820719051, 'recall': 0.502257667929285, 'f1-score': 0.4521275225252693, 'support': 4631.0}</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6568120599882818, 'recall': 0.7620384366227597, 'f1-score': 0.6748398446573446, 'support': 4631.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" customFormat="1" s="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier(algorithm='SAMME',
+                   estimator=DecisionTreeClassifier(criterion='entropy',
+                                                    max_depth=5,
+                                                    max_features='sqrt',
+                                                    min_samples_split=5),
+                   learning_rate=0.5, n_estimators=1000, random_state=42)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/samme/stat=['mean_statistics']</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>[0.64611072 0.66713385 0.62578837 0.64260687 0.67812062]</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([12.55606723, 13.80557728, 12.93220282, 13.25892234, 12.15950751]), 'score_time': array([0.57740664, 0.50563622, 0.5969243 , 0.46098065, 0.45408511]), 'test_accuracy': array([0.64611072, 0.66713385, 0.62578837, 0.64260687, 0.67812062]), 'test_precision': array([0.6580938 , 0.68642746, 0.63664122, 0.64688857, 0.69781931]), 'test_recall': array([0.6092437 , 0.6162465 , 0.58485273, 0.62692847, 0.628331  ]), 'test_f1': array([0.63272727, 0.64944649, 0.60964912, 0.63675214, 0.66125461]), 'test_roc_auc': array([0.7114129 , 0.72724237, 0.67375688, 0.70252729, 0.73213158]), 'test_average_precision': array([0.71414216, 0.74218786, 0.66766723, 0.71341228, 0.73983288]), 'test_neg_log_loss': array([-0.67154788, -0.66916511, -0.67722401, -0.67145078, -0.67068949]), 'test_neg_brier_score': array([-0.23928092, -0.23812582, -0.2420925 , -0.23923922, -0.23885801]), 'test_f1_macro': array([0.64564017, 0.66628429, 0.62514758, 0.642514  , 0.67732069]), 'test_f1_weighted': array([0.64563113, 0.66627249, 0.62515844, 0.64251804, 0.67732069]), 'test_balanced_accuracy': array([0.64613658, 0.66716953, 0.6257597 , 0.64259589, 0.67812062])}</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.6519484160358845</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.6378882893393613</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.664741641337386</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>[0.5        0.66474164 1.        ]</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.6131202691337259</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>[1.         0.61312027 0.        ]</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
         <v>0</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>[0 1]</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>[[2505 2568]
- [1968 3488]]</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>{'precision': 0.5600268276324615, 'recall': 0.4937906564163217, 'f1-score': 0.5248271527341295, 'support': 5073.0}</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>{'precision': 0.5759577278731837, 'recall': 0.6392961876832844, 'f1-score': 0.6059763724808895, 'support': 5456.0}</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>{'precision': 0.5679922777528226, 'recall': 0.5665434220498031, 'f1-score': 0.5654017626075095, 'support': 10529.0}</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>{'precision': 0.5682820267694526, 'recall': 0.5691898565865704, 'f1-score': 0.5668776934253938, 'support': 10529.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>RandomForestClassifier(max_leaf_nodes=16, n_estimators=500, n_jobs=-1,
-                       random_state=42)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>t=mean/event=under_over_2_5/oob=False/stat=['form']</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>[0.57210682 0.53649852 0.57151335 0.57541568 0.58491686]</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>{'fit_time': array([0.53788447, 0.54287815, 0.54045486, 0.53849745, 0.5384326 ]), 'score_time': array([0.12569594, 0.12595177, 0.12585044, 0.12599635, 0.11523724]), 'test_accuracy': array([0.57210682, 0.53649852, 0.57151335, 0.57541568, 0.58491686]), 'test_precision': array([0.57669903, 0.55396476, 0.57905337, 0.57677903, 0.59013092]), 'test_recall': array([0.67576792, 0.57224118, 0.65415245, 0.70079636, 0.66742597]), 'test_f1': array([0.62231535, 0.56295467, 0.61431624, 0.63276836, 0.62640299]), 'test_roc_auc': array([0.60189365, 0.55132298, 0.59820826, 0.60733753, 0.60644398]), 'test_average_precision': array([0.60710904, 0.57314774, 0.60847721, 0.61742179, 0.60936443]), 'test_neg_log_loss': array([-0.67887486, -0.69033175, -0.67735389, -0.67594733, -0.67608889]), 'test_neg_brier_score': array([-0.24291118, -0.24860135, -0.24221314, -0.24150444, -0.24156545]), 'test_f1_macro': array([0.56440887, 0.53479382, 0.56617014, 0.56480079, 0.57973456]), 'test_f1_weighted': array([0.56691758, 0.53601385, 0.56825599, 0.56778749, 0.58172989]), 'test_balanced_accuracy': array([0.5674125 , 0.5348799 , 0.56777101, 0.56965284, 0.58123159])}</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0.5680873797934227</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.6124014489665459</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.5757211538461539</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>[0.52166686 0.57572115 1.        ]</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>0.6540737369139736</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>[1.         0.65407374 0.        ]</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>[[2464 1103]
+ [1380 2187]]</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6409989594172737, 'recall': 0.6907765629380431, 'f1-score': 0.6649574956146269, 'support': 3567.0}</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>{'precision': 0.664741641337386, 'recall': 0.6131202691337259, 'f1-score': 0.6378882893393613, 'support': 3567.0}</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6528703003773298, 'recall': 0.6519484160358845, 'f1-score': 0.651422892476994, 'support': 7134.0}</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6528703003773298, 'recall': 0.6519484160358845, 'f1-score': 0.651422892476994, 'support': 7134.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" customFormat="1" s="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier(estimator=DecisionTreeClassifier(criterion='entropy',
+                                                    max_depth=5,
+                                                    max_features='sqrt',
+                                                    min_samples_split=5),
+                   learning_rate=0.5, n_estimators=1000, random_state=42)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/samme_r/stat=['mean_statistics']</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>[0.70847933 0.71548704 0.7042747  0.73160477 0.71809257]</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([23.836411  , 33.99231005, 18.48455405, 14.89143991, 13.46617556]), 'score_time': array([1.73670173, 1.3645525 , 0.60578847, 0.65846586, 0.61558938]), 'test_accuracy': array([0.70847933, 0.71548704, 0.7042747 , 0.73160477, 0.71809257]), 'test_precision': array([0.70926966, 0.73053892, 0.71179039, 0.72664835, 0.72968981]), 'test_recall': array([0.70728291, 0.68347339, 0.6858345 , 0.74193548, 0.69284712]), 'test_f1': array([0.70827489, 0.70622287, 0.69857143, 0.73421235, 0.71079137]), 'test_roc_auc': array([0.77153189, 0.78589697, 0.76562911, 0.79776932, 0.7829726 ]), 'test_average_precision': array([0.76692541, 0.77429512, 0.76077774, 0.78577963, 0.76996236]), 'test_neg_log_loss': array([-0.66381708, -0.66106446, -0.66296015, -0.65925118, -0.66269512]), 'test_neg_brier_score': array([-0.23540092, -0.2340503 , -0.23499315, -0.23314132, -0.23484522]), 'test_f1_macro': array([0.70847918, 0.71520382, 0.7041688 , 0.73157893, 0.71791278]), 'test_f1_weighted': array([0.70847904, 0.71519753, 0.70417272, 0.73157708, 0.71791278]), 'test_balanced_accuracy': array([0.70848017, 0.71550949, 0.70426179, 0.731612  , 0.71809257])}</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.7155873282870759</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.7117488279585168</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.7214861751152074</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>[0.5        0.72148618 1.        ]</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0.7022708158116064</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>[1.         0.70227082 0.        ]</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
         <v>0</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>[0 1]</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>[[1911 2118]
- [1520 2874]]</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>{'precision': 0.5569804721655494, 'recall': 0.4743112434847357, 'f1-score': 0.5123324396782842, 'support': 4029.0}</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>{'precision': 0.5757211538461539, 'recall': 0.6540737369139736, 'f1-score': 0.6124014489665459, 'support': 4394.0}</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>{'precision': 0.5663508130058517, 'recall': 0.5641924901993547, 'f1-score': 0.5623669443224151, 'support': 8423.0}</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>{'precision': 0.566756864817167, 'recall': 0.5680873797934227, 'f1-score': 0.5645351259910732, 'support': 8423.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>RandomForestClassifier(max_leaf_nodes=16, n_estimators=500, n_jobs=-1,
-                       oob_score=True, random_state=42)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>t=mean/event=under_over_3_5/oob=True/stat=['form']</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>[0.68266085 0.68047983 0.67720829 0.68558952 0.67467249]</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>{'fit_time': array([0.60779905, 0.61251521, 0.61202359, 0.61355281, 0.61536193]), 'score_time': array([0.12525892, 0.12648654, 0.12496734, 0.12537932, 0.1155746 ]), 'test_accuracy': array([0.68266085, 0.68047983, 0.67720829, 0.68558952, 0.67467249]), 'test_precision': array([0.44444444, 0.45238095, 0.36      , 0.5       , 0.38636364]), 'test_recall': array([0.02768166, 0.06574394, 0.03114187, 0.03819444, 0.05902778]), 'test_f1': array([0.05211726, 0.11480363, 0.05732484, 0.07096774, 0.10240964]), 'test_roc_auc': array([0.65331805, 0.6143246 , 0.60137637, 0.65070993, 0.61077937]), 'test_average_precision': array([0.43935169, 0.41410866, 0.39915676, 0.4465359 , 0.41776876]), 'test_neg_log_loss': array([-0.59443892, -0.60632565, -0.61102918, -0.59241915, -0.60438646]), 'test_neg_brier_score': array([-0.20342469, -0.20858076, -0.21056825, -0.20246929, -0.2075131 ]), 'test_f1_macro': array([0.43077376, 0.45993009, 0.431294  , 0.44087152, 0.45187149]), 'test_f1_weighted': array([0.57075691, 0.58751774, 0.56954432, 0.57817205, 0.5815844 ]), 'test_balanced_accuracy': array([0.50587905, 0.51455987, 0.50283208, 0.51033926, 0.50801707])}</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0.6801221907047785</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.0803011292346298</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.423841059602649</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>[0.31485926 0.42384106 1.        ]</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>0.0443520443520443</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>[1.         0.04435204 0.        ]</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>[[2600  967]
+ [1062 2505]]</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>{'precision': 0.70999453850355, 'recall': 0.7289038407625456, 'f1-score': 0.7193249412090192, 'support': 3567.0}</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7214861751152074, 'recall': 0.7022708158116064, 'f1-score': 0.7117488279585168, 'support': 3567.0}</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7157403568093788, 'recall': 0.7155873282870759, 'f1-score': 0.715536884583768, 'support': 7134.0}</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7157403568093786, 'recall': 0.7155873282870759, 'f1-score': 0.7155368845837681, 'support': 7134.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" customFormat="1" s="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier(algorithm='SAMME',
+                   estimator=DecisionTreeClassifier(criterion='entropy',
+                                                    max_depth=5,
+                                                    max_features='log2',
+                                                    min_samples_split=5),
+                   learning_rate=0.5, n_estimators=1000, random_state=42)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_3_5/samme/stat=['mean_statistics']</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>[0.63924051 0.62579114 0.6210443  0.62737342 0.6289557 ]</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([13.89026546, 16.76988196, 11.92416215,  8.05651593,  8.20500445]), 'score_time': array([0.56612229, 0.53921413, 0.32809305, 0.34982896, 0.34524798]), 'test_accuracy': array([0.63924051, 0.62579114, 0.6210443 , 0.62737342, 0.6289557 ]), 'test_precision': array([0.63707165, 0.62519685, 0.61679389, 0.62178517, 0.62635659]), 'test_recall': array([0.6471519 , 0.62816456, 0.63924051, 0.65031646, 0.63924051]), 'test_f1': array([0.64207221, 0.62667719, 0.62781663, 0.63573086, 0.63273297]), 'test_roc_auc': array([0.70361946, 0.66644218, 0.66687029, 0.67913671, 0.68220988]), 'test_average_precision': array([0.70656137, 0.64347435, 0.6509466 , 0.67997708, 0.66482026]), 'test_neg_log_loss': array([-0.67197115, -0.67483606, -0.67540659, -0.67496895, -0.67319605]), 'test_neg_brier_score': array([-0.23948123, -0.24092637, -0.2411771 , -0.24096505, -0.24009894]), 'test_f1_macro': array([0.63921792, 0.62578903, 0.62091879, 0.62717717, 0.62891644]), 'test_f1_weighted': array([0.63921792, 0.62578903, 0.62091879, 0.62717717, 0.62891644]), 'test_balanced_accuracy': array([0.63924051, 0.62579114, 0.6210443 , 0.62737342, 0.6289557 ])}</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.6284810126582279</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.6330103157236636</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.6253860407659049</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>[0.5        0.62538604 1.        ]</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0.6408227848101266</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>[1.         0.64082278 0.        ]</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
         <v>0</v>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>[0 1]</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>[[3053   87]
- [1379   64]]</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>{'precision': 0.6888537906137184, 'recall': 0.9722929936305732, 'f1-score': 0.806391970417327, 'support': 3140.0}</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>{'precision': 0.423841059602649, 'recall': 0.04435204435204435, 'f1-score': 0.08030112923462986, 'support': 1443.0}</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>{'precision': 0.5563474251081837, 'recall': 0.5083225189913088, 'f1-score': 0.44334654982597843, 'support': 4583.0}</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>{'precision': 0.6054120775766307, 'recall': 0.6801221907047785, 'f1-score': 0.5777755436604796, 'support': 4583.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RandomForestClassifier(max_leaf_nodes=16, n_estimators=500, n_jobs=-1,
-                       random_state=42)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>t=mean/event=under_over_3_5/oob=False/stat=['form']</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>[0.69891008 0.68485675 0.69167804 0.6957708  0.68076398]</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>{'fit_time': array([0.48497486, 0.47509408, 0.47912717, 0.47777319, 0.47893715]), 'score_time': array([0.11500525, 0.10252309, 0.10186505, 0.10305333, 0.1125958 ]), 'test_accuracy': array([0.69891008, 0.68485675, 0.69167804, 0.6957708 , 0.68076398]), 'test_precision': array([0.68421053, 0.42307692, 0.53333333, 0.5625    , 0.41025641]), 'test_recall': array([0.05701754, 0.04845815, 0.03524229, 0.07929515, 0.07048458]), 'test_f1': array([0.10526316, 0.08695652, 0.0661157 , 0.13899614, 0.12030075]), 'test_roc_auc': array([0.66067714, 0.62494123, 0.6368773 , 0.63198447, 0.61777611]), 'test_average_precision': array([0.47057614, 0.42301281, 0.42130117, 0.43873925, 0.41519426]), 'test_neg_log_loss': array([-0.58615778, -0.59884944, -0.59549464, -0.5974765 , -0.60081406]), 'test_neg_brier_score': array([-0.19955615, -0.20517799, -0.20383305, -0.20461209, -0.20599043]), 'test_f1_macro': array([0.46213199, 0.44825979, 0.44073759, 0.47712027, 0.46265038]), 'test_f1_weighted': array([0.59729484, 0.58578178, 0.583329  , 0.60581964, 0.59295808]), 'test_balanced_accuracy': array([0.52257992, 0.50940694, 0.51070415, 0.52581358, 0.51251502])}</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0.6903982542280415</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0.10418310970797158</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.5038167938931297</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>[0.30987452 0.50381679 1.        ]</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0.058098591549295774</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>[1.         0.05809859 0.        ]</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>[[1947 1213]
+ [1135 2025]]</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6317326411421155, 'recall': 0.6161392405063291, 'f1-score': 0.6238385132970202, 'support': 3160.0}</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6253860407659049, 'recall': 0.6408227848101266, 'f1-score': 0.6330103157236636, 'support': 3160.0}</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6285593409540102, 'recall': 0.6284810126582279, 'f1-score': 0.6284244145103419, 'support': 6320.0}</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6285593409540101, 'recall': 0.6284810126582279, 'f1-score': 0.6284244145103419, 'support': 6320.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" customFormat="1" s="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier(estimator=DecisionTreeClassifier(criterion='entropy',
+                                                    max_depth=5,
+                                                    max_features='log2',
+                                                    min_samples_split=5),
+                   learning_rate=0.5, n_estimators=1000, random_state=42)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_3_5/samme_r/stat=['mean_statistics']</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>[0.6835443  0.68670886 0.65585443 0.68037975 0.66218354]</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([9.07194471, 9.05125642, 9.05998015, 9.87525678, 9.12331104]), 'score_time': array([0.4681735 , 0.476161  , 0.46708965, 0.49788642, 0.6045053 ]), 'test_accuracy': array([0.6835443 , 0.68670886, 0.65585443, 0.68037975, 0.66218354]), 'test_precision': array([0.68068536, 0.68322981, 0.65366615, 0.66814159, 0.65648855]), 'test_recall': array([0.6914557 , 0.69620253, 0.66297468, 0.71677215, 0.68037975]), 'test_f1': array([0.68602826, 0.68965517, 0.65828751, 0.69160305, 0.66822067]), 'test_roc_auc': array([0.74272703, 0.73750701, 0.7061143 , 0.73543653, 0.72952301]), 'test_average_precision': array([0.73839195, 0.72871772, 0.68607256, 0.72826128, 0.7217206 ]), 'test_neg_log_loss': array([-0.66604632, -0.66757386, -0.67026031, -0.66777526, -0.667396  ]), 'test_neg_brier_score': array([-0.23651109, -0.23727213, -0.23860793, -0.23737058, -0.23719152]), 'test_f1_macro': array([0.6835245 , 0.68668062, 0.65583698, 0.67995588, 0.66207166]), 'test_f1_weighted': array([0.6835245 , 0.68668062, 0.65583698, 0.67995588, 0.66207166]), 'test_balanced_accuracy': array([0.6835443 , 0.68670886, 0.65585443, 0.68037975, 0.66218354])}</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.6737341772151899</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.678816199376947</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.6684049079754601</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>[0.5        0.66840491 1.        ]</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0.6895569620253165</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>[1.         0.68955696 0.        ]</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>[[2079 1081]
+ [ 981 2179]]</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6794117647058824, 'recall': 0.6579113924050632, 'f1-score': 0.6684887459807074, 'support': 3160.0}</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6684049079754601, 'recall': 0.6895569620253165, 'f1-score': 0.678816199376947, 'support': 3160.0}</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6739083363406713, 'recall': 0.6737341772151899, 'f1-score': 0.6736524726788272, 'support': 6320.0}</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6739083363406712, 'recall': 0.6737341772151899, 'f1-score': 0.6736524726788272, 'support': 6320.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" customFormat="1" s="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier(algorithm='SAMME',
+                   estimator=DecisionTreeClassifier(criterion='log_loss',
+                                                    max_depth=5,
+                                                    max_features='log2',
+                                                    min_samples_leaf=2,
+                                                    min_samples_split=5),
+                   learning_rate=0.5, n_estimators=1000, random_state=42)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_2_5/samme/stat=['mean_statistics']</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>[0.58604432 0.57897218 0.55141509 0.55990566 0.56886792]</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([10.91776609, 10.86200333, 11.44152188, 11.60160184, 11.17653108]), 'score_time': array([0.44626832, 0.43985033, 0.44208455, 0.47658682, 0.4502852 ]), 'test_accuracy': array([0.58604432, 0.57897218, 0.55141509, 0.55990566, 0.56886792]), 'test_precision': array([0.59395973, 0.5826087 , 0.5659051 , 0.57118644, 0.58202443]), 'test_recall': array([0.64246824, 0.66878403, 0.5849228 , 0.61217075, 0.60526316]), 'test_f1': array([0.61726242, 0.62272919, 0.57525681, 0.59096887, 0.59341637]), 'test_roc_auc': array([0.61140909, 0.59416816, 0.57004561, 0.58210664, 0.59236332]), 'test_average_precision': array([0.61386599, 0.61214816, 0.5822541 , 0.59182694, 0.60101369]), 'test_neg_log_loss': array([-0.68054511, -0.68375346, -0.68662909, -0.68550605, -0.68495425]), 'test_neg_brier_score': array([-0.24372722, -0.24532131, -0.24674104, -0.24621534, -0.24582912]), 'test_f1_macro': array([0.58327187, 0.57323126, 0.54999722, 0.55735274, 0.56729051]), 'test_f1_weighted': array([0.584602  , 0.57516824, 0.55097424, 0.55865298, 0.56832569]), 'test_balanced_accuracy': array([0.58374639, 0.57531449, 0.55006689, 0.55780275, 0.56736635])}</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.5690435766836446</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.60022749146907</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5792940381692282</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>[0.51952462 0.57929404 1.        ]</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0.6227305737109659</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>[1.         0.62273057 0.        ]</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>[[2603 2491]
+ [2078 3430]]</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5560777611621448, 'recall': 0.510993325480958, 'f1-score': 0.5325831202046036, 'support': 5094.0}</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5792940381692282, 'recall': 0.6227305737109659, 'f1-score': 0.60022749146907, 'support': 5508.0}</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5676858996656865, 'recall': 0.5668619495959619, 'f1-score': 0.5664053058368368, 'support': 10602.0}</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5681391886055531, 'recall': 0.5690435766836446, 'f1-score': 0.567726036345396, 'support': 10602.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" customFormat="1" s="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier(estimator=DecisionTreeClassifier(criterion='log_loss',
+                                                    max_depth=5,
+                                                    max_features='log2',
+                                                    min_samples_leaf=2,
+                                                    min_samples_split=5),
+                   learning_rate=0.5, n_estimators=1000, random_state=42)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_2_5/samme_r/stat=['mean_statistics']</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>[0.53465347 0.51249411 0.53207547 0.51462264 0.52122642]</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([19.71559095, 21.91354322, 19.89826393, 20.3789072 , 22.90109897]), 'score_time': array([1.00299978, 1.3212347 , 1.02996254, 1.01830792, 0.95186448]), 'test_accuracy': array([0.53465347, 0.51249411, 0.53207547, 0.51462264, 0.52122642]), 'test_precision': array([0.55232029, 0.5292599 , 0.54776512, 0.53098107, 0.53873553]), 'test_recall': array([0.5508167 , 0.55807623, 0.56766576, 0.56039964, 0.54900181]), 'test_f1': array([0.55156747, 0.54328622, 0.55753791, 0.54529386, 0.54382022]), 'test_roc_auc': array([0.54093369, 0.52124872, 0.52976106, 0.52539533, 0.53520925]), 'test_average_precision': array([0.55520503, 0.54556652, 0.55187953, 0.5420342 , 0.57045079]), 'test_neg_log_loss': array([-0.69119577, -0.69180603, -0.69170992, -0.69212236, -0.69119648]), 'test_neg_brier_score': array([-0.24902554, -0.24933176, -0.24928256, -0.24948798, -0.24902757]), 'test_f1_macro': array([0.5339905 , 0.51026798, 0.53052071, 0.51240414, 0.52004907]), 'test_f1_weighted': array([0.53467833, 0.51156007, 0.53156571, 0.51367629, 0.52099095]), 'test_balanced_accuracy': array([0.5339952 , 0.51063772, 0.53064348, 0.51278078, 0.52008048])}</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0.5230145255612149</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.5482804823581956</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.539651837524178</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>[0.51952462 0.53965184 1.        ]</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.5571895424836601</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>[1.         0.55718954 0.        ]</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>[0 1]</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>[[2465   65]
- [1070   66]]</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>{'precision': 0.6973125884016973, 'recall': 0.974308300395257, 'f1-score': 0.8128606760098929, 'support': 2530.0}</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>{'precision': 0.5038167938931297, 'recall': 0.058098591549295774, 'f1-score': 0.10418310970797158, 'support': 1136.0}</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>{'precision': 0.6005646911474135, 'recall': 0.5162034459722764, 'f1-score': 0.45852189285893225, 'support': 3666.0}</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>{'precision': 0.6373531714454145, 'recall': 0.6903982542280415, 'f1-score': 0.5932595534460678, 'support': 3666.0}</t>
-        </is>
-      </c>
-    </row>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>[[2476 2618]
+ [2439 3069]]</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>{'precision': 0.503763987792472, 'recall': 0.48606203376521395, 'f1-score': 0.4947547207513238, 'support': 5094.0}</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>{'precision': 0.539651837524178, 'recall': 0.5571895424836601, 'f1-score': 0.5482804823581956, 'support': 5508.0}</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5217079126583251, 'recall': 0.521625788124437, 'f1-score': 0.5215176015547597, 'support': 10602.0}</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>{'precision': 0.522408609215056, 'recall': 0.5230145255612149, 'f1-score': 0.5225626716031113, 'support': 10602.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" customFormat="1" s="1"/>
+    <row r="19" customFormat="1" s="1"/>
+    <row r="20" customFormat="1" s="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/service_ia/training/version_1/fit/report_fit_grid.xlsx
+++ b/src/service_ia/training/version_1/fit/report_fit_grid.xlsx
@@ -489,37 +489,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>features</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>best_estimator</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>best_params</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>best_scorer</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>scorer</t>
         </is>
@@ -624,10 +624,8 @@
           <t>{'class_weight': None, 'criterion': 'entropy', 'max_depth': 5, 'max_features': 'log2', 'min_samples_leaf': 1, 'min_samples_split': 5}</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0.6891525423728814</t>
-        </is>
+      <c r="F4" t="n">
+        <v>0.6891525423728814</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -636,22 +634,228 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n"/>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stat=['mean_statistics']</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>{'mean_expected_goals_home_stat', 'under_over_1_5', 'mean_expected_goals_away_stat'}</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>DecisionTreeClassifier(max_depth=5, min_samples_leaf=4, min_samples_split=5)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>{'class_weight': None, 'criterion': 'gini', 'max_depth': 5, 'max_features': None, 'min_samples_leaf': 4, 'min_samples_split': 5}</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.7770909090909092</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>make_scorer(accuracy_score, response_method='predict')</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n"/>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_2_5/stat=['mean_statistics']</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>{'under_over_2_5', 'mean_expected_goals_home_stat', 'mean_expected_goals_away_stat'}</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>DecisionTreeClassifier(class_weight='balanced', criterion='entropy',
+                       max_depth=5, max_features='sqrt', min_samples_leaf=2,
+                       min_samples_split=10)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>{'class_weight': 'balanced', 'criterion': 'entropy', 'max_depth': 5, 'max_features': 'sqrt', 'min_samples_leaf': 2, 'min_samples_split': 10}</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5858386122254189</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>make_scorer(accuracy_score, response_method='predict')</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n"/>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_3_5/stat=['mean_statistics']</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>{'mean_expected_goals_home_stat', 'under_over_3_5', 'mean_expected_goals_away_stat'}</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>DecisionTreeClassifier(max_depth=5, max_features='sqrt', min_samples_leaf=2)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>{'class_weight': None, 'criterion': 'gini', 'max_depth': 5, 'max_features': 'sqrt', 'min_samples_leaf': 2, 'min_samples_split': 2}</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.681021897810219</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>make_scorer(accuracy_score, response_method='predict')</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n"/>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stat=['mean_statistics']</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>{'mean_expected_goals_home_stat', 'mean_expected_goals_away_stat', 'under_over_1_5'}</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>KNeighborsClassifier(metric='euclidean', n_neighbors=3, p=1, weights='distance')</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3, 'p': 1, 'weights': 'distance'}</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0.7369281562503407</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>make_scorer(accuracy_score, response_method='predict')</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n"/>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stat=['mean_statistics']</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>{'mean_expected_goals_away_stat', 'under_over_1_5', 'mean_expected_goals_home_stat'}</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>XGBClassifier(base_score=None, booster=None, callbacks=None,
+              colsample_bylevel=None, colsample_bynode=None,
+              colsample_bytree=1.0, device=None, early_stopping_rounds=None,
+              enable_categorical=False, eval_metric=None, feature_types=None,
+              gamma=None, grow_policy=None, importance_type=None,
+              interaction_constraints=None, learning_rate=0.2, max_bin=None,
+              max_cat_threshold=None, max_cat_to_onehot=None,
+              max_delta_step=None, max_depth=10, max_leaves=None,
+              min_child_weight=None, missing=nan, monotone_constraints=None,
+              multi_strategy=None, n_estimators=200, n_jobs=None,
+              num_parallel_tree=None, random_state=None, ...)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>{'colsample_bytree': 1.0, 'learning_rate': 0.2, 'max_depth': 10, 'n_estimators': 200, 'scale_pos_weight': 2, 'subsample': 0.7}</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0.7324921754871918</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>make_scorer(accuracy_score, response_method='predict')</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stat=['mean_statistics']</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>{'mean_expected_goals_home_stat', 'mean_expected_goals_away_stat', 'under_over_1_5'}</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LogisticRegression(C=0.1, max_iter=4288, penalty='l1', solver='saga')</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>{'C': 0.1, 'class_weight': None, 'penalty': 'l1', 'solver': 'saga', 'max_iter': 4288}</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.5965720674354231</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>make_scorer(accuracy_score, response_method='predict')</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -684,7 +888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -2130,40 +2334,30 @@
           <t>{'fit_time': array([19.71559095, 21.91354322, 19.89826393, 20.3789072 , 22.90109897]), 'score_time': array([1.00299978, 1.3212347 , 1.02996254, 1.01830792, 0.95186448]), 'test_accuracy': array([0.53465347, 0.51249411, 0.53207547, 0.51462264, 0.52122642]), 'test_precision': array([0.55232029, 0.5292599 , 0.54776512, 0.53098107, 0.53873553]), 'test_recall': array([0.5508167 , 0.55807623, 0.56766576, 0.56039964, 0.54900181]), 'test_f1': array([0.55156747, 0.54328622, 0.55753791, 0.54529386, 0.54382022]), 'test_roc_auc': array([0.54093369, 0.52124872, 0.52976106, 0.52539533, 0.53520925]), 'test_average_precision': array([0.55520503, 0.54556652, 0.55187953, 0.5420342 , 0.57045079]), 'test_neg_log_loss': array([-0.69119577, -0.69180603, -0.69170992, -0.69212236, -0.69119648]), 'test_neg_brier_score': array([-0.24902554, -0.24933176, -0.24928256, -0.24948798, -0.24902757]), 'test_f1_macro': array([0.5339905 , 0.51026798, 0.53052071, 0.51240414, 0.52004907]), 'test_f1_weighted': array([0.53467833, 0.51156007, 0.53156571, 0.51367629, 0.52099095]), 'test_balanced_accuracy': array([0.5339952 , 0.51063772, 0.53064348, 0.51278078, 0.52008048])}</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>0.5230145255612149</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0.5482804823581956</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>0.539651837524178</t>
-        </is>
+      <c r="F17" t="n">
+        <v>0.5230145255612149</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.5482804823581956</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.539651837524178</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>[0.51952462 0.53965184 1.        ]</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>0.5571895424836601</t>
-        </is>
+      <c r="J17" t="n">
+        <v>0.5571895424836601</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>[1.         0.55718954 0.        ]</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="L17" t="n">
+        <v>0</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -2197,8 +2391,234 @@
         </is>
       </c>
     </row>
-    <row r="18" customFormat="1" s="1"/>
-    <row r="19" customFormat="1" s="1"/>
+    <row r="18" customFormat="1" s="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>StackingClassifier(cv=5,
+                   estimators=[('dt', DecisionTreeClassifier(max_depth=5)),
+                               ('svc', SVC(probability=True)),
+                               ('rf', RandomForestClassifier()),
+                               ('knn', KNeighborsClassifier()),
+                               ('xgb',
+                                XGBClassifier(base_score=None, booster=None,
+                                              callbacks=None,
+                                              colsample_bylevel=None,
+                                              colsample_bynode=None,
+                                              colsample_bytree=None,
+                                              device=None,
+                                              early_stopping_rounds=None,
+                                              enable_...
+                                              max_cat_threshold=None,
+                                              max_cat_to_onehot=None,
+                                              max_delta_step=None,
+                                              max_depth=None, max_leaves=None,
+                                              min_child_weight=None,
+                                              missing=nan,
+                                              monotone_constraints=None,
+                                              multi_strategy=None,
+                                              n_estimators=None, n_jobs=None,
+                                              num_parallel_tree=None,
+                                              random_state=None, ...))],
+                   final_estimator=LogisticRegression(), n_jobs=-1,
+                   passthrough=True, stack_method='predict_proba', verbose=2)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stack_method=predict_proba/stat=['mean_statistics'], passthrough=True</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>[0.77842227 0.77842227 0.77958237 0.77958237 0.77726218]</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([6.83393693, 5.59591818, 5.29194522, 5.07703352, 4.10983062]), 'score_time': array([0.76384902, 0.51504922, 0.52111483, 0.49997997, 0.50426984]), 'test_accuracy': array([0.77842227, 0.77842227, 0.77958237, 0.77958237, 0.77726218]), 'test_precision': array([0.77906977, 0.77972028, 0.77932636, 0.77932636, 0.77816492]), 'test_recall': array([0.99850969, 0.99701937, 1.        , 1.        , 0.99850969]), 'test_f1': array([0.87524494, 0.87508175, 0.87597911, 0.87597911, 0.87467363]), 'test_roc_auc': array([0.60021379, 0.63253252, 0.63417108, 0.68111204, 0.61419621]), 'test_average_precision': array([0.83910689, 0.85586606, 0.84744782, 0.87354771, 0.83358721]), 'test_neg_log_loss': array([-0.51804736, -0.50870798, -0.51078007, -0.49921384, -0.51862325]), 'test_neg_brier_score': array([-0.1688688 , -0.16583818, -0.1660428 , -0.16233188, -0.16807465]), 'test_f1_macro': array([0.44280382, 0.44779729, 0.44319789, 0.44319789, 0.43733681]), 'test_f1_weighted': array([0.6836063 , 0.68572831, 0.68418975, 0.68418975, 0.68086544]), 'test_balanced_accuracy': array([0.50187264, 0.50374529, 0.5026178 , 0.5026178 , 0.49925484])}</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0.7786542923433875</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.8753918495297806</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.7791211346198559</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>[0.77842227 0.77912113 1.        ]</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0.9988077496274218</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>[1.         0.99880775 0.        ]</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>[[   5  950]
+ [   4 3351]]</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5555555555555556, 'recall': 0.005235602094240838, 'f1-score': 0.01037344398340249, 'support': 955.0}</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7791211346198559, 'recall': 0.9988077496274218, 'f1-score': 0.8753918495297806, 'support': 3355.0}</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6673383450877057, 'recall': 0.5020216758608314, 'f1-score': 0.4428826467565915, 'support': 4310.0}</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>{'precision': 0.729583981950156, 'recall': 0.7786542923433875, 'f1-score': 0.6837230380920101, 'support': 4310.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" customFormat="1" s="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>StackingClassifier(cv=5,
+                   estimators=[('dt', DecisionTreeClassifier(max_depth=5)),
+                               ('svc', SVC(probability=True)),
+                               ('rf', RandomForestClassifier()),
+                               ('knn', KNeighborsClassifier()),
+                               ('xgb',
+                                XGBClassifier(base_score=None, booster=None,
+                                              callbacks=None,
+                                              colsample_bylevel=None,
+                                              colsample_bynode=None,
+                                              colsample_bytree=None,
+                                              device=None,
+                                              early_stopping_rounds=None,
+                                              enable_...
+                                              max_cat_threshold=None,
+                                              max_cat_to_onehot=None,
+                                              max_delta_step=None,
+                                              max_depth=None, max_leaves=None,
+                                              min_child_weight=None,
+                                              missing=nan,
+                                              monotone_constraints=None,
+                                              multi_strategy=None,
+                                              n_estimators=None, n_jobs=None,
+                                              num_parallel_tree=None,
+                                              random_state=None, ...))],
+                   final_estimator=LogisticRegression(), n_jobs=-1,
+                   passthrough=True, stack_method='predict_proba', verbose=2)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stack_method=predict_proba/stat=['mean_statistics'], passthrough=True</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>[0.7704918  0.80178838 0.77421759 0.77496274 0.79061103]</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([14.93475199, 13.78599405, 14.79828238, 15.81917262, 16.46792912]), 'score_time': array([1.29974842, 1.37794757, 1.31155562, 1.54709196, 1.54287004]), 'test_accuracy': array([0.77645306, 0.80402385, 0.77496274, 0.77868852, 0.78017884]), 'test_precision': array([0.7715959 , 0.82278481, 0.76470588, 0.76338028, 0.78658537]), 'test_recall': array([0.78539493, 0.77496274, 0.79433681, 0.80774963, 0.76900149]), 'test_f1': array([0.77843427, 0.7981581 , 0.77923977, 0.78493845, 0.77769405]), 'test_roc_auc': array([0.85828701, 0.88120806, 0.85359174, 0.86196282, 0.86668473]), 'test_average_precision': array([0.85929346, 0.88574889, 0.84582906, 0.86026989, 0.86769274]), 'test_neg_log_loss': array([-0.47103642, -0.43901924, -0.47845827, -0.46594212, -0.45909568]), 'test_neg_brier_score': array([-0.15400349, -0.14067379, -0.15587593, -0.15190837, -0.14929527]), 'test_f1_macro': array([0.77643518, 0.80385819, 0.77487824, 0.77850146, 0.78015137]), 'test_f1_weighted': array([0.77643518, 0.80385819, 0.77487824, 0.77850146, 0.78015137]), 'test_balanced_accuracy': array([0.77645306, 0.80402385, 0.77496274, 0.77868852, 0.78017884])}</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0.78301043219076</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.783139708072684</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0.782673414706758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>[0.5        0.78267341 1.        ]</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0.7836065573770492</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>[1.         0.78360656 0.        ]</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>[[2625  730]
+ [ 726 2629]]</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7833482542524619, 'recall': 0.7824143070044709, 'f1-score': 0.7828810020876826, 'support': 3355.0}</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>{'precision': 0.782673414706758, 'recall': 0.7836065573770492, 'f1-score': 0.783139708072684, 'support': 3355.0}</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>{'precision': 0.78301083447961, 'recall': 0.78301043219076, 'f1-score': 0.7830103550801832, 'support': 6710.0}</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7830108344796101, 'recall': 0.78301043219076, 'f1-score': 0.7830103550801832, 'support': 6710.0}</t>
+        </is>
+      </c>
+    </row>
     <row r="20" customFormat="1" s="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/src/service_ia/training/version_1/fit/report_fit_grid.xlsx
+++ b/src/service_ia/training/version_1/fit/report_fit_grid.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report BEST FIT" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report ML FIT" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Report BEST FIT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Report ML FIT" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -846,10 +846,8 @@
           <t>{'C': 0.1, 'class_weight': None, 'penalty': 'l1', 'solver': 'saga', 'max_iter': 4288}</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0.5965720674354231</t>
-        </is>
+      <c r="F10" t="n">
+        <v>0.5965720674354231</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -858,8 +856,42 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="C11" s="1" t="n"/>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stat=['mean_statistics']</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>{'mean_expected_goals_home_stat', 'under_over_1_5', 'mean_expected_goals_away_stat'}</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier(bootstrap=False, class_weight='balanced',
+                       max_features='log2', n_estimators=4272, warm_start=True)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>{'bootstrap': False, 'class_weight': 'balanced', 'max_depth': None, 'max_features': 'log2', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 4272}</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.7737480219962757</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>make_scorer(accuracy_score, response_method='predict')</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -888,7 +920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -2552,40 +2584,30 @@
           <t>{'fit_time': array([14.93475199, 13.78599405, 14.79828238, 15.81917262, 16.46792912]), 'score_time': array([1.29974842, 1.37794757, 1.31155562, 1.54709196, 1.54287004]), 'test_accuracy': array([0.77645306, 0.80402385, 0.77496274, 0.77868852, 0.78017884]), 'test_precision': array([0.7715959 , 0.82278481, 0.76470588, 0.76338028, 0.78658537]), 'test_recall': array([0.78539493, 0.77496274, 0.79433681, 0.80774963, 0.76900149]), 'test_f1': array([0.77843427, 0.7981581 , 0.77923977, 0.78493845, 0.77769405]), 'test_roc_auc': array([0.85828701, 0.88120806, 0.85359174, 0.86196282, 0.86668473]), 'test_average_precision': array([0.85929346, 0.88574889, 0.84582906, 0.86026989, 0.86769274]), 'test_neg_log_loss': array([-0.47103642, -0.43901924, -0.47845827, -0.46594212, -0.45909568]), 'test_neg_brier_score': array([-0.15400349, -0.14067379, -0.15587593, -0.15190837, -0.14929527]), 'test_f1_macro': array([0.77643518, 0.80385819, 0.77487824, 0.77850146, 0.78015137]), 'test_f1_weighted': array([0.77643518, 0.80385819, 0.77487824, 0.77850146, 0.78015137]), 'test_balanced_accuracy': array([0.77645306, 0.80402385, 0.77496274, 0.77868852, 0.78017884])}</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>0.78301043219076</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0.783139708072684</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>0.782673414706758</t>
-        </is>
+      <c r="F19" t="n">
+        <v>0.7830104321907601</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.783139708072684</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.782673414706758</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>[0.5        0.78267341 1.        ]</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>0.7836065573770492</t>
-        </is>
+      <c r="J19" t="n">
+        <v>0.7836065573770492</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>[1.         0.78360656 0.        ]</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="L19" t="n">
+        <v>0</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -2619,7 +2641,128 @@
         </is>
       </c>
     </row>
-    <row r="20" customFormat="1" s="1"/>
+    <row r="20" customFormat="1" s="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>StackingClassifier(cv=5,
+                   estimators=[('dt',
+                                DecisionTreeClassifier(criterion='entropy',
+                                                       max_depth=5,
+                                                       max_features='sqrt',
+                                                       min_samples_split=5)),
+                               ('svc', SVC(probability=True)),
+                               ('rf',
+                                RandomForestClassifier(bootstrap=False,
+                                                       class_weight='balanced',
+                                                       max_features='log2',
+                                                       n_estimators=4272,
+                                                       warm_start=True)),
+                               ('knn',
+                                KNeighborsClassifier(metric='euclidean',
+                                                     n_neighbo...
+                                              max_cat_threshold=None,
+                                              max_cat_to_onehot=None,
+                                              max_delta_step=None, max_depth=10,
+                                              max_leaves=None,
+                                              min_child_weight=None,
+                                              missing=nan,
+                                              monotone_constraints=None,
+                                              multi_strategy=None,
+                                              n_estimators=200, n_jobs=None,
+                                              num_parallel_tree=None,
+                                              random_state=None, ...))],
+                   final_estimator=LogisticRegression(), n_jobs=-1,
+                   passthrough=True, stack_method='predict_proba', verbose=2)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stack_method=predict_proba/stat=['mean_statistics'], passthrough=True</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>[0.78614009 0.7876304  0.79955291 0.79433681 0.79061103]</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([173.19554114, 168.8850553 , 193.54900908, 173.27430797,
+       163.90362048]), 'score_time': array([2.74760318, 2.7925365 , 2.97049212, 2.86263585, 2.74251223]), 'test_accuracy': array([0.78986587, 0.79359165, 0.79582712, 0.79657228, 0.79061103]), 'test_precision': array([0.79785605, 0.80122324, 0.78479197, 0.80709877, 0.81050955]), 'test_recall': array([0.77645306, 0.78092399, 0.81520119, 0.77943368, 0.7585693 ]), 'test_f1': array([0.78700906, 0.7909434 , 0.7997076 , 0.79302502, 0.78367975]), 'test_roc_auc': array([0.87495586, 0.87710137, 0.87903145, 0.88172112, 0.88097708]), 'test_average_precision': array([0.87917457, 0.86754238, 0.87767488, 0.88256025, 0.87662512]), 'test_neg_log_loss': array([-0.44731973, -0.44749844, -0.44324326, -0.43518718, -0.44155875]), 'test_neg_brier_score': array([-0.1450903 , -0.14357059, -0.14272175, -0.13924326, -0.14163746]), 'test_f1_macro': array([0.78982806, 0.79355853, 0.79575046, 0.79651251, 0.79039583]), 'test_f1_weighted': array([0.78982806, 0.79355853, 0.79575046, 0.79651251, 0.79039583]), 'test_balanced_accuracy': array([0.78986587, 0.79359165, 0.79582712, 0.79657228, 0.79061103])}</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0.7919523099850969</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0.7890601390148081</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0.8001838798651547</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>[0.5        0.80018388 1.        ]</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0.778241430700447</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>[1.         0.77824143 0.        ]</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>[[2703  652]
+ [ 744 2611]]</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7841601392515231, 'recall': 0.8056631892697467, 'f1-score': 0.7947662452219936, 'support': 3355.0}</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>{'precision': 0.8001838798651547, 'recall': 0.778241430700447, 'f1-score': 0.7890601390148081, 'support': 3355.0}</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7921720095583389, 'recall': 0.7919523099850969, 'f1-score': 0.7919131921184008, 'support': 6710.0}</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7921720095583389, 'recall': 0.7919523099850969, 'f1-score': 0.7919131921184008, 'support': 6710.0}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/service_ia/training/version_1/fit/report_fit_grid.xlsx
+++ b/src/service_ia/training/version_1/fit/report_fit_grid.xlsx
@@ -920,7 +920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:W30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -1020,6 +1020,31 @@
           <t>weighted avg</t>
         </is>
       </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>f1_alt</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>bast_i_alt</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>best_thr_alt</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
     </row>
     <row r="2" customFormat="1" s="1">
       <c r="A2" t="inlineStr">
@@ -1108,6 +1133,11 @@
           <t>{'precision': 0.6866507013813268, 'recall': 0.7650615417836321, 'f1-score': 0.6837975679350144, 'support': 4631.0}</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3" customFormat="1" s="1">
       <c r="A3" t="inlineStr">
@@ -1195,6 +1225,11 @@
           <t>{'precision': 0.6623329325431794, 'recall': 0.7296480241848413, 'f1-score': 0.683542263512542, 'support': 4631.0}</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4" customFormat="1" s="1">
       <c r="A4" t="inlineStr">
@@ -1283,6 +1318,11 @@
           <t>{'precision': 0.7288424514725529, 'recall': 0.2548045778449579, 'f1-score': 0.14255103964891733, 'support': 4631.0}</t>
         </is>
       </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5" customFormat="1" s="1">
       <c r="A5" t="inlineStr">
@@ -1370,6 +1410,11 @@
           <t>{'precision': 0.7150099658494417, 'recall': 0.26473763765925284, 'f1-score': 0.16550099488525769, 'support': 4631.0}</t>
         </is>
       </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6" customFormat="1" s="1">
       <c r="A6" t="inlineStr">
@@ -1458,6 +1503,11 @@
           <t>{'precision': 0.6957822195083141, 'recall': 0.4806737205787087, 'f1-score': 0.5127011190874851, 'support': 4631.0}</t>
         </is>
       </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7" customFormat="1" s="1">
       <c r="A7" t="inlineStr">
@@ -1545,6 +1595,11 @@
           <t>{'precision': 0.6695546817147678, 'recall': 0.4748434463398834, 'f1-score': 0.510610522863405, 'support': 4631.0}</t>
         </is>
       </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8" customFormat="1" s="1">
       <c r="A8" t="inlineStr">
@@ -1633,6 +1688,11 @@
           <t>{'precision': 0.7295244827524134, 'recall': 0.25372489743036064, 'f1-score': 0.14014118933018369, 'support': 4631.0}</t>
         </is>
       </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9" customFormat="1" s="1">
       <c r="A9" t="inlineStr">
@@ -1720,6 +1780,11 @@
           <t>{'precision': 0.7065979775883607, 'recall': 0.2988555387605269, 'f1-score': 0.23669459475071708, 'support': 4631.0}</t>
         </is>
       </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10" customFormat="1" s="1">
       <c r="A10" t="inlineStr">
@@ -1808,6 +1873,11 @@
           <t>{'precision': 0.6813324271200106, 'recall': 0.7691643273591017, 'f1-score': 0.6729361570919801, 'support': 4631.0}</t>
         </is>
       </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11" customFormat="1" s="1">
       <c r="A11" t="inlineStr">
@@ -1895,6 +1965,11 @@
           <t>{'precision': 0.6568120599882818, 'recall': 0.7620384366227597, 'f1-score': 0.6748398446573446, 'support': 4631.0}</t>
         </is>
       </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12" customFormat="1" s="1">
       <c r="A12" t="inlineStr">
@@ -1983,6 +2058,11 @@
           <t>{'precision': 0.6528703003773298, 'recall': 0.6519484160358845, 'f1-score': 0.651422892476994, 'support': 7134.0}</t>
         </is>
       </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13" customFormat="1" s="1">
       <c r="A13" t="inlineStr">
@@ -2070,6 +2150,11 @@
           <t>{'precision': 0.7157403568093786, 'recall': 0.7155873282870759, 'f1-score': 0.7155368845837681, 'support': 7134.0}</t>
         </is>
       </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14" customFormat="1" s="1">
       <c r="A14" t="inlineStr">
@@ -2158,6 +2243,11 @@
           <t>{'precision': 0.6285593409540101, 'recall': 0.6284810126582279, 'f1-score': 0.6284244145103419, 'support': 6320.0}</t>
         </is>
       </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15" customFormat="1" s="1">
       <c r="A15" t="inlineStr">
@@ -2245,6 +2335,11 @@
           <t>{'precision': 0.6739083363406712, 'recall': 0.6737341772151899, 'f1-score': 0.6736524726788272, 'support': 6320.0}</t>
         </is>
       </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16" customFormat="1" s="1">
       <c r="A16" t="inlineStr">
@@ -2334,6 +2429,11 @@
           <t>{'precision': 0.5681391886055531, 'recall': 0.5690435766836446, 'f1-score': 0.567726036345396, 'support': 10602.0}</t>
         </is>
       </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17" customFormat="1" s="1">
       <c r="A17" t="inlineStr">
@@ -2422,6 +2522,11 @@
           <t>{'precision': 0.522408609215056, 'recall': 0.5230145255612149, 'f1-score': 0.5225626716031113, 'support': 10602.0}</t>
         </is>
       </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
     </row>
     <row r="18" customFormat="1" s="1">
       <c r="A18" t="inlineStr">
@@ -2531,6 +2636,11 @@
           <t>{'precision': 0.729583981950156, 'recall': 0.7786542923433875, 'f1-score': 0.6837230380920101, 'support': 4310.0}</t>
         </is>
       </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
     </row>
     <row r="19" customFormat="1" s="1">
       <c r="A19" t="inlineStr">
@@ -2640,6 +2750,11 @@
           <t>{'precision': 0.7830108344796101, 'recall': 0.78301043219076, 'f1-score': 0.7830103550801832, 'support': 6710.0}</t>
         </is>
       </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
     </row>
     <row r="20" customFormat="1" s="1">
       <c r="A20" t="inlineStr">
@@ -2696,40 +2811,30 @@
        163.90362048]), 'score_time': array([2.74760318, 2.7925365 , 2.97049212, 2.86263585, 2.74251223]), 'test_accuracy': array([0.78986587, 0.79359165, 0.79582712, 0.79657228, 0.79061103]), 'test_precision': array([0.79785605, 0.80122324, 0.78479197, 0.80709877, 0.81050955]), 'test_recall': array([0.77645306, 0.78092399, 0.81520119, 0.77943368, 0.7585693 ]), 'test_f1': array([0.78700906, 0.7909434 , 0.7997076 , 0.79302502, 0.78367975]), 'test_roc_auc': array([0.87495586, 0.87710137, 0.87903145, 0.88172112, 0.88097708]), 'test_average_precision': array([0.87917457, 0.86754238, 0.87767488, 0.88256025, 0.87662512]), 'test_neg_log_loss': array([-0.44731973, -0.44749844, -0.44324326, -0.43518718, -0.44155875]), 'test_neg_brier_score': array([-0.1450903 , -0.14357059, -0.14272175, -0.13924326, -0.14163746]), 'test_f1_macro': array([0.78982806, 0.79355853, 0.79575046, 0.79651251, 0.79039583]), 'test_f1_weighted': array([0.78982806, 0.79355853, 0.79575046, 0.79651251, 0.79039583]), 'test_balanced_accuracy': array([0.78986587, 0.79359165, 0.79582712, 0.79657228, 0.79061103])}</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>0.7919523099850969</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0.7890601390148081</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>0.8001838798651547</t>
-        </is>
+      <c r="F20" t="n">
+        <v>0.7919523099850969</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.7890601390148081</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.8001838798651547</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>[0.5        0.80018388 1.        ]</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>0.778241430700447</t>
-        </is>
+      <c r="J20" t="n">
+        <v>0.778241430700447</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>[1.         0.77824143 0.        ]</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="L20" t="n">
+        <v>0</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -2760,6 +2865,1193 @@
       <c r="R20" t="inlineStr">
         <is>
           <t>{'precision': 0.7921720095583389, 'recall': 0.7919523099850969, 'f1-score': 0.7919131921184008, 'support': 6710.0}</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>StackingClassifier(cv=5,
+                   estimators=[('svc_cal',
+                                CalibratedClassifierCV(cv=3,
+                                                       estimator=SVC(probability=True))),
+                               ('rf',
+                                RandomForestClassifier(class_weight='balanced',
+                                                       n_estimators=800,
+                                                       n_jobs=-1,
+                                                       random_state=42)),
+                               ('knn',
+                                Pipeline(steps=[('standardscaler',
+                                                 StandardScaler(with_mean=False)),
+                                                ('kneighborsclassifier',
+                                                 KNeighborsClassifier(metric='euclidean',
+                                                                      n_nei...
+                                                                               n_estimators=400,
+                                                                               n_jobs=-1,
+                                                                               num_parallel_tree=None, ...),
+                                                       method='isotonic')),
+                               ('sgd_lin',
+                                Pipeline(steps=[('standardscaler',
+                                                 StandardScaler(with_mean=False)),
+                                                ('sgdclassifier',
+                                                 SGDClassifier(loss='log_loss',
+                                                               max_iter=2000,
+                                                               random_state=42))]))],
+                   final_estimator=LogisticRegression(C=0.5,
+                                                      class_weight='balanced',
+                                                      max_iter=2000),
+                   n_jobs=-1, stack_method='predict_proba', verbose=2)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_2_5/stack_method=predict_proba/stat=['mean_statistics'], passthrough=False</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>[0.58086124 0.57416268 0.56555024 0.55119617 0.58851675]</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([82.32055473, 65.41894293, 55.11756182, 58.70327473, 64.23909354]), 'score_time': array([3.96781445, 3.87100697, 3.99056506, 3.85002923, 3.96219921]), 'test_accuracy': array([0.58086124, 0.57416268, 0.56555024, 0.55119617, 0.58851675]), 'test_precision': array([0.61811024, 0.64615385, 0.60914761, 0.63975155, 0.61101549]), 'test_recall': array([0.56272401, 0.45080501, 0.52415027, 0.36851521, 0.63506261]), 'test_f1': array([0.5891182 , 0.53108535, 0.56346154, 0.4676504 , 0.62280702]), 'test_roc_auc': array([0.60499511, 0.6093222 , 0.60288066, 0.61864956, 0.63230563]), 'test_average_precision': array([0.62189388, 0.61951114, 0.64514742, 0.63604353, 0.65897779]), 'test_neg_log_loss': array([-0.67697316, -0.68768327, -0.68025434, -0.68807935, -0.67315338]), 'test_neg_brier_score': array([-0.24201225, -0.2470884 , -0.24360341, -0.24731505, -0.24009632]), 'test_f1_macro': array([0.58069191, 0.57053829, 0.56554029, 0.53986325, 0.58508772]), 'test_f1_weighted': array([0.58126442, 0.56778225, 0.56539508, 0.53481871, 0.58772266]), 'test_balanced_accuracy': array([0.58218336, 0.5834272 , 0.5686595 , 0.56491604, 0.58502102])}</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0.5720574162679426</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.5594956658786446</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.6222611744084137</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>[0.53473684 0.62226117 1.        ]</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0.5082319255547602</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>[1.         0.50823193 0.        ]</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>[[1569  862]
+ [1374 1420]]</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5331294597349643, 'recall': 0.6454134101192924, 'f1-score': 0.5839225902493487, 'support': 2431.0}</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6222611744084137, 'recall': 0.5082319255547602, 'f1-score': 0.5594956658786446, 'support': 2794.0}</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>{'precision': 0.577695317071689, 'recall': 0.5768226678370263, 'f1-score': 0.5717091280639967, 'support': 5225.0}</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>{'precision': 0.580791471370872, 'recall': 0.5720574162679426, 'f1-score': 0.5708606138490143, 'support': 5225.0}</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>StackingClassifier(cv=5,
+                   estimators=[('svc_cal',
+                                CalibratedClassifierCV(cv=3,
+                                                       estimator=SVC(probability=True))),
+                               ('rf',
+                                RandomForestClassifier(class_weight='balanced',
+                                                       n_estimators=800,
+                                                       n_jobs=-1,
+                                                       random_state=42)),
+                               ('knn',
+                                Pipeline(steps=[('standardscaler',
+                                                 StandardScaler(with_mean=False)),
+                                                ('kneighborsclassifier',
+                                                 KNeighborsClassifier(metric='euclidean',
+                                                                      n_nei...
+                                                                               num_parallel_tree=None, ...),
+                                                       method='isotonic')),
+                               ('sgd_lin',
+                                Pipeline(steps=[('standardscaler',
+                                                 StandardScaler(with_mean=False)),
+                                                ('sgdclassifier',
+                                                 SGDClassifier(loss='log_loss',
+                                                               max_iter=2000,
+                                                               random_state=42))]))],
+                   final_estimator=LogisticRegression(C=0.5,
+                                                      class_weight='balanced',
+                                                      max_iter=2000),
+                   n_jobs=-1, passthrough=True, stack_method='predict_proba',
+                   verbose=2)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_2_5/stack_method=predict_proba/stat=['mean_statistics'], passthrough=True</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>[0.58851675 0.58086124 0.56363636 0.56076555 0.60095694]</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([17.73396349, 17.08883739, 17.14603615, 49.24102283, 63.15540099]), 'score_time': array([2.14776015, 2.34148383, 2.60226893, 4.1419127 , 4.11817312]), 'test_accuracy': array([0.58851675, 0.58086124, 0.56363636, 0.56076555, 0.60095694]), 'test_precision': array([0.61678832, 0.65714286, 0.6112311 , 0.64880952, 0.66136364]), 'test_recall': array([0.60573477, 0.45259392, 0.50626118, 0.38998211, 0.52057245]), 'test_f1': array([0.61121157, 0.53601695, 0.55381605, 0.48715084, 0.58258258]), 'test_roc_auc': array([0.61362449, 0.61356626, 0.60528059, 0.6207403 , 0.63619632]), 'test_average_precision': array([0.63020578, 0.62936507, 0.63676299, 0.63862219, 0.66992663]), 'test_neg_log_loss': array([-0.67113807, -0.68362021, -0.67705038, -0.68523946, -0.66856204]), 'test_neg_brier_score': array([-0.23926354, -0.24504789, -0.24211704, -0.24548627, -0.2380176 ]), 'test_f1_macro': array([0.58710985, 0.576909  , 0.56342488, 0.55152521, 0.60018222]), 'test_f1_weighted': array([0.58874738, 0.57405242, 0.56275364, 0.54702824, 0.59895277]), 'test_balanced_accuracy': array([0.58726163, 0.59049449, 0.56794541, 0.57359188, 0.60699404])}</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0.5789473684210527</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.5569875151026984</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.6367403314917127</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>[0.53473684 0.63674033 1.        ]</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0.4949892627057981</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>[1.         0.49498926 0.        ]</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>[[1642  789]
+ [1411 1383]]</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5378316410088437, 'recall': 0.6754422048539696, 'f1-score': 0.5988329686360321, 'support': 2431.0}</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6367403314917127, 'recall': 0.4949892627057981, 'f1-score': 0.5569875151026984, 'support': 2794.0}</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5872859862502782, 'recall': 0.5852157337798838, 'f1-score': 0.5779102418693652, 'support': 5225.0}</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5907217618144199, 'recall': 0.5789473684210527, 'f1-score': 0.5764566629571547, 'support': 5225.0}</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Pipeline(steps=[('smote', SMOTE(random_state=42)),
+                ('stack',
+                 StackingClassifier(cv=5,
+                                    estimators=[('svc_cal',
+                                                 CalibratedClassifierCV(cv=3,
+                                                                        estimator=SVC(probability=True))),
+                                                ('rf',
+                                                 RandomForestClassifier(n_estimators=800,
+                                                                        n_jobs=-1,
+                                                                        random_state=42)),
+                                                ('knn',
+                                                 Pipeline(steps=[('standardscaler',
+                                                                  StandardScaler(with_mean=False)),
+                                                                 ('kneighborsclassifier',
+                                                                  KNeighborsC...
+                                                                                                multi_strategy=None,
+                                                                                                n_estimators=400,
+                                                                                                n_jobs=-1,
+                                                                                                num_parallel_tree=None, ...),
+                                                                        method='isotonic')),
+                                                ('sgd_lin',
+                                                 Pipeline(steps=[('standardscaler',
+                                                                  StandardScaler(with_mean=False)),
+                                                                 ('sgdclassifier',
+                                                                  SGDClassifier(loss='log_loss',
+                                                                                max_iter=2000,
+                                                                                random_state=42))]))],
+                                    final_estimator=LogisticRegression(C=0.5,
+                                                                       max_iter=2000),
+                                    n_jobs=-1, stack_method='predict_proba',
+                                    verbose=2))])</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stack_method=predict_proba/stat=['mean_statistics'], passthrough=False, smote=True</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>[0.69310345 0.68124281 0.68929804 0.69390104 0.68699655]</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([14.05911708, 13.81433558, 13.77107906, 13.89282799, 14.20299649]), 'score_time': array([1.33919621, 1.34930062, 1.32721543, 1.31043267, 1.31486106]), 'test_accuracy': array([0.69310345, 0.68124281, 0.68929804, 0.69390104, 0.68699655]), 'test_precision': array([0.78741259, 0.79791976, 0.79310345, 0.7917847 , 0.78481013]), 'test_recall': array([0.83038348, 0.7920354 , 0.81415929, 0.82448378, 0.82422452]), 'test_f1': array([0.80832735, 0.79496669, 0.80349345, 0.80780347, 0.80403458]), 'test_roc_auc': array([0.57471423, 0.58166921, 0.52756799, 0.55466494, 0.55225258]), 'test_average_precision': array([0.82728587, 0.83343721, 0.79127511, 0.79923921, 0.81054914]), 'test_neg_log_loss': array([-0.61368641, -0.63532379, -0.66433494, -0.63764753, -0.62751268]), 'test_neg_brier_score': array([-0.20628564, -0.21689909, -0.22003238, -0.21292106, -0.21095854]), 'test_f1_macro': array([0.51943745, 0.53960221, 0.5308676 , 0.52819552, 0.51344586]), 'test_f1_weighted': array([0.68081733, 0.68271211, 0.68365102, 0.6848918 , 0.67562714]), 'test_balanced_accuracy': array([0.51935841, 0.53999676, 0.5301163 , 0.52742513, 0.51367476])}</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0.7797975149562817</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.8762766645119586</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.7797975149562817</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>[0.77979751 1.        ]</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>[1. 0.]</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>[[   0  957]
+ [   0 3389]]</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>{'precision': 0.0, 'recall': 0.0, 'f1-score': 0.0, 'support': 957.0}</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7797975149562817, 'recall': 1.0, 'f1-score': 0.8762766645119586, 'support': 3389.0}</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>{'precision': 0.38989875747814084, 'recall': 0.5, 'f1-score': 0.4381383322559793, 'support': 4346.0}</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6080841643319923, 'recall': 0.7797975149562817, 'f1-score': 0.6833183654006046, 'support': 4346.0}</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Pipeline(steps=[('smote', SMOTE(random_state=42)),
+                ('stack',
+                 StackingClassifier(cv=5,
+                                    estimators=[('svc_cal',
+                                                 CalibratedClassifierCV(cv=3,
+                                                                        estimator=SVC(probability=True))),
+                                                ('rf',
+                                                 RandomForestClassifier(n_estimators=800,
+                                                                        n_jobs=-1,
+                                                                        random_state=42)),
+                                                ('knn',
+                                                 Pipeline(steps=[('standardscaler',
+                                                                  StandardScaler(with_mean=False)),
+                                                                 ('kneighborsclassifier',
+                                                                  KNeighborsC...
+                                                                                                n_estimators=400,
+                                                                                                n_jobs=-1,
+                                                                                                num_parallel_tree=None, ...),
+                                                                        method='isotonic')),
+                                                ('sgd_lin',
+                                                 Pipeline(steps=[('standardscaler',
+                                                                  StandardScaler(with_mean=False)),
+                                                                 ('sgdclassifier',
+                                                                  SGDClassifier(loss='log_loss',
+                                                                                max_iter=2000,
+                                                                                random_state=42))]))],
+                                    final_estimator=LogisticRegression(C=0.5,
+                                                                       max_iter=2000),
+                                    n_jobs=-1, passthrough=True,
+                                    stack_method='predict_proba', verbose=2))])</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stack_method=predict_proba/stat=['mean_statistics'], passthrough=True, smote=True</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>[0.6954023  0.67433832 0.69159954 0.69620253 0.67548907]</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([16.50779772, 16.53481102, 15.93377852, 16.4531734 , 16.27220225]), 'score_time': array([1.46892405, 1.4107933 , 1.35537887, 1.55970168, 1.42966151]), 'test_accuracy': array([0.6954023 , 0.67433832, 0.69159954, 0.69620253, 0.67548907]), 'test_precision': array([0.78881119, 0.80060883, 0.79369628, 0.79403409, 0.78335725]), 'test_recall': array([0.83185841, 0.77581121, 0.81710914, 0.82448378, 0.80649926]), 'test_f1': array([0.8097631 , 0.78801498, 0.80523256, 0.8089725 , 0.79475983]), 'test_roc_auc': array([0.58121313, 0.5843179 , 0.53520518, 0.5570588 , 0.55821486]), 'test_average_precision': array([0.83500613, 0.83662873, 0.80401929, 0.80936645, 0.82140859]), 'test_neg_log_loss': array([-0.6117138 , -0.64519538, -0.6596589 , -0.63762065, -0.62597506]), 'test_neg_brier_score': array([-0.20577875, -0.22140349, -0.21910789, -0.21349964, -0.21166781]), 'test_f1_macro': array([0.52303717, 0.54289087, 0.53245053, 0.53369973, 0.51001728]), 'test_f1_weighted': array([0.68320821, 0.68026192, 0.68532147, 0.68796652, 0.66893573]), 'test_balanced_accuracy': array([0.52270004, 0.54497367, 0.53159122, 0.53266074, 0.51002046])}</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0.7797975149562817</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.8762766645119586</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.7797975149562817</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>[0.77979751 1.        ]</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>[1. 0.]</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>[[   0  957]
+ [   0 3389]]</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>{'precision': 0.0, 'recall': 0.0, 'f1-score': 0.0, 'support': 957.0}</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7797975149562817, 'recall': 1.0, 'f1-score': 0.8762766645119586, 'support': 3389.0}</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>{'precision': 0.38989875747814084, 'recall': 0.5, 'f1-score': 0.4381383322559793, 'support': 4346.0}</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6080841643319923, 'recall': 0.7797975149562817, 'f1-score': 0.6833183654006046, 'support': 4346.0}</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Pipeline(steps=[('smote', SMOTE(random_state=42)),
+                ('stack',
+                 StackingClassifier(cv=5,
+                                    estimators=[('svc_cal',
+                                                 CalibratedClassifierCV(cv=3,
+                                                                        estimator=SVC(probability=True))),
+                                                ('rf',
+                                                 RandomForestClassifier(n_estimators=800,
+                                                                        n_jobs=-1,
+                                                                        random_state=42)),
+                                                ('knn',
+                                                 Pipeline(steps=[('standardscaler',
+                                                                  StandardScaler(with_mean=False)),
+                                                                 ('kneighborsclassifier',
+                                                                  KNeighborsC...
+                                                                                                multi_strategy=None,
+                                                                                                n_estimators=400,
+                                                                                                n_jobs=-1,
+                                                                                                num_parallel_tree=None, ...),
+                                                                        method='isotonic')),
+                                                ('sgd_lin',
+                                                 Pipeline(steps=[('standardscaler',
+                                                                  StandardScaler(with_mean=False)),
+                                                                 ('sgdclassifier',
+                                                                  SGDClassifier(loss='log_loss',
+                                                                                max_iter=2000,
+                                                                                random_state=42))]))],
+                                    final_estimator=LogisticRegression(C=0.5,
+                                                                       max_iter=2000),
+                                    n_jobs=-1, stack_method='predict_proba',
+                                    verbose=2))])</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stack_method=predict_proba/stat=['mean_statistics'], passthrough=False, smote=True</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>[0.69310345 0.68124281 0.68929804 0.69390104 0.68699655]</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([14.1000874 , 14.14432049, 13.5542872 , 14.00981021, 14.15084291]), 'score_time': array([1.3415072 , 1.35038853, 1.34168148, 1.30637002, 1.30803227]), 'test_accuracy': array([0.69310345, 0.68124281, 0.68929804, 0.69390104, 0.68699655]), 'test_precision': array([0.78741259, 0.79791976, 0.79310345, 0.7917847 , 0.78481013]), 'test_recall': array([0.83038348, 0.7920354 , 0.81415929, 0.82448378, 0.82422452]), 'test_f1': array([0.80832735, 0.79496669, 0.80349345, 0.80780347, 0.80403458]), 'test_roc_auc': array([0.57471423, 0.58166921, 0.52756799, 0.55466494, 0.55225258]), 'test_average_precision': array([0.82728587, 0.83343721, 0.79127511, 0.79923921, 0.81054914]), 'test_neg_log_loss': array([-0.61368641, -0.63532379, -0.66433494, -0.63764753, -0.62751268]), 'test_neg_brier_score': array([-0.20628564, -0.21689909, -0.22003238, -0.21292106, -0.21095854]), 'test_f1_macro': array([0.51943745, 0.53960221, 0.5308676 , 0.52819552, 0.51344586]), 'test_f1_weighted': array([0.68081733, 0.68271211, 0.68365102, 0.6848918 , 0.67562714]), 'test_balanced_accuracy': array([0.51935841, 0.53999676, 0.5301163 , 0.52742513, 0.51367476])}</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0.6889093419236079</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.8037735849056604</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.790916880891174</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>[0.77979751 0.79091688 1.        ]</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0.8170551785187371</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>[1.         0.81705518 0.        ]</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>[[ 225  732]
+ [ 620 2769]]</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>{'precision': 0.26627218934911245, 'recall': 0.23510971786833856, 'f1-score': 0.24972253052164262, 'support': 957.0}</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>{'precision': 0.790916880891174, 'recall': 0.8170551785187371, 'f1-score': 0.8037735849056604, 'support': 3389.0}</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5285945351201432, 'recall': 0.5260824481935378, 'f1-score': 0.5267480577136515, 'support': 4346.0}</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>{'precision': 0.675388816048617, 'recall': 0.6889093419236079, 'f1-score': 0.6817701658892074, 'support': 4346.0}</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Pipeline(steps=[('smote', SMOTE(random_state=42)),
+                ('stack',
+                 StackingClassifier(cv=5,
+                                    estimators=[('svc_cal',
+                                                 CalibratedClassifierCV(cv=3,
+                                                                        estimator=SVC(probability=True))),
+                                                ('rf',
+                                                 RandomForestClassifier(n_estimators=800,
+                                                                        n_jobs=-1,
+                                                                        random_state=42)),
+                                                ('knn',
+                                                 Pipeline(steps=[('standardscaler',
+                                                                  StandardScaler(with_mean=False)),
+                                                                 ('kneighborsclassifier',
+                                                                  KNeighborsC...
+                                                                                                n_estimators=400,
+                                                                                                n_jobs=-1,
+                                                                                                num_parallel_tree=None, ...),
+                                                                        method='isotonic')),
+                                                ('sgd_lin',
+                                                 Pipeline(steps=[('standardscaler',
+                                                                  StandardScaler(with_mean=False)),
+                                                                 ('sgdclassifier',
+                                                                  SGDClassifier(loss='log_loss',
+                                                                                max_iter=2000,
+                                                                                random_state=42))]))],
+                                    final_estimator=LogisticRegression(C=0.5,
+                                                                       max_iter=2000),
+                                    n_jobs=-1, passthrough=True,
+                                    stack_method='predict_proba', verbose=2))])</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stack_method=predict_proba/stat=['mean_statistics'], passthrough=True, smote=True</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>[0.6954023  0.67433832 0.69159954 0.69620253 0.67548907]</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([16.3627398 , 16.41499686, 16.08151746, 15.96194863, 16.32186341]), 'score_time': array([1.44878054, 1.42010713, 1.40734076, 1.49130774, 1.35953093]), 'test_accuracy': array([0.6954023 , 0.67433832, 0.69159954, 0.69620253, 0.67548907]), 'test_precision': array([0.78881119, 0.80060883, 0.79369628, 0.79403409, 0.78335725]), 'test_recall': array([0.83185841, 0.77581121, 0.81710914, 0.82448378, 0.80649926]), 'test_f1': array([0.8097631 , 0.78801498, 0.80523256, 0.8089725 , 0.79475983]), 'test_roc_auc': array([0.58121313, 0.5843179 , 0.53520518, 0.5570588 , 0.55821486]), 'test_average_precision': array([0.83500613, 0.83662873, 0.80401929, 0.80936645, 0.82140859]), 'test_neg_log_loss': array([-0.6117138 , -0.64519538, -0.6596589 , -0.63762065, -0.62597506]), 'test_neg_brier_score': array([-0.20577875, -0.22140349, -0.21910789, -0.21349964, -0.21166781]), 'test_f1_macro': array([0.52303717, 0.54289087, 0.53245053, 0.53369973, 0.51001728]), 'test_f1_weighted': array([0.68320821, 0.68026192, 0.68532147, 0.68796652, 0.66893573]), 'test_balanced_accuracy': array([0.52270004, 0.54497367, 0.53159122, 0.53266074, 0.51002046])}</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0.6866083755177175</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.8014577259475218</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.7919907807548257</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>[0.77979751 0.79199078 1.        ]</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0.8111537326645029</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>[1.         0.81115373 0.        ]</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>[0 1]</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>[[ 235  722]
+ [ 640 2749]]</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>{'precision': 0.26857142857142857, 'recall': 0.24555903866248693, 'f1-score': 0.25655021834061137, 'support': 957.0}</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7919907807548257, 'recall': 0.8111537326645029, 'f1-score': 0.8014577259475218, 'support': 3389.0}</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>{'precision': 0.5302811046631271, 'recall': 0.5283563856634949, 'f1-score': 0.5290039721440666, 'support': 4346.0}</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6767325386840685, 'recall': 0.6866083755177175, 'f1-score': 0.6814677386535013, 'support': 4346.0}</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Pipeline(steps=[('smote', SMOTE(random_state=42)),
+                ('stack',
+                 StackingClassifier(cv=5,
+                                    estimators=[('svc_cal',
+                                                 CalibratedClassifierCV(cv=3,
+                                                                        estimator=SVC(probability=True))),
+                                                ('rf',
+                                                 RandomForestClassifier(n_estimators=800,
+                                                                        n_jobs=-1,
+                                                                        random_state=42)),
+                                                ('knn',
+                                                 Pipeline(steps=[('standardscaler',
+                                                                  StandardScaler(with_mean=False)),
+                                                                 ('kneighborsclassifier',
+                                                                  KNeighborsC...
+                                                                                                multi_strategy=None,
+                                                                                                n_estimators=400,
+                                                                                                n_jobs=-1,
+                                                                                                num_parallel_tree=None, ...),
+                                                                        method='isotonic')),
+                                                ('sgd_lin',
+                                                 Pipeline(steps=[('standardscaler',
+                                                                  StandardScaler(with_mean=False)),
+                                                                 ('sgdclassifier',
+                                                                  SGDClassifier(loss='log_loss',
+                                                                                max_iter=2000,
+                                                                                random_state=42))]))],
+                                    final_estimator=LogisticRegression(C=0.5,
+                                                                       max_iter=2000),
+                                    n_jobs=-1, stack_method='predict_proba',
+                                    verbose=2))])</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stack_method=predict_proba/stat=['mean_statistics'], passthrough=False, smote=True</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>[0.69310345 0.68124281 0.68929804 0.69390104 0.68699655]</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([ 76.14938474,  81.798455  ,  77.59281373, 101.28522754,
+        80.59925151]), 'score_time': array([4.07967114, 4.07147408, 4.07798076, 4.27109361, 4.21923375]), 'test_accuracy': array([0.69310345, 0.68124281, 0.68929804, 0.69390104, 0.68699655]), 'test_precision': array([0.78741259, 0.79791976, 0.79310345, 0.7917847 , 0.78481013]), 'test_recall': array([0.83038348, 0.7920354 , 0.81415929, 0.82448378, 0.82422452]), 'test_f1': array([0.80832735, 0.79496669, 0.80349345, 0.80780347, 0.80403458]), 'test_roc_auc': array([0.57471423, 0.58166921, 0.52756799, 0.55466494, 0.55225258]), 'test_average_precision': array([0.82728587, 0.83343721, 0.79127511, 0.79923921, 0.81054914]), 'test_neg_log_loss': array([-0.61368641, -0.63532379, -0.66433494, -0.63764753, -0.62751268]), 'test_neg_brier_score': array([-0.20628564, -0.21689909, -0.22003238, -0.21292106, -0.21095854]), 'test_f1_macro': array([0.51943745, 0.53960221, 0.5308676 , 0.52819552, 0.51344586]), 'test_f1_weighted': array([0.68081733, 0.68271211, 0.68365102, 0.6848918 , 0.67562714]), 'test_balanced_accuracy': array([0.51935841, 0.53999676, 0.5301163 , 0.52742513, 0.51367476])}</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0.7797975149562817</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>[0.87627666 0.        ]</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>0.7797975149562817</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>[0.77979751 1.        ]</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>[1. 0.]</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>[[   0  957]
+ [   0 3389]]</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>{'precision': 0.38989875747814084, 'recall': 0.5, 'f1-score': 0.4381383322559793, 'support': 4346.0}</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6080841643319923, 'recall': 0.7797975149562817, 'f1-score': 0.6833183654006046, 'support': 4346.0}</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>[0.87627666 0.        ]</t>
+        </is>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>{'precision': 0.0, 'recall': 0.0, 'f1-score': 0.0, 'support': 957.0}</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7797975149562817, 'recall': 1.0, 'f1-score': 0.8762766645119586, 'support': 3389.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Pipeline(steps=[('smote', SMOTE(random_state=42)),
+                ('stack',
+                 StackingClassifier(cv=5,
+                                    estimators=[('svc_cal',
+                                                 CalibratedClassifierCV(cv=3,
+                                                                        estimator=SVC(probability=True))),
+                                                ('rf',
+                                                 RandomForestClassifier(n_estimators=800,
+                                                                        n_jobs=-1,
+                                                                        random_state=42)),
+                                                ('knn',
+                                                 Pipeline(steps=[('standardscaler',
+                                                                  StandardScaler(with_mean=False)),
+                                                                 ('kneighborsclassifier',
+                                                                  KNeighborsC...
+                                                                                                n_estimators=400,
+                                                                                                n_jobs=-1,
+                                                                                                num_parallel_tree=None, ...),
+                                                                        method='isotonic')),
+                                                ('sgd_lin',
+                                                 Pipeline(steps=[('standardscaler',
+                                                                  StandardScaler(with_mean=False)),
+                                                                 ('sgdclassifier',
+                                                                  SGDClassifier(loss='log_loss',
+                                                                                max_iter=2000,
+                                                                                random_state=42))]))],
+                                    final_estimator=LogisticRegression(C=0.5,
+                                                                       max_iter=2000),
+                                    n_jobs=-1, passthrough=True,
+                                    stack_method='predict_proba', verbose=2))])</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stack_method=predict_proba/stat=['mean_statistics'], passthrough=True, smote=True</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>[0.6954023  0.67433832 0.69159954 0.69620253 0.67548907]</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([20.64193654, 21.57825804, 21.67785406, 20.52125502, 21.90608406]), 'score_time': array([2.09047103, 2.32089496, 2.18854475, 2.10921693, 2.1553061 ]), 'test_accuracy': array([0.6954023 , 0.67433832, 0.69159954, 0.69620253, 0.67548907]), 'test_precision': array([0.78881119, 0.80060883, 0.79369628, 0.79403409, 0.78335725]), 'test_recall': array([0.83185841, 0.77581121, 0.81710914, 0.82448378, 0.80649926]), 'test_f1': array([0.8097631 , 0.78801498, 0.80523256, 0.8089725 , 0.79475983]), 'test_roc_auc': array([0.58121313, 0.5843179 , 0.53520518, 0.5570588 , 0.55821486]), 'test_average_precision': array([0.83500613, 0.83662873, 0.80401929, 0.80936645, 0.82140859]), 'test_neg_log_loss': array([-0.6117138 , -0.64519538, -0.6596589 , -0.63762065, -0.62597506]), 'test_neg_brier_score': array([-0.20577875, -0.22140349, -0.21910789, -0.21349964, -0.21166781]), 'test_f1_macro': array([0.52303717, 0.54289087, 0.53245053, 0.53369973, 0.51001728]), 'test_f1_weighted': array([0.68320821, 0.68026192, 0.68532147, 0.68796652, 0.66893573]), 'test_balanced_accuracy': array([0.52270004, 0.54497367, 0.53159122, 0.53266074, 0.51002046])}</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0.7797975149562817</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>[0.87627666 0.        ]</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>0.7797975149562817</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>[0.77979751 1.        ]</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>[1. 0.]</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>[[   0  957]
+ [   0 3389]]</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>{'precision': 0.38989875747814084, 'recall': 0.5, 'f1-score': 0.4381383322559793, 'support': 4346.0}</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6080841643319923, 'recall': 0.7797975149562817, 'f1-score': 0.6833183654006046, 'support': 4346.0}</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>[0.87627666 0.        ]</t>
+        </is>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>{'precision': 0.0, 'recall': 0.0, 'f1-score': 0.0, 'support': 957.0}</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7797975149562817, 'recall': 1.0, 'f1-score': 0.8762766645119586, 'support': 3389.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Pipeline(steps=[('smote', SMOTE(random_state=42)),
+                ('stack',
+                 StackingClassifier(cv=5,
+                                    estimators=[('svc_cal',
+                                                 CalibratedClassifierCV(cv=3,
+                                                                        estimator=SVC(probability=True))),
+                                                ('rf',
+                                                 RandomForestClassifier(n_estimators=800,
+                                                                        n_jobs=-1,
+                                                                        random_state=42)),
+                                                ('knn',
+                                                 Pipeline(steps=[('standardscaler',
+                                                                  StandardScaler(with_mean=False)),
+                                                                 ('kneighborsclassifier',
+                                                                  KNeighborsC...
+                                                                                                multi_strategy=None,
+                                                                                                n_estimators=400,
+                                                                                                n_jobs=-1,
+                                                                                                num_parallel_tree=None, ...),
+                                                                        method='isotonic')),
+                                                ('sgd_lin',
+                                                 Pipeline(steps=[('standardscaler',
+                                                                  StandardScaler(with_mean=False)),
+                                                                 ('sgdclassifier',
+                                                                  SGDClassifier(loss='log_loss',
+                                                                                max_iter=2000,
+                                                                                random_state=42))]))],
+                                    final_estimator=LogisticRegression(C=0.5,
+                                                                       max_iter=2000),
+                                    n_jobs=-1, stack_method='predict_proba',
+                                    verbose=2))])</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stack_method=predict_proba/stat=['mean_statistics'], passthrough=False, smote=True</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>[0.69310345 0.68124281 0.68929804 0.69390104 0.68699655]</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([21.29005933, 22.094486  , 21.02675724, 22.05957198, 22.41319013]), 'score_time': array([2.22497869, 2.24618578, 2.23116398, 2.20355821, 2.26780033]), 'test_accuracy': array([0.69310345, 0.68124281, 0.68929804, 0.69390104, 0.68699655]), 'test_precision': array([0.78741259, 0.79791976, 0.79310345, 0.7917847 , 0.78481013]), 'test_recall': array([0.83038348, 0.7920354 , 0.81415929, 0.82448378, 0.82422452]), 'test_f1': array([0.80832735, 0.79496669, 0.80349345, 0.80780347, 0.80403458]), 'test_roc_auc': array([0.57471423, 0.58166921, 0.52756799, 0.55466494, 0.55225258]), 'test_average_precision': array([0.82728587, 0.83343721, 0.79127511, 0.79923921, 0.81054914]), 'test_neg_log_loss': array([-0.61368641, -0.63532379, -0.66433494, -0.63764753, -0.62751268]), 'test_neg_brier_score': array([-0.20628564, -0.21689909, -0.22003238, -0.21292106, -0.21095854]), 'test_f1_macro': array([0.51943745, 0.53960221, 0.5308676 , 0.52819552, 0.51344586]), 'test_f1_weighted': array([0.68081733, 0.68271211, 0.68365102, 0.6848918 , 0.67562714]), 'test_balanced_accuracy': array([0.51935841, 0.53999676, 0.5301163 , 0.52742513, 0.51367476])}</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0.7797975149562817</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0.8762766645119586</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>0.7797975149562817</v>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>0.0527417705615808</v>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>[[   0  957]
+ [   0 3389]]</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>{'precision': 0.38989875747814084, 'recall': 0.5, 'f1-score': 0.4381383322559793, 'support': 4346.0}</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6080841643319923, 'recall': 0.7797975149562817, 'f1-score': 0.6833183654006046, 'support': 4346.0}</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>{'precision': 0.0, 'recall': 0.0, 'f1-score': 0.0, 'support': 957.0}</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7797975149562817, 'recall': 1.0, 'f1-score': 0.8762766645119586, 'support': 3389.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Pipeline(steps=[('smote', SMOTE(random_state=42)),
+                ('stack',
+                 StackingClassifier(cv=5,
+                                    estimators=[('svc_cal',
+                                                 CalibratedClassifierCV(cv=3,
+                                                                        estimator=SVC(probability=True))),
+                                                ('rf',
+                                                 RandomForestClassifier(n_estimators=800,
+                                                                        n_jobs=-1,
+                                                                        random_state=42)),
+                                                ('knn',
+                                                 Pipeline(steps=[('standardscaler',
+                                                                  StandardScaler(with_mean=False)),
+                                                                 ('kneighborsclassifier',
+                                                                  KNeighborsC...
+                                                                                                n_estimators=400,
+                                                                                                n_jobs=-1,
+                                                                                                num_parallel_tree=None, ...),
+                                                                        method='isotonic')),
+                                                ('sgd_lin',
+                                                 Pipeline(steps=[('standardscaler',
+                                                                  StandardScaler(with_mean=False)),
+                                                                 ('sgdclassifier',
+                                                                  SGDClassifier(loss='log_loss',
+                                                                                max_iter=2000,
+                                                                                random_state=42))]))],
+                                    final_estimator=LogisticRegression(C=0.5,
+                                                                       max_iter=2000),
+                                    n_jobs=-1, passthrough=True,
+                                    stack_method='predict_proba', verbose=2))])</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stack_method=predict_proba/stat=['mean_statistics'], passthrough=True, smote=True</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>[0.6954023  0.67433832 0.69159954 0.69620253 0.67548907]</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>{'fit_time': array([39.94671369, 39.9442935 , 39.09432292, 39.53138185, 39.76131272]), 'score_time': array([3.97397542, 3.966187  , 4.0245018 , 3.93901443, 3.94799185]), 'test_accuracy': array([0.6954023 , 0.67433832, 0.69159954, 0.69620253, 0.67548907]), 'test_precision': array([0.78881119, 0.80060883, 0.79369628, 0.79403409, 0.78335725]), 'test_recall': array([0.83185841, 0.77581121, 0.81710914, 0.82448378, 0.80649926]), 'test_f1': array([0.8097631 , 0.78801498, 0.80523256, 0.8089725 , 0.79475983]), 'test_roc_auc': array([0.58121313, 0.5843179 , 0.53520518, 0.5570588 , 0.55821486]), 'test_average_precision': array([0.83500613, 0.83662873, 0.80401929, 0.80936645, 0.82140859]), 'test_neg_log_loss': array([-0.6117138 , -0.64519538, -0.6596589 , -0.63762065, -0.62597506]), 'test_neg_brier_score': array([-0.20577875, -0.22140349, -0.21910789, -0.21349964, -0.21166781]), 'test_f1_macro': array([0.52303717, 0.54289087, 0.53245053, 0.53369973, 0.51001728]), 'test_f1_weighted': array([0.68320821, 0.68026192, 0.68532147, 0.68796652, 0.66893573]), 'test_balanced_accuracy': array([0.52270004, 0.54497367, 0.53159122, 0.53266074, 0.51002046])}</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0.7797975149562817</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0.8762766645119586</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>0.7797975149562817</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0.046065247297054905</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>[[   0  957]
+ [   0 3389]]</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>{'precision': 0.38989875747814084, 'recall': 0.5, 'f1-score': 0.4381383322559793, 'support': 4346.0}</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>{'precision': 0.6080841643319923, 'recall': 0.7797975149562817, 'f1-score': 0.6833183654006046, 'support': 4346.0}</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>{'precision': 0.0, 'recall': 0.0, 'f1-score': 0.0, 'support': 957.0}</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>{'precision': 0.7797975149562817, 'recall': 1.0, 'f1-score': 0.8762766645119586, 'support': 3389.0}</t>
         </is>
       </c>
     </row>

--- a/src/service_ia/training/version_1/fit/report_fit_grid.xlsx
+++ b/src/service_ia/training/version_1/fit/report_fit_grid.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Report BEST FIT" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Report ML FIT" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report BEST FIT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report ML FIT" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -882,10 +882,8 @@
           <t>{'bootstrap': False, 'class_weight': 'balanced', 'max_depth': None, 'max_features': 'log2', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 4272}</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0.7737480219962757</t>
-        </is>
+      <c r="F11" t="n">
+        <v>0.7737480219962757</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -894,7 +892,41 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n"/>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stat=['mean_statistics']</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>{'under_over_1_5', 'mean_expected_goals_away_stat', 'mean_expected_goals_home_stat'}</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>DecisionTreeClassifier(class_weight='balanced', criterion='log_loss')</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>{'class_weight': 'balanced', 'criterion': 'log_loss', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0.6888636363636363</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>make_scorer(accuracy_score, response_method='predict')</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -1133,11 +1165,6 @@
           <t>{'precision': 0.6866507013813268, 'recall': 0.7650615417836321, 'f1-score': 0.6837975679350144, 'support': 4631.0}</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3" customFormat="1" s="1">
       <c r="A3" t="inlineStr">
@@ -1225,11 +1252,6 @@
           <t>{'precision': 0.6623329325431794, 'recall': 0.7296480241848413, 'f1-score': 0.683542263512542, 'support': 4631.0}</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4" customFormat="1" s="1">
       <c r="A4" t="inlineStr">
@@ -1318,11 +1340,6 @@
           <t>{'precision': 0.7288424514725529, 'recall': 0.2548045778449579, 'f1-score': 0.14255103964891733, 'support': 4631.0}</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5" customFormat="1" s="1">
       <c r="A5" t="inlineStr">
@@ -1410,11 +1427,6 @@
           <t>{'precision': 0.7150099658494417, 'recall': 0.26473763765925284, 'f1-score': 0.16550099488525769, 'support': 4631.0}</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6" customFormat="1" s="1">
       <c r="A6" t="inlineStr">
@@ -1503,11 +1515,6 @@
           <t>{'precision': 0.6957822195083141, 'recall': 0.4806737205787087, 'f1-score': 0.5127011190874851, 'support': 4631.0}</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7" customFormat="1" s="1">
       <c r="A7" t="inlineStr">
@@ -1595,11 +1602,6 @@
           <t>{'precision': 0.6695546817147678, 'recall': 0.4748434463398834, 'f1-score': 0.510610522863405, 'support': 4631.0}</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8" customFormat="1" s="1">
       <c r="A8" t="inlineStr">
@@ -1688,11 +1690,6 @@
           <t>{'precision': 0.7295244827524134, 'recall': 0.25372489743036064, 'f1-score': 0.14014118933018369, 'support': 4631.0}</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9" customFormat="1" s="1">
       <c r="A9" t="inlineStr">
@@ -1780,11 +1777,6 @@
           <t>{'precision': 0.7065979775883607, 'recall': 0.2988555387605269, 'f1-score': 0.23669459475071708, 'support': 4631.0}</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10" customFormat="1" s="1">
       <c r="A10" t="inlineStr">
@@ -1873,11 +1865,6 @@
           <t>{'precision': 0.6813324271200106, 'recall': 0.7691643273591017, 'f1-score': 0.6729361570919801, 'support': 4631.0}</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11" customFormat="1" s="1">
       <c r="A11" t="inlineStr">
@@ -1965,11 +1952,6 @@
           <t>{'precision': 0.6568120599882818, 'recall': 0.7620384366227597, 'f1-score': 0.6748398446573446, 'support': 4631.0}</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12" customFormat="1" s="1">
       <c r="A12" t="inlineStr">
@@ -2058,11 +2040,6 @@
           <t>{'precision': 0.6528703003773298, 'recall': 0.6519484160358845, 'f1-score': 0.651422892476994, 'support': 7134.0}</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13" customFormat="1" s="1">
       <c r="A13" t="inlineStr">
@@ -2150,11 +2127,6 @@
           <t>{'precision': 0.7157403568093786, 'recall': 0.7155873282870759, 'f1-score': 0.7155368845837681, 'support': 7134.0}</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14" customFormat="1" s="1">
       <c r="A14" t="inlineStr">
@@ -2243,11 +2215,6 @@
           <t>{'precision': 0.6285593409540101, 'recall': 0.6284810126582279, 'f1-score': 0.6284244145103419, 'support': 6320.0}</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15" customFormat="1" s="1">
       <c r="A15" t="inlineStr">
@@ -2335,11 +2302,6 @@
           <t>{'precision': 0.6739083363406712, 'recall': 0.6737341772151899, 'f1-score': 0.6736524726788272, 'support': 6320.0}</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16" customFormat="1" s="1">
       <c r="A16" t="inlineStr">
@@ -2429,11 +2391,6 @@
           <t>{'precision': 0.5681391886055531, 'recall': 0.5690435766836446, 'f1-score': 0.567726036345396, 'support': 10602.0}</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17" customFormat="1" s="1">
       <c r="A17" t="inlineStr">
@@ -2522,11 +2479,6 @@
           <t>{'precision': 0.522408609215056, 'recall': 0.5230145255612149, 'f1-score': 0.5225626716031113, 'support': 10602.0}</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
     </row>
     <row r="18" customFormat="1" s="1">
       <c r="A18" t="inlineStr">
@@ -2636,11 +2588,6 @@
           <t>{'precision': 0.729583981950156, 'recall': 0.7786542923433875, 'f1-score': 0.6837230380920101, 'support': 4310.0}</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
     </row>
     <row r="19" customFormat="1" s="1">
       <c r="A19" t="inlineStr">
@@ -2750,11 +2697,6 @@
           <t>{'precision': 0.7830108344796101, 'recall': 0.78301043219076, 'f1-score': 0.7830103550801832, 'support': 6710.0}</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
     </row>
     <row r="20" customFormat="1" s="1">
       <c r="A20" t="inlineStr">
@@ -2867,11 +2809,6 @@
           <t>{'precision': 0.7921720095583389, 'recall': 0.7919523099850969, 'f1-score': 0.7919131921184008, 'support': 6710.0}</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2984,11 +2921,6 @@
           <t>{'precision': 0.580791471370872, 'recall': 0.5720574162679426, 'f1-score': 0.5708606138490143, 'support': 5225.0}</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3100,11 +3032,6 @@
           <t>{'precision': 0.5907217618144199, 'recall': 0.5789473684210527, 'f1-score': 0.5764566629571547, 'support': 5225.0}</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3218,11 +3145,6 @@
           <t>{'precision': 0.6080841643319923, 'recall': 0.7797975149562817, 'f1-score': 0.6833183654006046, 'support': 4346.0}</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3335,11 +3257,6 @@
           <t>{'precision': 0.6080841643319923, 'recall': 0.7797975149562817, 'f1-score': 0.6833183654006046, 'support': 4346.0}</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3453,11 +3370,6 @@
           <t>{'precision': 0.675388816048617, 'recall': 0.6889093419236079, 'f1-score': 0.6817701658892074, 'support': 4346.0}</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3570,11 +3482,6 @@
           <t>{'precision': 0.6767325386840685, 'recall': 0.6866083755177175, 'f1-score': 0.6814677386535013, 'support': 4346.0}</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3671,8 +3578,6 @@
  [   0 3389]]</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
           <t>{'precision': 0.38989875747814084, 'recall': 0.5, 'f1-score': 0.4381383322559793, 'support': 4346.0}</t>
@@ -3798,8 +3703,6 @@
  [   0 3389]]</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
           <t>{'precision': 0.38989875747814084, 'recall': 0.5, 'f1-score': 0.4381383322559793, 'support': 4346.0}</t>
@@ -3899,23 +3802,18 @@
       <c r="H29" t="n">
         <v>0.7797975149562817</v>
       </c>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
         <v>0.0527417705615808</v>
       </c>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>[[   0  957]
  [   0 3389]]</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
           <t>{'precision': 0.38989875747814084, 'recall': 0.5, 'f1-score': 0.4381383322559793, 'support': 4346.0}</t>
@@ -3926,9 +3824,6 @@
           <t>{'precision': 0.6080841643319923, 'recall': 0.7797975149562817, 'f1-score': 0.6833183654006046, 'support': 4346.0}</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
           <t>{'precision': 0.0, 'recall': 0.0, 'f1-score': 0.0, 'support': 957.0}</t>
@@ -4010,27 +3905,22 @@
           <t>0.7797975149562817</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>0.046065247297054905</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>[[   0  957]
  [   0 3389]]</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
           <t>{'precision': 0.38989875747814084, 'recall': 0.5, 'f1-score': 0.4381383322559793, 'support': 4346.0}</t>
@@ -4041,9 +3931,6 @@
           <t>{'precision': 0.6080841643319923, 'recall': 0.7797975149562817, 'f1-score': 0.6833183654006046, 'support': 4346.0}</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr">
         <is>
           <t>{'precision': 0.0, 'recall': 0.0, 'f1-score': 0.0, 'support': 957.0}</t>

--- a/src/service_ia/training/version_1/fit/report_fit_grid.xlsx
+++ b/src/service_ia/training/version_1/fit/report_fit_grid.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report BEST FIT" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report ML FIT" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Report BEST FIT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Report ML FIT" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.109375" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -467,37 +467,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>features</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>best_estimator</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>best_params</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>best_scorer</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>scorer</t>
         </is>
@@ -895,10 +895,8 @@
           <t>{'class_weight': 'balanced', 'criterion': 'log_loss', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0.6888636363636363</t>
-        </is>
+      <c r="F12" t="n">
+        <v>0.6888636363636363</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -907,16 +905,237 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n"/>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_1_5/stat=['mean_statistics']/smote=True/scaler=True</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>['mean_under', 'mean_over', 'mean_expected_goals_home_stat', 'mean_expected_goals_away_stat']</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Pipeline(steps=[('smote', SMOTE(random_state=42)), ('scaler', StandardScaler()),
+                ('model', DecisionTreeClassifier(max_features='sqrt'))])</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>{'model__class_weight': None, 'model__criterion': 'gini', 'model__max_depth': None, 'model__max_features': 'sqrt', 'model__min_samples_leaf': 1, 'model__min_samples_split': 2}</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.6284745762711864</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>make_scorer(accuracy_score, response_method='predict')</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n"/>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_1_5/stat=['mean_statistics']/smote=True/scaler=True</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>['std_under', 'std_over', 'mean_expected_goals_home_stat', 'mean_expected_goals_away_stat']</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Pipeline(steps=[('smote', SMOTE(random_state=42)), ('scaler', StandardScaler()),
+                ('model',
+                 DecisionTreeClassifier(class_weight='balanced',
+                                        criterion='log_loss',
+                                        max_features='log2'))])</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>{'model__class_weight': 'balanced', 'model__criterion': 'log_loss', 'model__max_depth': None, 'model__max_features': 'log2', 'model__min_samples_leaf': 1, 'model__min_samples_split': 2}</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.6043737922705315</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>make_scorer(accuracy_score, response_method='predict')</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n"/>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_2_5/stat=['mean_statistics']/smote=True/scaler=True</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>['mean_under', 'mean_over', 'mean_expected_goals_home_stat', 'mean_expected_goals_away_stat']</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Pipeline(steps=[('smote', SMOTE(random_state=42)), ('scaler', StandardScaler()),
+                ('model',
+                 DecisionTreeClassifier(criterion='log_loss', max_depth=5,
+                                        max_features='log2', min_samples_leaf=2,
+                                        min_samples_split=5))])</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>{'model__class_weight': None, 'model__criterion': 'log_loss', 'model__max_depth': 5, 'model__max_features': 'log2', 'model__min_samples_leaf': 2, 'model__min_samples_split': 5}</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.5857876115414051</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>make_scorer(accuracy_score, response_method='predict')</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n"/>
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_2_5/stat=['mean_statistics']/smote=True/scaler=True</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>['std_under', 'std_over', 'mean_expected_goals_home_stat', 'mean_expected_goals_away_stat']</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Pipeline(steps=[('smote', SMOTE(random_state=42)), ('scaler', StandardScaler()),
+                ('model',
+                 DecisionTreeClassifier(criterion='entropy', max_depth=5,
+                                        max_features='sqrt',
+                                        min_samples_leaf=2))])</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>{'model__class_weight': None, 'model__criterion': 'entropy', 'model__max_depth': 5, 'model__max_features': 'sqrt', 'model__min_samples_leaf': 2, 'model__min_samples_split': 2}</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.5606592740188858</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>make_scorer(accuracy_score, response_method='predict')</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>t=mean/event=under_over_3_5/stat=['mean_statistics']/smote=True/scaler=True</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>['mean_under', 'mean_over', 'mean_expected_goals_home_stat', 'mean_expected_goals_away_stat']</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Pipeline(steps=[('smote', SMOTE(random_state=42)), ('scaler', StandardScaler()),
+                ('model',
+                 DecisionTreeClassifier(criterion='log_loss', max_depth=5,
+                                        max_features='log2',
+                                        min_samples_split=10))])</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>{'model__class_weight': None, 'model__criterion': 'log_loss', 'model__max_depth': 5, 'model__max_features': 'log2', 'model__min_samples_leaf': 1, 'model__min_samples_split': 10}</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0.6115646258503402</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>make_scorer(accuracy_score, response_method='predict')</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>t=std/event=under_over_3_5/stat=['mean_statistics']/smote=True/scaler=True</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>['std_under', 'std_over', 'mean_expected_goals_home_stat', 'mean_expected_goals_away_stat']</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Pipeline(steps=[('smote', SMOTE(random_state=42)), ('scaler', StandardScaler()),
+                ('model',
+                 DecisionTreeClassifier(criterion='entropy',
+                                        max_features='log2', min_samples_leaf=4,
+                                        min_samples_split=5))])</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>{'model__class_weight': None, 'model__criterion': 'entropy', 'model__max_depth': None, 'model__max_features': 'log2', 'model__min_samples_leaf': 4, 'model__min_samples_split': 5}</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0.5810250121679108</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>make_scorer(accuracy_score, response_method='predict')</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/src/service_ia/training/version_1/fit/report_fit_grid.xlsx
+++ b/src/service_ia/training/version_1/fit/report_fit_grid.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trotta\git\Predict Soccer\ia_predict_soccer\src\service_ia\training\version_1\fit\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trott\git\ia_predict_soccer\src\service_ia\training\version_1\fit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834FACAD-EB26-4E6C-9121-2ABA2F2A87A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2768B2E5-EE66-42EE-ACA4-0FC42754A988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25420" windowHeight="16300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report BEST FIT" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="147">
   <si>
     <t>data</t>
   </si>
@@ -369,24 +369,6 @@
     <t>[0.789375   0.46083333 0.88958333 ... 0.50020833 0.64208333 0.955     ]</t>
   </si>
   <si>
-    <t>0.5</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>0.6655120155877896</t>
-  </si>
-  <si>
-    <t>0.7874301675977654</t>
-  </si>
-  <si>
-    <t>0.7824035525950597</t>
-  </si>
-  <si>
-    <t>0.7849088124738967</t>
-  </si>
-  <si>
     <t>[[ 255  761]
  [ 784 2819]]</t>
   </si>
@@ -404,13 +386,668 @@
        1.       ]), 'tpr': array([0.        , 0.00444074, 0.00527338, ..., 0.99916736, 0.99916736,
        1.        ]), 'thresholds': array([           inf, 1.00000000e+00, 9.99375000e-01, ...,
        2.14583333e-02, 1.25000000e-02, 8.33333333e-04]), 'roc_auc': np.float64(0.5414613751445099)}</t>
+  </si>
+  <si>
+    <t>StackingClassifier(cv=5,
+                   estimators=[('rf',
+                                Pipeline(steps=[('smote',
+                                                 SMOTE(random_state=42)),
+                                                ('model',
+                                                 RandomForestClassifier(max_depth=10,
+                                                                        max_features='log2',
+                                                                        min_samples_leaf=4,
+                                                                        n_estimators=400,
+                                                                        n_jobs=-1,
+                                                                        random_state=42))])),
+                               ('svc',
+                                Pipeline(steps=[('scaler', StandardScaler()),
+                                                ('smote',
+                                                 SMOTE(random_state=42)),
+                                                ('model',
+                                                 SVC(C=0.21544346900318834,
+                                                     gamma=1....
+                                                 AdaBoostClassifier(algorithm='SAMME',
+                                                                    learning_rate=0.5,
+                                                                    n_estimators=800,
+                                                                    random_state=42))])),
+                               ('gbc',
+                                Pipeline(steps=[('smote',
+                                                 SMOTE(random_state=42)),
+                                                ('model',
+                                                 GradientBoostingClassifier(learning_rate=0.05,
+                                                                            n_estimators=200,
+                                                                            random_state=42))]))],
+                   final_estimator=LogisticRegression(C=0.1, max_iter=2000,
+                                                      n_jobs=-1,
+                                                      random_state=42),
+                   n_jobs=-1, stack_method='predict_proba', verbose=2)</t>
+  </si>
+  <si>
+    <t>C:\Users\trott\git\ia_predict_soccer\src\service_ia\training\version_1\fit\best_models\best_mean_under_over_2_5_stacking_predict_proba.pkl</t>
+  </si>
+  <si>
+    <t>t=mean/event=under_over_2_5/stat=['mean_statistics']/smote=True/scaler=True/stack_method=predict_proba/passthrough=False</t>
+  </si>
+  <si>
+    <t>[0.55515371 0.60216998 0.59493671 0.58190045 0.56832579]</t>
+  </si>
+  <si>
+    <t>{'fit_time': array([9.80370092, 9.96341729, 9.53313637, 9.80087423, 9.9853375 ]), 'score_time': array([0.82331991, 0.85319638, 0.88881445, 0.86136413, 0.84529185]), 'test_accuracy': array([0.55515371, 0.60216998, 0.59493671, 0.58190045, 0.56832579]), 'test_precision': array([0.57757296, 0.60186418, 0.60084034, 0.59232955, 0.58970359]), 'test_recall': array([0.63406408, 0.76222597, 0.72466216, 0.70439189, 0.63851351]), 'test_f1': array([0.60450161, 0.67261905, 0.65696784, 0.64351852, 0.61313869]), 'test_roc_auc': array([0.58770451, 0.63523433, 0.62304462, 0.61415033, 0.59171342]), 'test_average_precision': array([0.61287485, 0.65054925, 0.63297551, 0.6319122 , 0.62852057]), 'test_neg_log_loss': array([-0.67882414, -0.66898209, -0.67040755, -0.67282193, -0.67678784]), 'test_neg_brier_score': array([-0.24291792, -0.23806479, -0.23877816, -0.23997008, -0.24196971]), 'test_f1_macro': array([0.54811857, 0.5828533 , 0.5812433 , 0.56902403, 0.56245471]), 'test_f1_weighted': array([0.55219691, 0.5893463 , 0.58658373, 0.57434988, 0.56607827]), 'test_balanced_accuracy': array([0.54900085, 0.58968998, 0.58509373, 0.57246885, 0.56292147])}</t>
+  </si>
+  <si>
+    <t>[0.50780433 0.45742555 0.54648414 ... 0.48741176 0.50399771 0.49665473]</t>
+  </si>
+  <si>
+    <t>[[1157 1409]
+ [ 910 2052]]</t>
+  </si>
+  <si>
+    <t>{'0': {'precision': 0.559748427672956, 'recall': 0.45089633671083396, 'f1-score': 0.49946039283401683, 'support': 2566.0}, '1': {'precision': 0.5928922276798613, 'recall': 0.6927751519243754, 'f1-score': 0.6389537599252686, 'support': 2962.0}, 'accuracy': 0.5804992764109985, 'macro avg': {'precision': 0.5763203276764086, 'recall': 0.5718357443176048, 'f1-score': 0.5692070763796427, 'support': 5528.0}, 'weighted avg': {'precision': 0.5775074608893912, 'recall': 0.5804992764109985, 'f1-score': 0.5742034017566449, 'support': 5528.0}}</t>
+  </si>
+  <si>
+    <t>{'precisions': array([0.53581766, 0.53573367, 0.53564966, ..., 0.        , 0.        ,
+       1.        ]), 'recalls': array([1.        , 0.99966239, 0.99932478, ..., 0.        , 0.        ,
+       0.        ]), 'thresholds': array([0.35650093, 0.3669044 , 0.37123591, ..., 0.73208819, 0.73510846,
+       0.73576816]), 'average_precision': 0.6276983930743818}</t>
+  </si>
+  <si>
+    <t>{'fpr': array([0.00000000e+00, 3.89711613e-04, 7.79423227e-04, ...,
+       9.98441154e-01, 1.00000000e+00, 1.00000000e+00]), 'tpr': array([0.        , 0.        , 0.        , ..., 0.99864956, 0.99864956,
+       1.        ]), 'thresholds': array([       inf, 0.73576816, 0.73510846, ..., 0.37669058, 0.37326407,
+       0.35650093]), 'roc_auc': 0.6088097981025439}</t>
+  </si>
+  <si>
+    <t>StackingClassifier(cv=5,
+                   estimators=[('rf',
+                                Pipeline(steps=[('smote',
+                                                 SMOTE(random_state=42)),
+                                                ('model',
+                                                 RandomForestClassifier(max_depth=10,
+                                                                        max_features='log2',
+                                                                        min_samples_leaf=4,
+                                                                        n_estimators=400,
+                                                                        n_jobs=-1,
+                                                                        random_state=42))])),
+                               ('svc',
+                                Pipeline(steps=[('scaler', StandardScaler()),
+                                                ('smote',
+                                                 SMOTE(random_state=42)),
+                                                ('model',
+                                                 SVC(C=0.21544346900318834,
+                                                     gamma=1....
+                                                                    learning_rate=0.5,
+                                                                    n_estimators=800,
+                                                                    random_state=42))])),
+                               ('gbc',
+                                Pipeline(steps=[('smote',
+                                                 SMOTE(random_state=42)),
+                                                ('model',
+                                                 GradientBoostingClassifier(learning_rate=0.05,
+                                                                            n_estimators=200,
+                                                                            random_state=42))]))],
+                   final_estimator=LogisticRegression(C=0.1, max_iter=2000,
+                                                      n_jobs=-1,
+                                                      random_state=42),
+                   n_jobs=-1, passthrough=True, stack_method='predict_proba',
+                   verbose=2)</t>
+  </si>
+  <si>
+    <t>C:\Users\trott\git\ia_predict_soccer\src\service_ia\training\version_1\fit\best_models\best_mean_under_over_2_5_stacking_predict_proba_pass=True.pkl</t>
+  </si>
+  <si>
+    <t>t=mean/event=under_over_2_5/stat=['mean_statistics']/smote=True/scaler=True/stack_method=predict_proba/passthrough=True</t>
+  </si>
+  <si>
+    <t>[0.5641953  0.61754069 0.60216998 0.58190045 0.57104072]</t>
+  </si>
+  <si>
+    <t>{'fit_time': array([9.68006682, 9.67833567, 9.82814693, 9.31673121, 9.48235917]), 'score_time': array([0.82701635, 0.8462646 , 0.84043908, 0.82811761, 0.84138608]), 'test_accuracy': array([0.5641953 , 0.61754069, 0.60216998, 0.58190045, 0.57104072]), 'test_precision': array([0.58499234, 0.62318841, 0.61143695, 0.5915493 , 0.58939394]), 'test_recall': array([0.64418212, 0.72512648, 0.70439189, 0.70945946, 0.65709459]), 'test_f1': array([0.61316212, 0.67030398, 0.65463108, 0.64516129, 0.62140575]), 'test_roc_auc': array([0.59760559, 0.63859386, 0.62974222, 0.60887862, 0.60601391]), 'test_average_precision': array([0.61688045, 0.65332253, 0.6471556 , 0.62730879, 0.64799913]), 'test_neg_log_loss': array([-0.68003824, -0.66420492, -0.66605553, -0.6744081 , -0.6700699 ]), 'test_neg_brier_score': array([-0.24290578, -0.23561956, -0.23671699, -0.24064632, -0.23898945]), 'test_f1_macro': array([0.55709866, 0.60748783, 0.59277396, 0.56817536, 0.56331248]), 'test_f1_weighted': array([0.56115388, 0.6120315 , 0.5971364 , 0.57367933, 0.56746575]), 'test_balanced_accuracy': array([0.55795851, 0.60915193, 0.59441384, 0.57207866, 0.56441474])}</t>
+  </si>
+  <si>
+    <t>[0.48862559 0.4629365  0.55846463 ... 0.50119961 0.52002709 0.48546771]</t>
+  </si>
+  <si>
+    <t>[[1209 1357]
+ [ 924 2038]]</t>
+  </si>
+  <si>
+    <t>{'0': {'precision': 0.5668073136427567, 'recall': 0.4711613406079501, 'f1-score': 0.5145775696956799, 'support': 2566.0}, '1': {'precision': 0.6002945508100147, 'recall': 0.6880486158001351, 'f1-score': 0.6411829479314142, 'support': 2962.0}, 'accuracy': 0.5873733719247467, 'macro avg': {'precision': 0.5835509322263857, 'recall': 0.5796049782040427, 'f1-score': 0.577880258813547, 'support': 5528.0}, 'weighted avg': {'precision': 0.5847503665532882, 'recall': 0.5873733719247467, 'f1-score': 0.5824149666447112, 'support': 5528.0}}</t>
+  </si>
+  <si>
+    <t>{'precisions': array([0.53581766, 0.5359146 , 0.53583062, ..., 0.5       , 0.        ,
+       1.        ]), 'recalls': array([1.00000000e+00, 1.00000000e+00, 9.99662390e-01, ...,
+       3.37609723e-04, 0.00000000e+00, 0.00000000e+00]), 'thresholds': array([0.14936257, 0.18058891, 0.20008018, ..., 0.93080491, 0.93315974,
+       0.93861447]), 'average_precision': 0.6362656202910865}</t>
+  </si>
+  <si>
+    <t>{'fpr': array([0.00000000e+00, 3.89711613e-04, 3.89711613e-04, ...,
+       9.99610288e-01, 9.99610288e-01, 1.00000000e+00]), 'tpr': array([0.00000000e+00, 0.00000000e+00, 6.75219446e-04, ...,
+       9.98649561e-01, 1.00000000e+00, 1.00000000e+00]), 'thresholds': array([       inf, 0.93861447, 0.93080491, ..., 0.25523719, 0.18058891,
+       0.14936257]), 'roc_auc': 0.6158396061728635}</t>
+  </si>
+  <si>
+    <t>Pipeline(steps=[('smote', SMOTE(random_state=42)),
+                ('model',
+                 RandomForestClassifier(max_depth=10, max_features='log2',
+                                        min_samples_leaf=4, n_jobs=-1,
+                                        verbose=1))])</t>
+  </si>
+  <si>
+    <t>C:\Users\trott\git\ia_predict_soccer\src\service_ia\training\version_1\fit\best_models\best_mean_under_over_2_5_random.pkl</t>
+  </si>
+  <si>
+    <t>t=mean/event=under_over_2_5/stat=['mean_statistics']/smote=True/scaler=True/stat=['mean_statistics']/oob=False</t>
+  </si>
+  <si>
+    <t>[0.54611212 0.59222423 0.57233273 0.5719457  0.55837104]</t>
+  </si>
+  <si>
+    <t>{'fit_time': array([0.23832369, 0.17910504, 0.15346313, 0.15165091, 0.15618086]), 'score_time': array([0.06709385, 0.05779958, 0.06562018, 0.05509567, 0.05780196]), 'test_accuracy': array([0.539783  , 0.58860759, 0.56329114, 0.57375566, 0.56289593]), 'test_precision': array([0.58015267, 0.63018868, 0.60380952, 0.62027833, 0.60341556]), 'test_recall': array([0.51264755, 0.56323777, 0.53547297, 0.52702703, 0.53716216]), 'test_f1': array([0.54431513, 0.59483526, 0.56759176, 0.56986301, 0.56836461]), 'test_roc_auc': array([0.56283345, 0.61727957, 0.59880114, 0.59931971, 0.57707708]), 'test_average_precision': array([0.59659217, 0.63089749, 0.61599856, 0.62576206, 0.60298851]), 'test_neg_log_loss': array([-0.69899057, -0.67407423, -0.68008079, -0.68111197, -0.69117445]), 'test_neg_brier_score': array([-0.25175605, -0.24044877, -0.24345211, -0.24382878, -0.24859551]), 'test_f1_macro': array([0.53973747, 0.58851038, 0.56324794, 0.57372074, 0.56282575]), 'test_f1_weighted': array([0.54006859, 0.58896787, 0.56355428, 0.57344494, 0.56322174]), 'test_balanced_accuracy': array([0.54189883, 0.59058575, 0.56540186, 0.57735367, 0.56487738])}</t>
+  </si>
+  <si>
+    <t>[0.53113131 0.37423979 0.47952698 ... 0.40891789 0.45956577 0.47764416]</t>
+  </si>
+  <si>
+    <t>[[1522 1044]
+ [1341 1621]]</t>
+  </si>
+  <si>
+    <t>{'0': {'precision': 0.5316101990918617, 'recall': 0.593141075604053, 'f1-score': 0.5606925769018235, 'support': 2566.0}, '1': {'precision': 0.6082551594746717, 'recall': 0.5472653612424038, 'f1-score': 0.576150701972632, 'support': 2962.0}, 'accuracy': 0.5685600578871202, 'macro avg': {'precision': 0.5699326792832666, 'recall': 0.5702032184232284, 'f1-score': 0.5684216394372277, 'support': 5528.0}, 'weighted avg': {'precision': 0.5726779220755598, 'recall': 0.5685600578871202, 'f1-score': 0.5689753132367972, 'support': 5528.0}}</t>
+  </si>
+  <si>
+    <t>{'precisions': array([0.53581766, 0.5359146 , 0.53601158, ..., 1.        , 1.        ,
+       1.        ]), 'recalls': array([1.00000000e+00, 1.00000000e+00, 1.00000000e+00, ...,
+       6.75219446e-04, 3.37609723e-04, 0.00000000e+00]), 'thresholds': array([0.13949003, 0.14964631, 0.14979549, ..., 0.89858344, 0.89949674,
+       0.90537624]), 'average_precision': 0.6141977139600322}</t>
+  </si>
+  <si>
+    <t>{'fpr': array([0.        , 0.        , 0.        , ..., 0.99766173, 0.99766173,
+       1.        ]), 'tpr': array([0.00000000e+00, 3.37609723e-04, 1.01282917e-03, ...,
+       9.99662390e-01, 1.00000000e+00, 1.00000000e+00]), 'thresholds': array([       inf, 0.90537624, 0.89858344, ..., 0.17249821, 0.1686713 ,
+       0.13949003]), 'roc_auc': 0.5906788665786373}</t>
+  </si>
+  <si>
+    <t>Pipeline(steps=[('smote', SMOTE(random_state=42)),
+                ('model',
+                 XGBClassifier(base_score=None, booster=None, callbacks=None,
+                               colsample_bylevel=None, colsample_bynode=None,
+                               colsample_bytree=1.0, device=None,
+                               early_stopping_rounds=None,
+                               enable_categorical=False, eval_metric=None,
+                               feature_types=None, feature_weights=None,
+                               gamma=None, grow_policy=None,
+                               importance_type=None,
+                               interaction_constraints=None, learning_rate=0.2,
+                               max_bin=None, max_cat_threshold=None,
+                               max_cat_to_onehot=None, max_delta_step=None,
+                               max_depth=3, max_leaves=None,
+                               min_child_weight=None, missing=nan,
+                               monotone_constraints=None, multi_strategy=None,
+                               n_estimators=100, n_jobs=None,
+                               num_parallel_tree=None, ...))])</t>
+  </si>
+  <si>
+    <t>C:\Users\trott\git\ia_predict_soccer\src\service_ia\training\version_1\fit\best_models\best_mean_under_over_2_5_xgb.pkl</t>
+  </si>
+  <si>
+    <t>[0.53435805 0.55877034 0.5596745  0.56923077 0.54932127]</t>
+  </si>
+  <si>
+    <t>{'fit_time': array([0.04281402, 0.03420687, 0.03523731, 0.04134083, 0.04690862]), 'score_time': array([0.01554227, 0.01210284, 0.01690745, 0.01810169, 0.01306462]), 'test_accuracy': array([0.53435805, 0.55877034, 0.5596745 , 0.56923077, 0.54932127]), 'test_precision': array([0.57142857, 0.59776536, 0.59562842, 0.61328125, 0.58483755]), 'test_recall': array([0.52613828, 0.54131535, 0.55236486, 0.53040541, 0.5472973 ]), 'test_f1': array([0.54784899, 0.56814159, 0.57318142, 0.56884058, 0.56544503]), 'test_roc_auc': array([0.56171744, 0.59845698, 0.58522518, 0.60158843, 0.56088654]), 'test_average_precision': array([0.6003621 , 0.61477453, 0.6080669 , 0.63127366, 0.58382914]), 'test_neg_log_loss': array([-0.70489705, -0.68381432, -0.69126442, -0.68135423, -0.70520141]), 'test_neg_brier_score': array([-0.25418012, -0.24489982, -0.2481167 , -0.24375948, -0.25454811]), 'test_f1_macro': array([0.53394313, 0.55856248, 0.5592331 , 0.56923042, 0.54869996]), 'test_f1_weighted': array([0.53494898, 0.55925536, 0.5602168 , 0.56920255, 0.54989712]), 'test_balanced_accuracy': array([0.53499896, 0.56013136, 0.56022913, 0.57222025, 0.54947711])}</t>
+  </si>
+  <si>
+    <t>[0.43181005 0.6251393  0.4745462  ... 0.4433863  0.49659896 0.46054092]</t>
+  </si>
+  <si>
+    <t>[[1466 1100]
+ [1364 1598]]</t>
+  </si>
+  <si>
+    <t>{'0': {'precision': 0.5180212014134276, 'recall': 0.5713172252533125, 'f1-score': 0.5433654558932542, 'support': 2566.0}, '1': {'precision': 0.5922905856189771, 'recall': 0.5395003376097232, 'f1-score': 0.5646643109540636, 'support': 2962.0}, 'accuracy': 0.5542691751085383, 'macro avg': {'precision': 0.5551558935162023, 'recall': 0.5554087814315178, 'f1-score': 0.5540148834236589, 'support': 5528.0}, 'weighted avg': {'precision': 0.5578160487391941, 'recall': 0.5542691751085383, 'f1-score': 0.5547777584782971, 'support': 5528.0}}</t>
+  </si>
+  <si>
+    <t>{'precisions': array([0.53581766, 0.5359146 , 0.53583062, ..., 1.        , 1.        ,
+       1.        ]), 'recalls': array([1.00000000e+00, 1.00000000e+00, 9.99662390e-01, ...,
+       6.75219446e-04, 3.37609723e-04, 0.00000000e+00]), 'thresholds': array([0.06269497, 0.09320159, 0.10583874, ..., 0.9322194 , 0.94372594,
+       0.94838256], dtype=float32), 'average_precision': 0.6059199236702687}</t>
+  </si>
+  <si>
+    <t>{'fpr': array([0.        , 0.        , 0.        , ..., 0.99961029, 0.99961029,
+       1.        ]), 'tpr': array([0.00000000e+00, 3.37609723e-04, 1.01282917e-03, ...,
+       9.99662390e-01, 1.00000000e+00, 1.00000000e+00]), 'thresholds': array([       inf, 0.94838256, 0.9322194 , ..., 0.10583874, 0.09320159,
+       0.06269497], dtype=float32), 'roc_auc': 0.5818317419451268}</t>
+  </si>
+  <si>
+    <t>Pipeline(steps=[('smote', SMOTE(random_state=42)),
+                ('model',
+                 GradientBoostingClassifier(learning_rate=0.05,
+                                            n_estimators=200))])</t>
+  </si>
+  <si>
+    <t>C:\Users\trott\git\ia_predict_soccer\src\service_ia\training\version_1\fit\best_models\best_mean_under_over_2_5_gb.pkl</t>
+  </si>
+  <si>
+    <t>[0.5641953  0.58589512 0.58499096 0.57647059 0.560181  ]</t>
+  </si>
+  <si>
+    <t>{'fit_time': array([1.04104829, 1.0401969 , 1.03796697, 1.03802705, 1.03662753]), 'score_time': array([0.0126121 , 0.01230097, 0.01293564, 0.01334047, 0.01262307]), 'test_accuracy': array([0.5641953 , 0.58589512, 0.58499096, 0.57647059, 0.560181  ]), 'test_precision': array([0.60571429, 0.63261297, 0.63273453, 0.62601626, 0.60816327]), 'test_recall': array([0.53625632, 0.54300169, 0.53547297, 0.52027027, 0.50337838]), 'test_f1': array([0.56887299, 0.58439201, 0.58005489, 0.56826568, 0.55083179]), 'test_roc_auc': array([0.58536565, 0.61607152, 0.61130081, 0.6142557 , 0.59167062]), 'test_average_precision': array([0.614119  , 0.62491869, 0.62925239, 0.63360769, 0.6215676 ]), 'test_neg_log_loss': array([-0.68829966, -0.67404132, -0.67568911, -0.6739194 , -0.68267189]), 'test_neg_brier_score': array([-0.24685709, -0.24026233, -0.24130689, -0.24043398, -0.24473179]), 'test_f1_macro': array([0.56414399, 0.5858897 , 0.58493361, 0.57631757, 0.55999036]), 'test_f1_weighted': array([0.56448605, 0.58578137, 0.58458954, 0.57574191, 0.55933559]), 'test_balanced_accuracy': array([0.56637378, 0.58923963, 0.58874816, 0.5807979 , 0.56455469])}</t>
+  </si>
+  <si>
+    <t>[0.38555727 0.26927987 0.43043364 ... 0.45687399 0.48195205 0.45736084]</t>
+  </si>
+  <si>
+    <t>[[1612  954]
+ [1399 1563]]</t>
+  </si>
+  <si>
+    <t>{'0': {'precision': 0.5353703088674859, 'recall': 0.6282151208106002, 'f1-score': 0.578088578088578, 'support': 2566.0}, '1': {'precision': 0.6209773539928486, 'recall': 0.5276839972991222, 'f1-score': 0.5705420697207519, 'support': 2962.0}, 'accuracy': 0.5743487698986975, 'macro avg': {'precision': 0.5781738314301672, 'recall': 0.5779495590548611, 'f1-score': 0.574315323904665, 'support': 5528.0}, 'weighted avg': {'precision': 0.581240075086973, 'recall': 0.5743487698986975, 'f1-score': 0.5740450256671777, 'support': 5528.0}}</t>
+  </si>
+  <si>
+    <t>{'precisions': array([0.53581766, 0.53573367, 0.53583062, ..., 1.        , 1.        ,
+       1.        ]), 'recalls': array([1.00000000e+00, 9.99662390e-01, 9.99662390e-01, ...,
+       6.75219446e-04, 3.37609723e-04, 0.00000000e+00]), 'thresholds': array([0.13455352, 0.14440389, 0.17487404, ..., 0.90631831, 0.91353227,
+       0.91794546]), 'average_precision': 0.6237742350509401}</t>
+  </si>
+  <si>
+    <t>{'fpr': array([0.        , 0.        , 0.        , ..., 0.99961029, 1.        ,
+       1.        ]), 'tpr': array([0.00000000e+00, 3.37609723e-04, 1.01282917e-03, ...,
+       9.99662390e-01, 9.99662390e-01, 1.00000000e+00]), 'thresholds': array([       inf, 0.91794546, 0.90631831, ..., 0.17487404, 0.14440389,
+       0.13455352]), 'roc_auc': 0.6037212459403944}</t>
+  </si>
+  <si>
+    <t>Pipeline(steps=[('scaler', StandardScaler()), ('smote', SMOTE(random_state=42)),
+                ('model',
+                 AdaBoostClassifier(algorithm='SAMME', learning_rate=0.5,
+                                    n_estimators=800))])</t>
+  </si>
+  <si>
+    <t>C:\Users\trott\git\ia_predict_soccer\src\service_ia\training\version_1\fit\best_models\best_mean_under_over_2_5_ada.pkl</t>
+  </si>
+  <si>
+    <t>t=mean/event=under_over_2_5/stat=['mean_statistics']/smote=True/scaler=True/stat=['mean_statistics']</t>
+  </si>
+  <si>
+    <t>[0.57414105 0.59764919 0.58860759 0.57104072 0.56470588]</t>
+  </si>
+  <si>
+    <t>[0.48571021 0.48571021 0.58337678 ... 0.4533293  0.47127122 0.46790607]</t>
+  </si>
+  <si>
+    <t>[[1684  882]
+ [1444 1518]]</t>
+  </si>
+  <si>
+    <t>{'0': {'precision': 0.5383631713554987, 'recall': 0.6562743569758379, 'f1-score': 0.5914998243765367, 'support': 2566.0}, '1': {'precision': 0.6325, 'recall': 0.512491559756921, 'f1-score': 0.566206639313689, 'support': 2962.0}, 'accuracy': 0.579232995658466, 'macro avg': {'precision': 0.5854315856777493, 'recall': 0.5843829583663794, 'f1-score': 0.5788532318451128, 'support': 5528.0}, 'weighted avg': {'precision': 0.5888033461827441, 'recall': 0.579232995658466, 'f1-score': 0.5779472892542221, 'support': 5528.0}}</t>
+  </si>
+  <si>
+    <t>{'precisions': array([0.53581766, 0.53583062, 0.53566256, 0.53542308, 0.53543593,
+       0.53553299, 0.53605244, 0.53663004, 0.53672834, 0.53779658,
+       0.53857512, 0.53860362, 0.54097443, 0.54107543, 0.54117647,
+       0.54155747, 0.54431818, 0.54681504, 0.54709727, 0.54866227,
+       0.54845601, 0.54888241, 0.54898911, 0.54968823, 0.55004878,
+       0.55000979, 0.55086751, 0.55088757, 0.55156065, 0.55140372,
+       0.55131501, 0.5514444 , 0.55290581, 0.55301664, 0.55317014,
+       0.55330255, 0.55321285, 0.55530658, 0.55514781, 0.55528356,
+       0.55519282, 0.55555556, 0.55591903, 0.55754581, 0.55777961,
+       0.55947412, 0.55929019, 0.55936455, 0.55950638, 0.56000839,
+       0.56017643, 0.56034483, 0.56087782, 0.56078514, 0.56069242,
+       0.56093948, 0.56108406, 0.56128075, 0.56236696, 0.56248669,
+       0.56251331, 0.56263315, 0.5625933 , 0.56282051, 0.5629408 ,
+       0.5630382 , 0.5637851 , 0.56439814, 0.56734234, 0.56747015,
+       0.56778705, 0.56791516, 0.56803797, 0.56899682, 0.56927642,
+       0.57034483, 0.57060452, 0.57441191, 0.57559682, 0.57528958,
+       0.5758162 , 0.5790932 , 0.57898715, 0.57902697, 0.5814433 ,
+       0.58231469, 0.58246618, 0.58261775, 0.58270383, 0.58272443,
+       0.5835084 , 0.58344284, 0.58364019, 0.58353065, 0.58522273,
+       0.58537887, 0.58955224, 0.58960177, 0.590301  , 0.59046557,
+       0.59429888, 0.59721416, 0.5983702 , 0.59801923, 0.59912152,
+       0.60035842, 0.60023902, 0.60041841, 0.60060241, 0.60470152,
+       0.60577819, 0.60604173, 0.605919  , 0.60608914, 0.60596546,
+       0.6063562 , 0.60636943, 0.60624403, 0.60886962, 0.61874768,
+       0.61860638, 0.62214612, 0.62050497, 0.63223657, 0.6325    ,
+       0.63340292, 0.63644252, 0.63812886, 0.63796909, 0.63915635,
+       0.63981265, 0.64095238, 0.64156339, 0.64139247, 0.64169847,
+       0.64200477, 0.64448858, 0.64875824, 0.6503642 , 0.65299685,
+       0.66534317, 0.66553095, 0.66534091, 0.6653085 , 0.66568743,
+       0.66549089, 0.66588097, 0.66666667, 0.66726404, 0.66766288,
+       0.66907776, 0.66887817, 0.67197452, 0.6759388 , 0.67530598,
+       0.68342086, 0.68369647, 0.68353474, 0.68580295, 0.68686869,
+       0.68662519, 0.68652038, 0.68656716, 0.68607396, 0.68508287,
+       0.68654311, 0.69039735, 0.68896321, 0.68836806, 0.68875327,
+       0.68935428, 0.68926056, 0.69045412, 0.69245837, 0.69162562,
+       0.6913215 , 0.69477912, 0.69547739, 0.69614984, 0.696875  ,
+       0.69578947, 0.69673913, 0.69834254, 0.69565217, 0.69626168,
+       0.69590643, 0.69951923, 0.70036101, 0.7014742 , 0.70036991,
+       0.70136307, 0.70157068, 0.696011  , 0.6969697 , 0.7027417 ,
+       0.70231214, 0.70250368, 0.7013373 , 0.7057903 , 0.70551181,
+       0.70616114, 0.70406504, 0.70473083, 0.71122112, 0.71600688,
+       0.71551724, 0.71268657, 0.71401869, 0.71702128, 0.71205357,
+       0.70438799, 0.70629371, 0.69948187, 0.6987013 , 0.6957672 ,
+       0.69496021, 0.69716088, 0.69863014, 0.70149254, 0.70037453,
+       0.69924812, 0.69230769, 0.69082126, 0.70967742, 0.71351351,
+       0.72108844, 0.71917808, 0.71014493, 0.6984127 , 0.69354839,
+       0.68852459, 0.75280899, 0.76136364, 0.76829268, 0.75      ,
+       0.75342466, 0.77464789, 0.77941176, 0.7761194 , 0.75806452,
+       0.76271186, 0.74545455, 0.73584906, 0.75      , 0.72340426,
+       0.7173913 , 0.71111111, 0.70454545, 0.71428571, 0.75675676,
+       0.73333333, 0.72413793, 0.71428571, 0.73076923, 0.72      ,
+       0.69565217, 0.68181818, 0.7       , 0.68421053, 0.66666667,
+       0.66666667, 0.66666667, 0.71428571, 0.66666667, 0.6       ,
+       0.75      , 0.66666667, 0.5       , 0.        , 1.        ]), 'recalls': array([1.00000000e+00, 9.99662390e-01, 9.98987171e-01, 9.97636732e-01,
+       9.97299122e-01, 9.97299122e-01, 9.93923025e-01, 9.89196489e-01,
+       9.89196489e-01, 9.87170831e-01, 9.85145172e-01, 9.84469953e-01,
+       9.78392978e-01, 9.78392978e-01, 9.78392978e-01, 9.76704929e-01,
+       9.70290344e-01, 9.62187711e-01, 9.60837272e-01, 9.55435517e-01,
+       9.53409858e-01, 9.53409858e-01, 9.53409858e-01, 9.52397029e-01,
+       9.51721810e-01, 9.48683322e-01, 9.43281567e-01, 9.42943957e-01,
+       9.42606347e-01, 9.41593518e-01, 9.41255908e-01, 9.40918298e-01,
+       9.31465226e-01, 9.31465226e-01, 9.30790007e-01, 9.30452397e-01,
+       9.30114787e-01, 9.20324105e-01, 9.19311276e-01, 9.18973666e-01,
+       9.18636057e-01, 9.18298447e-01, 9.17960837e-01, 9.14247130e-01,
+       9.12559082e-01, 9.05131668e-01, 9.04456448e-01, 9.03443619e-01,
+       9.03106009e-01, 9.01080351e-01, 9.00405132e-01, 8.99729912e-01,
+       8.97366644e-01, 8.97029034e-01, 8.96691425e-01, 8.95003376e-01,
+       8.94665766e-01, 8.93652937e-01, 8.91964889e-01, 8.91964889e-01,
+       8.91627279e-01, 8.91627279e-01, 8.90614450e-01, 8.89264011e-01,
+       8.89264011e-01, 8.60904794e-01, 8.60904794e-01, 8.59554355e-01,
+       8.50438893e-01, 8.50438893e-01, 8.49763673e-01, 8.49763673e-01,
+       8.48413234e-01, 8.46387576e-01, 8.41998650e-01, 8.37609723e-01,
+       8.34908845e-01, 8.07900068e-01, 8.05874409e-01, 8.04861580e-01,
+       8.03848751e-01, 7.76164754e-01, 7.75827144e-01, 7.75489534e-01,
+       7.61647535e-01, 7.55908170e-01, 7.55908170e-01, 7.55908170e-01,
+       7.55232951e-01, 7.53882512e-01, 7.50168805e-01, 7.49493585e-01,
+       7.49155976e-01, 7.48818366e-01, 7.40715733e-01, 7.40715733e-01,
+       7.20121540e-01, 7.19783930e-01, 7.15057394e-01, 7.15057394e-01,
+       6.96826469e-01, 6.94800810e-01, 6.94125591e-01, 6.93112762e-01,
+       6.90749494e-01, 6.78595544e-01, 6.78257934e-01, 6.78257934e-01,
+       6.73193788e-01, 6.60027009e-01, 6.58338960e-01, 6.56988521e-01,
+       6.56650912e-01, 6.51924375e-01, 6.51586766e-01, 6.50573937e-01,
+       6.42808913e-01, 6.42471303e-01, 6.16475354e-01, 5.63808238e-01,
+       5.63470628e-01, 5.51991897e-01, 5.47602971e-01, 5.12491560e-01,
+       5.12491560e-01, 5.12153950e-01, 4.95273464e-01, 4.88183660e-01,
+       4.87846050e-01, 4.70627954e-01, 4.61174882e-01, 4.54422687e-01,
+       4.54422687e-01, 4.54085078e-01, 4.54085078e-01, 4.54085078e-01,
+       4.38217421e-01, 4.32140446e-01, 4.22012154e-01, 4.19311276e-01,
+       3.96016205e-01, 3.95678596e-01, 3.95340986e-01, 3.85887914e-01,
+       3.82511816e-01, 3.82174207e-01, 3.81498987e-01, 3.80823768e-01,
+       3.77110061e-01, 3.77110061e-01, 3.74746793e-01, 3.74409183e-01,
+       3.56178258e-01, 3.28156651e-01, 3.16677920e-01, 3.07562458e-01,
+       3.07224848e-01, 3.05536799e-01, 2.98446995e-01, 2.98446995e-01,
+       2.98109386e-01, 2.95746117e-01, 2.95070898e-01, 2.94395679e-01,
+       2.93045240e-01, 2.87643484e-01, 2.81566509e-01, 2.78190412e-01,
+       2.67724510e-01, 2.66711681e-01, 2.66711681e-01, 2.64348413e-01,
+       2.51519244e-01, 2.38690074e-01, 2.37002026e-01, 2.36664416e-01,
+       2.33625928e-01, 2.33625928e-01, 2.25860905e-01, 2.25860905e-01,
+       2.23160027e-01, 2.16407833e-01, 2.13369345e-01, 2.05266712e-01,
+       2.01215395e-01, 2.00877785e-01, 1.96488859e-01, 1.96488859e-01,
+       1.92775152e-01, 1.91762323e-01, 1.91087103e-01, 1.80958812e-01,
+       1.70830520e-01, 1.70830520e-01, 1.64415935e-01, 1.64078325e-01,
+       1.61039838e-01, 1.59351789e-01, 1.52261985e-01, 1.51249156e-01,
+       1.50911546e-01, 1.46185010e-01, 1.45847400e-01, 1.45509791e-01,
+       1.40445645e-01, 1.40108035e-01, 1.28966914e-01, 1.28966914e-01,
+       1.13774477e-01, 1.07697502e-01, 1.02970966e-01, 1.02295746e-01,
+       9.11546253e-02, 9.08170155e-02, 8.87913572e-02, 8.84537475e-02,
+       7.46117488e-02, 6.88723835e-02, 6.34706280e-02, 6.31330182e-02,
+       6.27954085e-02, 4.86158001e-02, 4.82781904e-02, 4.45644835e-02,
+       4.45644835e-02, 3.57866307e-02, 3.54490209e-02, 3.30857529e-02,
+       2.97096556e-02, 2.90344362e-02, 2.83592167e-02, 2.26198515e-02,
+       2.26198515e-02, 2.12694126e-02, 1.92437542e-02, 1.85685348e-02,
+       1.85685348e-02, 1.78933153e-02, 1.75557056e-02, 1.58676570e-02,
+       1.51924375e-02, 1.38419986e-02, 1.31667792e-02, 1.31667792e-02,
+       1.14787306e-02, 1.11411209e-02, 1.08035111e-02, 1.04659014e-02,
+       1.01282917e-02, 9.45307225e-03, 7.42741391e-03, 7.08980419e-03,
+       6.75219446e-03, 6.41458474e-03, 6.07697502e-03, 5.40175557e-03,
+       5.06414585e-03, 4.72653612e-03, 4.38892640e-03, 4.05131668e-03,
+       3.37609723e-03, 2.02565834e-03, 1.68804862e-03, 1.35043889e-03,
+       1.01282917e-03, 1.01282917e-03, 6.75219446e-04, 3.37609723e-04,
+       0.00000000e+00, 0.00000000e+00]), 'thresholds': array([0.15469319, 0.20829986, 0.30184364, 0.32638762, 0.34708104,
+       0.35456261, 0.35503126, 0.35613068, 0.36248916, 0.3627281 ,
+       0.36289393, 0.36347767, 0.36533769, 0.36681486, 0.36700964,
+       0.36758484, 0.36843143, 0.3702663 , 0.37259239, 0.37495752,
+       0.37608266, 0.37706469, 0.37710678, 0.37823246, 0.37880966,
+       0.38046324, 0.38105364, 0.38282993, 0.38358976, 0.38399639,
+       0.38446446, 0.38512993, 0.38590003, 0.38720458, 0.38725861,
+       0.38838041, 0.38895237, 0.39054629, 0.39154794, 0.39207404,
+       0.39319745, 0.39322965, 0.39420259, 0.39534895, 0.39755451,
+       0.39827676, 0.39870545, 0.39900413, 0.39906191, 0.39959651,
+       0.40022457, 0.40221904, 0.40470388, 0.40530532, 0.40666926,
+       0.40766715, 0.40880858, 0.40949182, 0.41021124, 0.41065251,
+       0.41086897, 0.41149643, 0.41277888, 0.41334608, 0.41351597,
+       0.41549733, 0.41760486, 0.41769187, 0.41938524, 0.42210511,
+       0.42502914, 0.42514187, 0.42533607, 0.42776044, 0.42940785,
+       0.42946958, 0.43565772, 0.43648259, 0.43661091, 0.43818927,
+       0.438772  , 0.44053989, 0.44096582, 0.44146561, 0.44450353,
+       0.44501782, 0.44509688, 0.44844133, 0.45003586, 0.4503207 ,
+       0.45093236, 0.45210566, 0.45212057, 0.4533293 , 0.45440106,
+       0.4567343 , 0.45758946, 0.45887595, 0.45922793, 0.45958696,
+       0.46077884, 0.46220365, 0.4638195 , 0.46700239, 0.46790607,
+       0.47063062, 0.47103785, 0.47127122, 0.47250859, 0.47415153,
+       0.47866041, 0.47990223, 0.48571021, 0.48658432, 0.48707312,
+       0.48826424, 0.49008494, 0.49076578, 0.4937284 , 0.49543363,
+       0.49579502, 0.49699444, 0.49745095, 0.49826216, 0.50005246,
+       0.50276177, 0.50415809, 0.50598688, 0.50877624, 0.50914298,
+       0.51169802, 0.51170251, 0.51252211, 0.5165661 , 0.51672219,
+       0.51720512, 0.52367949, 0.52591887, 0.53756429, 0.53791529,
+       0.54089678, 0.54760877, 0.55240873, 0.55261633, 0.55299137,
+       0.56174697, 0.56188945, 0.56205407, 0.56323473, 0.56444839,
+       0.56624151, 0.5662929 , 0.56665816, 0.56686396, 0.56917793,
+       0.56996496, 0.5702707 , 0.57031926, 0.57149462, 0.57152165,
+       0.5732171 , 0.57368009, 0.57444373, 0.5744875 , 0.57479242,
+       0.57774284, 0.57849711, 0.57860655, 0.57878167, 0.57947702,
+       0.58022375, 0.58299557, 0.58337678, 0.58491357, 0.5853597 ,
+       0.58729863, 0.58868769, 0.58956435, 0.58957976, 0.59157116,
+       0.59404357, 0.59751123, 0.59751999, 0.59789366, 0.59886105,
+       0.59887924, 0.60132798, 0.60527155, 0.60662937, 0.60770055,
+       0.60900472, 0.61269917, 0.61371595, 0.61377209, 0.61388314,
+       0.6147889 , 0.61492555, 0.61748431, 0.61879319, 0.61895019,
+       0.62025524, 0.62268033, 0.6228159 , 0.62301993, 0.62333508,
+       0.62373799, 0.62414614, 0.62490277, 0.62701128, 0.62714623,
+       0.62764322, 0.62875331, 0.62928236, 0.63084399, 0.63372269,
+       0.63513614, 0.6385014 , 0.63937145, 0.64341322, 0.64412701,
+       0.64740082, 0.64859773, 0.65008422, 0.65191477, 0.65406501,
+       0.65807016, 0.66097771, 0.66217475, 0.66420721, 0.66824006,
+       0.66853556, 0.67132118, 0.67455773, 0.67512462, 0.67593101,
+       0.67892257, 0.67965021, 0.6811756 , 0.68169877, 0.6832153 ,
+       0.68720046, 0.6887564 , 0.68913205, 0.68987731, 0.69019144,
+       0.69120517, 0.69704388, 0.69906238, 0.70035789, 0.70103713,
+       0.70135275, 0.70554086, 0.70769949, 0.70972691, 0.71232004,
+       0.714866  , 0.71832457, 0.71951282, 0.72467573, 0.72667142,
+       0.7360985 , 0.73832929, 0.74055147, 0.74509572, 0.77787065,
+       0.78153872, 0.80469448, 0.80622033, 0.86830281]), 'average_precision': 0.6338952418800463}</t>
+  </si>
+  <si>
+    <t>{'fpr': array([0.00000000e+00, 3.89711613e-04, 3.89711613e-04, 7.79423227e-04,
+       7.79423227e-04, 1.16913484e-03, 1.94855807e-03, 2.33826968e-03,
+       2.33826968e-03, 2.72798129e-03, 2.72798129e-03, 2.72798129e-03,
+       2.72798129e-03, 3.11769291e-03, 3.11769291e-03, 3.50740452e-03,
+       4.67653936e-03, 5.06625097e-03, 5.06625097e-03, 5.06625097e-03,
+       5.45596259e-03, 5.45596259e-03, 5.45596259e-03, 5.84567420e-03,
+       5.84567420e-03, 5.84567420e-03, 6.23538581e-03, 7.01480904e-03,
+       7.40452065e-03, 7.40452065e-03, 8.18394388e-03, 8.57365549e-03,
+       1.48090413e-02, 1.48090413e-02, 1.55884645e-02, 1.59781761e-02,
+       1.59781761e-02, 2.06547155e-02, 2.10444271e-02, 2.49415433e-02,
+       2.49415433e-02, 3.11769291e-02, 3.11769291e-02, 3.42946220e-02,
+       3.74123149e-02, 4.48168355e-02, 4.48168355e-02, 4.52065472e-02,
+       4.52065472e-02, 4.91036633e-02, 4.98830865e-02, 5.02727981e-02,
+       5.18316446e-02, 5.96258769e-02, 6.00155885e-02, 6.43024162e-02,
+       6.43024162e-02, 6.81995323e-02, 7.05378020e-02, 7.09275136e-02,
+       7.24863601e-02, 7.28760717e-02, 7.32657833e-02, 7.83320343e-02,
+       7.87217459e-02, 8.02805924e-02, 8.02805924e-02, 8.57365549e-02,
+       8.61262666e-02, 8.88542479e-02, 9.39204988e-02, 9.46999221e-02,
+       9.46999221e-02, 9.70381917e-02, 9.74279034e-02, 1.01325019e-01,
+       1.01325019e-01, 1.03663289e-01, 1.06391270e-01, 1.08729540e-01,
+       1.12626656e-01, 1.13406080e-01, 1.13795791e-01, 1.18082619e-01,
+       1.18472330e-01, 1.21979735e-01, 1.21979735e-01, 1.22369447e-01,
+       1.30163679e-01, 1.37568200e-01, 1.38737334e-01, 1.39127046e-01,
+       1.39906469e-01, 1.44972720e-01, 1.45752143e-01, 1.51597818e-01,
+       1.55494934e-01, 1.55494934e-01, 1.55494934e-01, 1.55884645e-01,
+       1.57053780e-01, 1.57053780e-01, 1.57833203e-01, 1.63289166e-01,
+       1.64068589e-01, 1.64458301e-01, 1.75759938e-01, 1.81605612e-01,
+       2.00701481e-01, 2.13951676e-01, 2.13951676e-01, 2.16679657e-01,
+       2.17069369e-01, 2.19797350e-01, 2.20966485e-01, 2.21745908e-01,
+       2.21745908e-01, 2.24084178e-01, 2.29540140e-01, 2.29540140e-01,
+       2.29929852e-01, 2.57209665e-01, 2.61886204e-01, 2.70070148e-01,
+       2.79033515e-01, 2.92283710e-01, 2.93063133e-01, 2.93063133e-01,
+       2.93842557e-01, 2.99688231e-01, 3.06703040e-01, 3.19563523e-01,
+       3.19563523e-01, 3.26578332e-01, 3.42166797e-01, 3.43725643e-01,
+       3.44115355e-01, 3.86593920e-01, 3.86983632e-01, 4.01013250e-01,
+       4.01013250e-01, 4.57131723e-01, 4.81683554e-01, 4.81683554e-01,
+       4.87529228e-01, 4.89088075e-01, 4.89088075e-01, 4.92985191e-01,
+       4.92985191e-01, 4.94544037e-01, 4.98051442e-01, 5.16757599e-01,
+       5.21044427e-01, 5.21434139e-01, 5.21434139e-01, 5.33515199e-01,
+       5.37802027e-01, 5.37802027e-01, 5.40919719e-01, 5.49103663e-01,
+       5.72486360e-01, 5.72876072e-01, 5.78332034e-01, 5.78721746e-01,
+       6.05611847e-01, 6.06001559e-01, 6.16913484e-01, 6.16913484e-01,
+       6.17692907e-01, 6.18082619e-01, 6.23148870e-01, 6.24318005e-01,
+       6.25097428e-01, 6.25876851e-01, 6.32891660e-01, 6.50818394e-01,
+       6.51208106e-01, 6.51208106e-01, 6.83554170e-01, 6.85892440e-01,
+       6.85892440e-01, 6.90958691e-01, 7.25253313e-01, 7.28371005e-01,
+       7.35385814e-01, 7.40062354e-01, 7.44738893e-01, 7.46297740e-01,
+       7.46687451e-01, 7.48246298e-01, 7.48636009e-01, 7.65783320e-01,
+       7.68901013e-01, 7.71239283e-01, 7.96960249e-01, 7.97349961e-01,
+       7.99298519e-01, 8.00077942e-01, 8.00467654e-01, 8.00857366e-01,
+       8.01247077e-01, 8.06313328e-01, 8.07872175e-01, 8.08651598e-01,
+       8.10989867e-01, 8.10989867e-01, 8.14886984e-01, 8.17225253e-01,
+       8.20732658e-01, 8.21512081e-01, 8.22681216e-01, 8.22681216e-01,
+       8.35151988e-01, 8.37490257e-01, 8.46453624e-01, 8.49571317e-01,
+       8.49571317e-01, 8.50350740e-01, 8.50740452e-01, 8.67108340e-01,
+       8.67108340e-01, 8.67887763e-01, 8.69056898e-01, 8.69446610e-01,
+       8.83476228e-01, 8.84255651e-01, 8.84255651e-01, 8.84645362e-01,
+       8.87373344e-01, 8.87763055e-01, 8.95946999e-01, 8.98674981e-01,
+       9.00623539e-01, 9.04130943e-01, 9.04520655e-01, 9.06079501e-01,
+       9.07248636e-01, 9.18160561e-01, 9.20498831e-01, 9.37646142e-01,
+       9.54403741e-01, 9.57521434e-01, 9.58300857e-01, 9.73499610e-01,
+       9.74279034e-01, 9.79345284e-01, 9.85580670e-01, 9.85970382e-01,
+       9.92985191e-01, 9.98441154e-01, 9.98830865e-01, 9.99220577e-01,
+       9.99610288e-01, 9.99610288e-01, 1.00000000e+00]), 'tpr': array([0.        , 0.        , 0.00101283, 0.00101283, 0.00168805,
+       0.00202566, 0.0033761 , 0.00405132, 0.00472654, 0.00506415,
+       0.00540176, 0.00607698, 0.00641458, 0.00675219, 0.00742741,
+       0.00945307, 0.01012829, 0.0104659 , 0.01147873, 0.01316678,
+       0.01316678, 0.013842  , 0.01519244, 0.01586766, 0.01755571,
+       0.01789332, 0.01856853, 0.01856853, 0.01924375, 0.02126941,
+       0.02261985, 0.02261985, 0.02835922, 0.02970966, 0.03308575,
+       0.03544902, 0.03578663, 0.04456448, 0.04456448, 0.04827819,
+       0.0486158 , 0.06279541, 0.06347063, 0.06887238, 0.07461175,
+       0.08845375, 0.08879136, 0.09081702, 0.09115463, 0.10229575,
+       0.10297097, 0.1076975 , 0.11377448, 0.12896691, 0.12896691,
+       0.14010804, 0.14044564, 0.14550979, 0.1458474 , 0.14618501,
+       0.15091155, 0.15124916, 0.15226199, 0.15935179, 0.16103984,
+       0.16407833, 0.16441594, 0.17083052, 0.17083052, 0.18095881,
+       0.1910871 , 0.19176232, 0.19277515, 0.19648886, 0.19648886,
+       0.20087779, 0.2012154 , 0.20526671, 0.21336935, 0.21640783,
+       0.22316003, 0.2258609 , 0.2258609 , 0.23362593, 0.23362593,
+       0.23666442, 0.23700203, 0.23869007, 0.25151924, 0.26434841,
+       0.26671168, 0.26671168, 0.26772451, 0.27819041, 0.28156651,
+       0.28764348, 0.29304524, 0.29439568, 0.2950709 , 0.29574612,
+       0.29810939, 0.298447  , 0.298447  , 0.3055368 , 0.30722485,
+       0.30756246, 0.31667792, 0.32815665, 0.35617826, 0.37440918,
+       0.37474679, 0.37711006, 0.37711006, 0.38082377, 0.38149899,
+       0.38217421, 0.38251182, 0.38588791, 0.39534099, 0.3956786 ,
+       0.39601621, 0.41931128, 0.42201215, 0.43214045, 0.43821742,
+       0.45408508, 0.45408508, 0.45442269, 0.45442269, 0.46117488,
+       0.47062795, 0.48784605, 0.48818366, 0.49527346, 0.51215395,
+       0.51249156, 0.51249156, 0.54760297, 0.5519919 , 0.56347063,
+       0.56380824, 0.61647535, 0.6424713 , 0.64280891, 0.65057394,
+       0.65158677, 0.65192438, 0.65665091, 0.65698852, 0.65833896,
+       0.66002701, 0.67319379, 0.67825793, 0.67825793, 0.67859554,
+       0.69074949, 0.69311276, 0.69412559, 0.69480081, 0.69682647,
+       0.71505739, 0.71505739, 0.71978393, 0.72012154, 0.74071573,
+       0.74071573, 0.74881837, 0.74915598, 0.74949359, 0.7501688 ,
+       0.75388251, 0.75523295, 0.75590817, 0.75590817, 0.76164754,
+       0.77548953, 0.77582714, 0.77616475, 0.80384875, 0.80486158,
+       0.80587441, 0.80790007, 0.83490885, 0.83760972, 0.84199865,
+       0.84638758, 0.84841323, 0.84976367, 0.84976367, 0.85043889,
+       0.85043889, 0.85955436, 0.86090479, 0.86090479, 0.88926401,
+       0.88926401, 0.89061445, 0.89162728, 0.89162728, 0.89196489,
+       0.89196489, 0.89365294, 0.89466577, 0.89500338, 0.89669142,
+       0.89736664, 0.89972991, 0.90108035, 0.90310601, 0.90344362,
+       0.90445645, 0.90513167, 0.91255908, 0.91424713, 0.91796084,
+       0.91863606, 0.91897367, 0.91931128, 0.92032411, 0.93011479,
+       0.9304524 , 0.93079001, 0.93146523, 0.93146523, 0.9409183 ,
+       0.94125591, 0.94159352, 0.94260635, 0.94294396, 0.94328157,
+       0.94868332, 0.95172181, 0.95239703, 0.95340986, 0.95340986,
+       0.95340986, 0.95543552, 0.96083727, 0.96218771, 0.97029034,
+       0.97670493, 0.97839298, 0.97839298, 0.98446995, 0.98514517,
+       0.98717083, 0.98919649, 0.98919649, 0.99392302, 0.99729912,
+       0.99729912, 0.99763673, 0.99898717, 0.99966239, 1.        ]), 'thresholds': array([       inf, 0.86830281, 0.78153872, 0.77787065, 0.74055147,
+       0.73832929, 0.7360985 , 0.72667142, 0.71951282, 0.71832457,
+       0.714866  , 0.71232004, 0.70972691, 0.70769949, 0.70135275,
+       0.70103713, 0.70035789, 0.69906238, 0.69019144, 0.68987731,
+       0.68913205, 0.6887564 , 0.68720046, 0.6832153 , 0.68169877,
+       0.6811756 , 0.67965021, 0.67892257, 0.67593101, 0.67512462,
+       0.67455773, 0.67132118, 0.66853556, 0.66420721, 0.66217475,
+       0.66097771, 0.65807016, 0.65406501, 0.65191477, 0.65008422,
+       0.64859773, 0.64740082, 0.64341322, 0.63937145, 0.6385014 ,
+       0.63513614, 0.63372269, 0.63084399, 0.62928236, 0.62875331,
+       0.62764322, 0.62714623, 0.62701128, 0.62490277, 0.62414614,
+       0.62373799, 0.62333508, 0.62301993, 0.6228159 , 0.62268033,
+       0.62025524, 0.61895019, 0.61879319, 0.61748431, 0.61492555,
+       0.6147889 , 0.61388314, 0.61377209, 0.61371595, 0.61269917,
+       0.60900472, 0.60770055, 0.60662937, 0.60527155, 0.60132798,
+       0.59887924, 0.59886105, 0.59789366, 0.59751999, 0.59751123,
+       0.59404357, 0.59157116, 0.58957976, 0.58956435, 0.58868769,
+       0.58729863, 0.5853597 , 0.58491357, 0.58337678, 0.58299557,
+       0.58022375, 0.57947702, 0.57878167, 0.57860655, 0.57849711,
+       0.57774284, 0.57479242, 0.5744875 , 0.57444373, 0.57368009,
+       0.5732171 , 0.57152165, 0.57149462, 0.57031926, 0.5702707 ,
+       0.56996496, 0.56917793, 0.56686396, 0.56665816, 0.5662929 ,
+       0.56624151, 0.56444839, 0.56323473, 0.56205407, 0.56188945,
+       0.56174697, 0.55299137, 0.55261633, 0.55240873, 0.54760877,
+       0.54089678, 0.53791529, 0.53756429, 0.52591887, 0.52367949,
+       0.51720512, 0.5165661 , 0.51252211, 0.51170251, 0.51169802,
+       0.50914298, 0.50877624, 0.50598688, 0.50415809, 0.50276177,
+       0.50005246, 0.49826216, 0.49745095, 0.49699444, 0.49579502,
+       0.49543363, 0.4937284 , 0.49076578, 0.49008494, 0.48826424,
+       0.48707312, 0.48658432, 0.48571021, 0.47990223, 0.47866041,
+       0.47415153, 0.47250859, 0.47127122, 0.47103785, 0.47063062,
+       0.46790607, 0.46700239, 0.4638195 , 0.46220365, 0.46077884,
+       0.45958696, 0.45922793, 0.45887595, 0.45758946, 0.4567343 ,
+       0.45440106, 0.4533293 , 0.45212057, 0.45210566, 0.45093236,
+       0.4503207 , 0.45003586, 0.44844133, 0.44501782, 0.44450353,
+       0.44146561, 0.44096582, 0.44053989, 0.438772  , 0.43818927,
+       0.43661091, 0.43648259, 0.43565772, 0.42946958, 0.42940785,
+       0.42776044, 0.42533607, 0.42514187, 0.42502914, 0.42210511,
+       0.41938524, 0.41769187, 0.41760486, 0.41549733, 0.41351597,
+       0.41334608, 0.41277888, 0.41149643, 0.41086897, 0.41065251,
+       0.41021124, 0.40949182, 0.40880858, 0.40766715, 0.40666926,
+       0.40470388, 0.40221904, 0.39959651, 0.39906191, 0.39900413,
+       0.39870545, 0.39827676, 0.39755451, 0.39534895, 0.39420259,
+       0.39319745, 0.39207404, 0.39154794, 0.39054629, 0.38895237,
+       0.38838041, 0.38725861, 0.38720458, 0.38590003, 0.38512993,
+       0.38446446, 0.38399639, 0.38358976, 0.38282993, 0.38105364,
+       0.38046324, 0.37880966, 0.37823246, 0.37710678, 0.37706469,
+       0.37608266, 0.37495752, 0.37259239, 0.3702663 , 0.36843143,
+       0.36758484, 0.36700964, 0.36533769, 0.36347767, 0.36289393,
+       0.3627281 , 0.36248916, 0.35613068, 0.35503126, 0.35456261,
+       0.34708104, 0.32638762, 0.30184364, 0.20829986, 0.15469319]), 'roc_auc': 0.6144828518995875}</t>
+  </si>
+  <si>
+    <t>{'fit_time': array([2.04153895, 2.05814981, 2.03889489, 2.0290122 , 2.0098567 ]), 'score_time': array([0.14250445, 0.14375949, 0.14347124, 0.14428425, 0.14299417]), 'test_accuracy': array([0.57414105, 0.59764919, 0.58860759, 0.57104072, 0.56470588]), 'test_precision': array([0.63436123, 0.64919355, 0.62851782, 0.6460396 , 0.60818713]), 'test_recall': array([0.4856661 , 0.54300169, 0.56587838, 0.44087838, 0.52702703]), 'test_f1': array([0.55014327, 0.59136823, 0.59555556, 0.52409639, 0.56470588]), 'test_roc_auc': array([0.597553  , 0.63791998, 0.62837838, 0.61131032, 0.60854769]), 'test_average_precision': array([0.60960689, 0.65227066, 0.64169926, 0.61725971, 0.64239669]), 'test_neg_log_loss': array([-0.68047227, -0.66701142, -0.66965744, -0.67667054, -0.67500601]), 'test_neg_brier_score': array([-0.24352819, -0.23714033, -0.23840738, -0.24168038, -0.24116311]), 'test_f1_macro': array([0.57292571, 0.5975541 , 0.58848615, 0.56682579, 0.56470588]), 'test_f1_weighted': array([0.57127779, 0.59710666, 0.58898472, 0.56377093, 0.56470588]), 'test_balanced_accuracy': array([0.58103968, 0.6019102 , 0.59033219, 0.58106297, 0.56760708])}</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0.579232995658466</t>
+  </si>
+  <si>
+    <t>0.6325</t>
+  </si>
+  <si>
+    <t>0.512491559756921</t>
+  </si>
+  <si>
+    <t>0.566206639313689</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -422,6 +1059,14 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -479,12 +1124,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -790,35 +1436,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -844,7 +1490,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -870,7 +1516,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -896,7 +1542,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -922,7 +1568,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -948,7 +1594,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -974,7 +1620,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1000,7 +1646,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1026,7 +1672,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1052,7 +1698,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -1078,7 +1724,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -1111,70 +1757,70 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:R13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="14" max="14" width="15.21875" customWidth="1"/>
-    <col min="15" max="15" width="22.21875" customWidth="1"/>
+    <col min="14" max="14" width="15.1796875" customWidth="1"/>
+    <col min="15" max="15" width="22.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>62</v>
       </c>
@@ -1230,7 +1876,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -1255,36 +1901,378 @@
       <c r="H3" t="s">
         <v>78</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3">
+        <v>0.5</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>0.66551201558778961</v>
+      </c>
+      <c r="L3">
+        <v>0.78743016759776541</v>
+      </c>
+      <c r="M3">
+        <v>0.78240355259505967</v>
+      </c>
+      <c r="N3">
+        <v>0.78490881247389666</v>
+      </c>
+      <c r="O3" t="s">
         <v>79</v>
       </c>
-      <c r="J3" t="s">
+      <c r="P3" t="s">
         <v>80</v>
       </c>
-      <c r="K3" t="s">
+      <c r="Q3" t="s">
         <v>81</v>
       </c>
-      <c r="L3" t="s">
+      <c r="R3" t="s">
         <v>82</v>
       </c>
-      <c r="M3" t="s">
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>83</v>
       </c>
-      <c r="N3" t="s">
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
         <v>84</v>
       </c>
-      <c r="O3" t="s">
+      <c r="D4" t="s">
         <v>85</v>
       </c>
-      <c r="P3" t="s">
+      <c r="E4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" t="s">
         <v>86</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="G4" t="s">
         <v>87</v>
       </c>
-      <c r="R3" t="s">
+      <c r="H4" t="s">
         <v>88</v>
       </c>
+      <c r="I4">
+        <v>0.5</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>0.58049927641099852</v>
+      </c>
+      <c r="L4">
+        <v>0.59289222767986127</v>
+      </c>
+      <c r="M4">
+        <v>0.69277515192437544</v>
+      </c>
+      <c r="N4">
+        <v>0.63895375992526859</v>
+      </c>
+      <c r="O4" t="s">
+        <v>89</v>
+      </c>
+      <c r="P4" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>91</v>
+      </c>
+      <c r="R4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H5" t="s">
+        <v>98</v>
+      </c>
+      <c r="I5">
+        <v>0.5</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>0.5873733719247467</v>
+      </c>
+      <c r="L5">
+        <v>0.6002945508100147</v>
+      </c>
+      <c r="M5">
+        <v>0.6880486158001351</v>
+      </c>
+      <c r="N5">
+        <v>0.64118294793141417</v>
+      </c>
+      <c r="O5" t="s">
+        <v>99</v>
+      </c>
+      <c r="P5" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>101</v>
+      </c>
+      <c r="R5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F6" t="s">
+        <v>106</v>
+      </c>
+      <c r="G6" t="s">
+        <v>107</v>
+      </c>
+      <c r="H6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I6">
+        <v>0.5</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>0.56856005788712016</v>
+      </c>
+      <c r="L6">
+        <v>0.60825515947467168</v>
+      </c>
+      <c r="M6">
+        <v>0.54726536124240377</v>
+      </c>
+      <c r="N6">
+        <v>0.57615070197263196</v>
+      </c>
+      <c r="O6" t="s">
+        <v>109</v>
+      </c>
+      <c r="P6" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>111</v>
+      </c>
+      <c r="R6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" t="s">
+        <v>115</v>
+      </c>
+      <c r="G7" t="s">
+        <v>116</v>
+      </c>
+      <c r="H7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I7">
+        <v>0.5</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>0.55426917510853835</v>
+      </c>
+      <c r="L7">
+        <v>0.59229058561897707</v>
+      </c>
+      <c r="M7">
+        <v>0.53950033760972316</v>
+      </c>
+      <c r="N7">
+        <v>0.56466431095406355</v>
+      </c>
+      <c r="O7" t="s">
+        <v>118</v>
+      </c>
+      <c r="P7" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>120</v>
+      </c>
+      <c r="R7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>122</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" t="s">
+        <v>124</v>
+      </c>
+      <c r="G8" t="s">
+        <v>125</v>
+      </c>
+      <c r="H8" t="s">
+        <v>126</v>
+      </c>
+      <c r="I8">
+        <v>0.5</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>0.57434876989869754</v>
+      </c>
+      <c r="L8">
+        <v>0.62097735399284859</v>
+      </c>
+      <c r="M8">
+        <v>0.52768399729912219</v>
+      </c>
+      <c r="N8">
+        <v>0.57054206972075194</v>
+      </c>
+      <c r="O8" t="s">
+        <v>127</v>
+      </c>
+      <c r="P8" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>129</v>
+      </c>
+      <c r="R8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>131</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>132</v>
+      </c>
+      <c r="D9" t="s">
+        <v>133</v>
+      </c>
+      <c r="E9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F9" t="s">
+        <v>134</v>
+      </c>
+      <c r="G9" t="s">
+        <v>140</v>
+      </c>
+      <c r="H9" t="s">
+        <v>135</v>
+      </c>
+      <c r="I9" t="s">
+        <v>141</v>
+      </c>
+      <c r="J9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K9" t="s">
+        <v>143</v>
+      </c>
+      <c r="L9" t="s">
+        <v>144</v>
+      </c>
+      <c r="M9" t="s">
+        <v>145</v>
+      </c>
+      <c r="N9" t="s">
+        <v>146</v>
+      </c>
+      <c r="O9" t="s">
+        <v>136</v>
+      </c>
+      <c r="P9" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>138</v>
+      </c>
+      <c r="R9" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="B10" s="2"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="H13" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/src/service_ia/training/version_1/fit/report_fit_grid.xlsx
+++ b/src/service_ia/training/version_1/fit/report_fit_grid.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trotta\git\Predict Soccer\ia_predict_soccer\src\service_ia\training\version_1\fit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A8A055A-F0C3-4653-B327-056D4B2CD545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0968D60F-BC0E-4E1B-BEEC-935A01254619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report BEST FIT" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="99">
   <si>
     <t>data</t>
   </si>
@@ -387,12 +387,6 @@
        1.        ]), 'tpr': array([0.        , 0.01776298, 0.02026089, ..., 0.99888981, 1.        ,
        1.        ]), 'thresholds': array([       inf, 1.        , 0.9975    , ..., 0.03416667, 0.01666667,
        0.01333333]), 'roc_auc': np.float64(0.574293130615126)}</t>
-  </si>
-  <si>
-    <t>C:\Users\trotta\git\Predict Soccer\ia_predict_soccer\src\service_ia\training\version_1\fit\best_models\mean_under_over_1_5_stacking_predict_proba_calibrated_sigmoid.pkl</t>
-  </si>
-  <si>
-    <t>t=mean/event=under_over_1_5/stat=['mean_statistics']/smote=True/scaler=True/stack_method=predict_proba/passthrough=False</t>
   </si>
   <si>
     <t>StackingClassifier(cv=5,
@@ -435,6 +429,9 @@
     <t>C:\Users\trotta\git\Predict Soccer\ia_predict_soccer\src\service_ia\training\version_1\fit\best_models\mean_under_over_1_5_stacking_predict_proba.pkl</t>
   </si>
   <si>
+    <t>t=mean/event=under_over_1_5/stat=['mean_statistics']/smote=True/scaler=True/stack_method=predict_proba/passthrough=False</t>
+  </si>
+  <si>
     <t>[0.74242424 0.74458874 0.71536797 0.745671   0.7291441 ]</t>
   </si>
   <si>
@@ -461,89 +458,6 @@
        1.        ]), 'tpr': array([0.        , 0.0036081 , 0.00471829, ..., 0.99944491, 0.99944491,
        1.        ]), 'thresholds': array([       inf, 1.        , 0.999375  , ..., 0.15520833, 0.144375  ,
        0.09020833]), 'roc_auc': np.float64(0.5295509155756031)}</t>
-  </si>
-  <si>
-    <t>StackingClassifier(cv=5,
-                   estimators=[('rf',
-                                CalibratedClassifierCV(estimator=Pipeline(steps=[('smote',
-                                                                                  SMOTE(random_state=42)),
-                                                                                 ('model',
-                                                                                  RandomForestClassifier(bootstrap=False,
-                                                                                                         max_features='log2',
-                                                                                                         min_samples_split=5,
-                                                                                                         n_estimators=400,
-                                                                                                         n_jobs=-1,
-                                                                                                         random_state=42))]))),
-                               ('svc',
-                                CalibratedClassifierCV(estimator=Pipeline(steps=[('scaler',
-                                                                                  StandardScaler()),
-                                                                                 ('smo...
-                                                                                                max_cat_to_onehot=None,
-                                                                                                max_delta_step=None,
-                                                                                                max_depth=3,
-                                                                                                max_leaves=None,
-                                                                                                min_child_weight=None,
-                                                                                                missing=nan,
-                                                                                                monotone_constraints=None,
-                                                                                                multi_strategy=None,
-                                                                                                n_estimators=200,
-                                                                                                n_jobs=None,
-                                                                                                num_parallel_tree=None,
-                                                                                                random_state=None, ...))])))],
-                   final_estimator=LogisticRegression(C=0.75,
-                                                      class_weight='balanced',
-                                                      max_iter=500),
-                   n_jobs=-1, stack_method='predict_proba', verbose=2)</t>
-  </si>
-  <si>
-    <t>2025-10-17</t>
-  </si>
-  <si>
-    <t>[0.61038961 0.64069264 0.60497835 0.63311688 0.60780065]</t>
-  </si>
-  <si>
-    <t>{'fit_time': array([ 83.3331039 ,  80.11974335, 100.03772163,  98.44357538,
-        89.11612964]), 'score_time': array([5.71174383, 5.63468742, 7.78887892, 5.88189149, 5.90735054]), 'test_accuracy': array([0.61038961, 0.64069264, 0.60497835, 0.63311688, 0.60780065]), 'test_precision': array([0.81034483, 0.81729201, 0.81560284, 0.83159722, 0.82664234]), 'test_recall': array([0.65277778, 0.69486824, 0.63800277, 0.66435506, 0.62916667]), 'test_f1': array([0.72307692, 0.75112444, 0.71595331, 0.7386276 , 0.71451104]), 'test_roc_auc': array([0.56676198, 0.59780819, 0.59236966, 0.62394184, 0.616263  ]), 'test_average_precision': array([0.80283453, 0.83141227, 0.81969632, 0.84385609, 0.84696127]), 'test_neg_log_loss': array([-0.68205662, -0.67917674, -0.6801103 , -0.67749911, -0.6835766 ]), 'test_neg_brier_score': array([-0.24437827, -0.242975  , -0.24349011, -0.24217415, -0.24521479]), 'test_f1_macro': array([0.53307131, 0.55260502, 0.53382035, 0.5616913 , 0.54410673]), 'test_f1_weighted': array([0.63917834, 0.66389621, 0.63592519, 0.66088286, 0.6395553 ]), 'test_balanced_accuracy': array([0.55678105, 0.57157205, 0.56284375, 0.59326128, 0.58059319])}</t>
-  </si>
-  <si>
-    <t>[0.53847594 0.52222964 0.53991679 ... 0.45521332 0.4993918  0.50059689]</t>
-  </si>
-  <si>
-    <t>0.5</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>0.6193981381251353</t>
-  </si>
-  <si>
-    <t>0.820201318986463</t>
-  </si>
-  <si>
-    <t>0.655842353594227</t>
-  </si>
-  <si>
-    <t>0.7288710672424429</t>
-  </si>
-  <si>
-    <t>[[ 498  518]
- [1240 2363]]</t>
-  </si>
-  <si>
-    <t>{'0': {'precision': 0.286536248561565, 'recall': 0.49015748031496065, 'f1-score': 0.3616557734204793, 'support': 1016.0}, '1': {'precision': 0.820201318986463, 'recall': 0.655842353594227, 'f1-score': 0.7288710672424429, 'support': 3603.0}, 'accuracy': 0.6193981381251353, 'macro avg': {'precision': 0.553368783774014, 'recall': 0.5729999169545938, 'f1-score': 0.545263420331461, 'support': 4619.0}, 'weighted avg': {'precision': 0.7028158001400251, 'recall': 0.6193981381251353, 'f1-score': 0.6480980127884236, 'support': 4619.0}}</t>
-  </si>
-  <si>
-    <t>{'precisions': array([0.78003897, 0.77999134, 0.77994369, ..., 1.        , 1.        ,
-       1.        ]), 'recalls': array([1.00000000e+00, 9.99722454e-01, 9.99444907e-01, ...,
-       5.55092978e-04, 2.77546489e-04, 0.00000000e+00]), 'thresholds': array([0.34656484, 0.35275031, 0.35619831, ..., 0.59535853, 0.59554416,
-       0.59817101]), 'average_precision': np.float64(0.8218198784763399)}</t>
-  </si>
-  <si>
-    <t>{'fpr': array([0.        , 0.        , 0.        , ..., 0.99901575, 1.        ,
-       1.        ]), 'tpr': array([0.00000000e+00, 2.77546489e-04, 8.32639467e-04, ...,
-       9.98612268e-01, 9.98612268e-01, 1.00000000e+00]), 'thresholds': array([       inf, 0.59817101, 0.59535853, ..., 0.36166499, 0.35963641,
-       0.34656484]), 'roc_auc': np.float64(0.5965025864273211)}</t>
   </si>
 </sst>
 </file>
@@ -1237,7 +1151,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="14" max="14" width="18" customWidth="1"/>
@@ -1470,28 +1384,28 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B5" t="s">
         <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
         <v>63</v>
       </c>
       <c r="F5" t="s">
+        <v>92</v>
+      </c>
+      <c r="G5" t="s">
         <v>93</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>94</v>
-      </c>
-      <c r="H5" t="s">
-        <v>95</v>
       </c>
       <c r="I5">
         <v>0.5</v>
@@ -1512,72 +1426,16 @@
         <v>0.84448969203359636</v>
       </c>
       <c r="O5" t="s">
+        <v>95</v>
+      </c>
+      <c r="P5" t="s">
         <v>96</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>97</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>98</v>
-      </c>
-      <c r="R5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G6" t="s">
-        <v>103</v>
-      </c>
-      <c r="H6" t="s">
-        <v>104</v>
-      </c>
-      <c r="I6" t="s">
-        <v>105</v>
-      </c>
-      <c r="J6" t="s">
-        <v>106</v>
-      </c>
-      <c r="K6" t="s">
-        <v>107</v>
-      </c>
-      <c r="L6" t="s">
-        <v>108</v>
-      </c>
-      <c r="M6" t="s">
-        <v>109</v>
-      </c>
-      <c r="N6" t="s">
-        <v>110</v>
-      </c>
-      <c r="O6" t="s">
-        <v>111</v>
-      </c>
-      <c r="P6" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>113</v>
-      </c>
-      <c r="R6" t="s">
-        <v>114</v>
       </c>
     </row>
   </sheetData>
